--- a/docs/case_files/CASE_GUA.xlsx
+++ b/docs/case_files/CASE_GUA.xlsx
@@ -28156,9 +28156,11 @@
       <c r="AD194" s="14" t="n">
         <v>0.7679312376206273</v>
       </c>
-      <c r="AE194" s="14" t="inlineStr"/>
-      <c r="AF194" s="14" t="inlineStr"/>
-      <c r="AG194" s="14" t="inlineStr"/>
+      <c r="AE194" s="14" t="n">
+        <v>133763.5</v>
+      </c>
+      <c r="AF194" s="14" t="n"/>
+      <c r="AG194" s="14" t="n"/>
       <c r="AH194" s="14" t="inlineStr"/>
       <c r="AI194" s="14" t="inlineStr">
         <is>
@@ -28312,9 +28314,11 @@
       <c r="AD195" s="14" t="n">
         <v>0.8870390275210638</v>
       </c>
-      <c r="AE195" s="14" t="inlineStr"/>
-      <c r="AF195" s="14" t="inlineStr"/>
-      <c r="AG195" s="14" t="inlineStr"/>
+      <c r="AE195" s="14" t="n">
+        <v>2782883.09</v>
+      </c>
+      <c r="AF195" s="14" t="n"/>
+      <c r="AG195" s="14" t="n"/>
       <c r="AH195" s="14" t="inlineStr"/>
       <c r="AI195" s="14" t="inlineStr">
         <is>
@@ -28468,9 +28472,11 @@
       <c r="AD196" s="14" t="n">
         <v>0.901265524513426</v>
       </c>
-      <c r="AE196" s="14" t="inlineStr"/>
-      <c r="AF196" s="14" t="inlineStr"/>
-      <c r="AG196" s="14" t="inlineStr"/>
+      <c r="AE196" s="14" t="n">
+        <v>424020.27</v>
+      </c>
+      <c r="AF196" s="14" t="n"/>
+      <c r="AG196" s="14" t="n"/>
       <c r="AH196" s="14" t="inlineStr"/>
       <c r="AI196" s="14" t="inlineStr">
         <is>
@@ -28624,9 +28630,11 @@
       <c r="AD197" s="14" t="n">
         <v>0.8702244940145547</v>
       </c>
-      <c r="AE197" s="14" t="inlineStr"/>
-      <c r="AF197" s="14" t="inlineStr"/>
-      <c r="AG197" s="14" t="inlineStr"/>
+      <c r="AE197" s="14" t="n">
+        <v>112152</v>
+      </c>
+      <c r="AF197" s="14" t="n"/>
+      <c r="AG197" s="14" t="n"/>
       <c r="AH197" s="14" t="inlineStr"/>
       <c r="AI197" s="14" t="inlineStr">
         <is>
@@ -28780,9 +28788,11 @@
       <c r="AD198" s="14" t="n">
         <v>0.8665818841929512</v>
       </c>
-      <c r="AE198" s="14" t="inlineStr"/>
-      <c r="AF198" s="14" t="inlineStr"/>
-      <c r="AG198" s="14" t="inlineStr"/>
+      <c r="AE198" s="14" t="n">
+        <v>41359.21</v>
+      </c>
+      <c r="AF198" s="14" t="n"/>
+      <c r="AG198" s="14" t="n"/>
       <c r="AH198" s="14" t="inlineStr"/>
       <c r="AI198" s="14" t="inlineStr">
         <is>
@@ -28936,9 +28946,11 @@
       <c r="AD199" s="14" t="n">
         <v>0.8760104412928778</v>
       </c>
-      <c r="AE199" s="14" t="inlineStr"/>
-      <c r="AF199" s="14" t="inlineStr"/>
-      <c r="AG199" s="14" t="inlineStr"/>
+      <c r="AE199" s="14" t="n">
+        <v>41513.48</v>
+      </c>
+      <c r="AF199" s="14" t="n"/>
+      <c r="AG199" s="14" t="n"/>
       <c r="AH199" s="14" t="inlineStr"/>
       <c r="AI199" s="14" t="inlineStr">
         <is>
@@ -29092,9 +29104,11 @@
       <c r="AD200" s="14" t="n">
         <v>0.7505972657923646</v>
       </c>
-      <c r="AE200" s="14" t="inlineStr"/>
-      <c r="AF200" s="14" t="inlineStr"/>
-      <c r="AG200" s="14" t="inlineStr"/>
+      <c r="AE200" s="14" t="n">
+        <v>85372.74000000001</v>
+      </c>
+      <c r="AF200" s="14" t="n"/>
+      <c r="AG200" s="14" t="n"/>
       <c r="AH200" s="14" t="inlineStr"/>
       <c r="AI200" s="14" t="inlineStr">
         <is>
@@ -29248,9 +29262,11 @@
       <c r="AD201" s="14" t="n">
         <v>0.920264352053598</v>
       </c>
-      <c r="AE201" s="14" t="inlineStr"/>
-      <c r="AF201" s="14" t="inlineStr"/>
-      <c r="AG201" s="14" t="inlineStr"/>
+      <c r="AE201" s="14" t="n">
+        <v>39359.1</v>
+      </c>
+      <c r="AF201" s="14" t="n"/>
+      <c r="AG201" s="14" t="n"/>
       <c r="AH201" s="14" t="inlineStr"/>
       <c r="AI201" s="14" t="inlineStr">
         <is>
@@ -29404,9 +29420,11 @@
       <c r="AD202" s="14" t="n">
         <v>0.8849337530411966</v>
       </c>
-      <c r="AE202" s="14" t="inlineStr"/>
-      <c r="AF202" s="14" t="inlineStr"/>
-      <c r="AG202" s="14" t="inlineStr"/>
+      <c r="AE202" s="14" t="n">
+        <v>31739.83</v>
+      </c>
+      <c r="AF202" s="14" t="n"/>
+      <c r="AG202" s="14" t="n"/>
       <c r="AH202" s="14" t="inlineStr"/>
       <c r="AI202" s="14" t="inlineStr">
         <is>
@@ -29560,9 +29578,11 @@
       <c r="AD203" s="14" t="n">
         <v>0.9552042842085368</v>
       </c>
-      <c r="AE203" s="14" t="inlineStr"/>
-      <c r="AF203" s="14" t="inlineStr"/>
-      <c r="AG203" s="14" t="inlineStr"/>
+      <c r="AE203" s="14" t="n">
+        <v>707702.4</v>
+      </c>
+      <c r="AF203" s="14" t="n"/>
+      <c r="AG203" s="14" t="n"/>
       <c r="AH203" s="14" t="inlineStr"/>
       <c r="AI203" s="14" t="inlineStr">
         <is>
@@ -29716,9 +29736,11 @@
       <c r="AD204" s="14" t="n">
         <v>0.9636193042356076</v>
       </c>
-      <c r="AE204" s="14" t="inlineStr"/>
-      <c r="AF204" s="14" t="inlineStr"/>
-      <c r="AG204" s="14" t="inlineStr"/>
+      <c r="AE204" s="14" t="n">
+        <v>205184.69</v>
+      </c>
+      <c r="AF204" s="14" t="n"/>
+      <c r="AG204" s="14" t="n"/>
       <c r="AH204" s="14" t="inlineStr"/>
       <c r="AI204" s="14" t="inlineStr">
         <is>
@@ -29876,9 +29898,13 @@
       <c r="AD205" s="14" t="n">
         <v>0.8727540911224712</v>
       </c>
-      <c r="AE205" s="14" t="inlineStr"/>
-      <c r="AF205" s="14" t="inlineStr"/>
-      <c r="AG205" s="14" t="inlineStr"/>
+      <c r="AE205" s="14" t="n">
+        <v>136096.67</v>
+      </c>
+      <c r="AF205" s="14" t="n"/>
+      <c r="AG205" s="14" t="n">
+        <v>0.030425</v>
+      </c>
       <c r="AH205" s="14" t="inlineStr"/>
       <c r="AI205" s="14" t="inlineStr">
         <is>
@@ -30036,9 +30062,13 @@
       <c r="AD206" s="14" t="n">
         <v>0.8911021333131565</v>
       </c>
-      <c r="AE206" s="14" t="inlineStr"/>
-      <c r="AF206" s="14" t="inlineStr"/>
-      <c r="AG206" s="14" t="inlineStr"/>
+      <c r="AE206" s="14" t="n">
+        <v>53541.13</v>
+      </c>
+      <c r="AF206" s="14" t="n"/>
+      <c r="AG206" s="14" t="n">
+        <v>0.012257</v>
+      </c>
       <c r="AH206" s="14" t="inlineStr"/>
       <c r="AI206" s="14" t="inlineStr">
         <is>
@@ -30196,9 +30226,13 @@
       <c r="AD207" s="14" t="n">
         <v>0.9460859440335908</v>
       </c>
-      <c r="AE207" s="14" t="inlineStr"/>
-      <c r="AF207" s="14" t="inlineStr"/>
-      <c r="AG207" s="14" t="inlineStr"/>
+      <c r="AE207" s="14" t="n">
+        <v>11110</v>
+      </c>
+      <c r="AF207" s="14" t="n"/>
+      <c r="AG207" s="14" t="n">
+        <v>0.002764</v>
+      </c>
       <c r="AH207" s="14" t="inlineStr"/>
       <c r="AI207" s="14" t="inlineStr">
         <is>
@@ -30356,9 +30390,13 @@
       <c r="AD208" s="14" t="n">
         <v>1.063482696234339</v>
       </c>
-      <c r="AE208" s="14" t="inlineStr"/>
-      <c r="AF208" s="14" t="inlineStr"/>
-      <c r="AG208" s="14" t="inlineStr"/>
+      <c r="AE208" s="14" t="n">
+        <v>19383.96</v>
+      </c>
+      <c r="AF208" s="14" t="n"/>
+      <c r="AG208" s="14" t="n">
+        <v>0.004696</v>
+      </c>
       <c r="AH208" s="14" t="inlineStr"/>
       <c r="AI208" s="14" t="inlineStr">
         <is>
@@ -30516,9 +30554,13 @@
       <c r="AD209" s="14" t="n">
         <v>0.9881075041911432</v>
       </c>
-      <c r="AE209" s="14" t="inlineStr"/>
-      <c r="AF209" s="14" t="inlineStr"/>
-      <c r="AG209" s="14" t="inlineStr"/>
+      <c r="AE209" s="14" t="n">
+        <v>57855.69</v>
+      </c>
+      <c r="AF209" s="14" t="n"/>
+      <c r="AG209" s="14" t="n">
+        <v>0.013705</v>
+      </c>
       <c r="AH209" s="14" t="inlineStr"/>
       <c r="AI209" s="14" t="inlineStr">
         <is>
@@ -30676,9 +30718,13 @@
       <c r="AD210" s="14" t="n">
         <v>0.921254476412496</v>
       </c>
-      <c r="AE210" s="14" t="inlineStr"/>
-      <c r="AF210" s="14" t="inlineStr"/>
-      <c r="AG210" s="14" t="inlineStr"/>
+      <c r="AE210" s="14" t="n">
+        <v>29601.74</v>
+      </c>
+      <c r="AF210" s="14" t="n"/>
+      <c r="AG210" s="14" t="n">
+        <v>0.006433</v>
+      </c>
       <c r="AH210" s="14" t="inlineStr"/>
       <c r="AI210" s="14" t="inlineStr">
         <is>
@@ -30836,9 +30882,13 @@
       <c r="AD211" s="14" t="n">
         <v>0.9358800562021976</v>
       </c>
-      <c r="AE211" s="14" t="inlineStr"/>
-      <c r="AF211" s="14" t="inlineStr"/>
-      <c r="AG211" s="14" t="inlineStr"/>
+      <c r="AE211" s="14" t="n">
+        <v>32022.5</v>
+      </c>
+      <c r="AF211" s="14" t="n"/>
+      <c r="AG211" s="14" t="n">
+        <v>0.007413</v>
+      </c>
       <c r="AH211" s="14" t="inlineStr"/>
       <c r="AI211" s="14" t="inlineStr">
         <is>
@@ -30998,9 +31048,13 @@
       <c r="AD212" s="14" t="n">
         <v>0.926058610223794</v>
       </c>
-      <c r="AE212" s="14" t="inlineStr"/>
-      <c r="AF212" s="14" t="inlineStr"/>
-      <c r="AG212" s="14" t="inlineStr"/>
+      <c r="AE212" s="14" t="n">
+        <v>95765.56</v>
+      </c>
+      <c r="AF212" s="14" t="n"/>
+      <c r="AG212" s="14" t="n">
+        <v>0.021194</v>
+      </c>
       <c r="AH212" s="14" t="inlineStr"/>
       <c r="AI212" s="14" t="inlineStr">
         <is>
@@ -31160,9 +31214,13 @@
       <c r="AD213" s="14" t="n">
         <v>0.9353820249988504</v>
       </c>
-      <c r="AE213" s="14" t="inlineStr"/>
-      <c r="AF213" s="14" t="inlineStr"/>
-      <c r="AG213" s="14" t="inlineStr"/>
+      <c r="AE213" s="14" t="n">
+        <v>53425.59</v>
+      </c>
+      <c r="AF213" s="14" t="n"/>
+      <c r="AG213" s="14" t="n">
+        <v>0.012577</v>
+      </c>
       <c r="AH213" s="14" t="inlineStr"/>
       <c r="AI213" s="14" t="inlineStr">
         <is>
@@ -31322,9 +31380,13 @@
       <c r="AD214" s="14" t="n">
         <v>1.009504528995584</v>
       </c>
-      <c r="AE214" s="14" t="inlineStr"/>
-      <c r="AF214" s="14" t="inlineStr"/>
-      <c r="AG214" s="14" t="inlineStr"/>
+      <c r="AE214" s="14" t="n">
+        <v>44008.16</v>
+      </c>
+      <c r="AF214" s="14" t="n"/>
+      <c r="AG214" s="14" t="n">
+        <v>0.010426</v>
+      </c>
       <c r="AH214" s="14" t="inlineStr"/>
       <c r="AI214" s="14" t="inlineStr">
         <is>
@@ -31486,9 +31548,13 @@
       <c r="AD215" s="14" t="n">
         <v>0.9791226188321752</v>
       </c>
-      <c r="AE215" s="14" t="inlineStr"/>
-      <c r="AF215" s="14" t="inlineStr"/>
-      <c r="AG215" s="14" t="inlineStr"/>
+      <c r="AE215" s="14" t="n">
+        <v>11469.32</v>
+      </c>
+      <c r="AF215" s="14" t="n"/>
+      <c r="AG215" s="14" t="n">
+        <v>0.002643</v>
+      </c>
       <c r="AH215" s="14" t="inlineStr"/>
       <c r="AI215" s="14" t="inlineStr">
         <is>
@@ -31650,9 +31716,13 @@
       <c r="AD216" s="14" t="n">
         <v>0.948862942852872</v>
       </c>
-      <c r="AE216" s="14" t="inlineStr"/>
-      <c r="AF216" s="14" t="inlineStr"/>
-      <c r="AG216" s="14" t="inlineStr"/>
+      <c r="AE216" s="14" t="n">
+        <v>30876.93</v>
+      </c>
+      <c r="AF216" s="14" t="n"/>
+      <c r="AG216" s="14" t="n">
+        <v>0.007105</v>
+      </c>
       <c r="AH216" s="14" t="inlineStr"/>
       <c r="AI216" s="14" t="inlineStr">
         <is>
@@ -31796,9 +31866,13 @@
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="14" t="inlineStr"/>
       <c r="AD217" s="14" t="inlineStr"/>
-      <c r="AE217" s="14" t="inlineStr"/>
-      <c r="AF217" s="14" t="inlineStr"/>
-      <c r="AG217" s="14" t="inlineStr"/>
+      <c r="AE217" s="14" t="n">
+        <v>100193.47</v>
+      </c>
+      <c r="AF217" s="14" t="n"/>
+      <c r="AG217" s="14" t="n">
+        <v>0.02307</v>
+      </c>
       <c r="AH217" s="14" t="inlineStr"/>
       <c r="AI217" s="14" t="inlineStr">
         <is>
@@ -31942,9 +32016,13 @@
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="14" t="inlineStr"/>
       <c r="AD218" s="14" t="inlineStr"/>
-      <c r="AE218" s="14" t="inlineStr"/>
-      <c r="AF218" s="14" t="inlineStr"/>
-      <c r="AG218" s="14" t="inlineStr"/>
+      <c r="AE218" s="14" t="n">
+        <v>21973.92</v>
+      </c>
+      <c r="AF218" s="14" t="n"/>
+      <c r="AG218" s="14" t="n">
+        <v>0.005261</v>
+      </c>
       <c r="AH218" s="14" t="inlineStr"/>
       <c r="AI218" s="14" t="inlineStr">
         <is>
@@ -32088,9 +32166,13 @@
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="14" t="inlineStr"/>
       <c r="AD219" s="14" t="inlineStr"/>
-      <c r="AE219" s="14" t="inlineStr"/>
-      <c r="AF219" s="14" t="inlineStr"/>
-      <c r="AG219" s="14" t="inlineStr"/>
+      <c r="AE219" s="14" t="n">
+        <v>8129.08</v>
+      </c>
+      <c r="AF219" s="14" t="n"/>
+      <c r="AG219" s="14" t="n">
+        <v>0.001839</v>
+      </c>
       <c r="AH219" s="14" t="inlineStr"/>
       <c r="AI219" s="14" t="inlineStr">
         <is>
@@ -32246,9 +32328,13 @@
       <c r="AD220" s="14" t="n">
         <v>0.8959</v>
       </c>
-      <c r="AE220" s="14" t="inlineStr"/>
-      <c r="AF220" s="14" t="inlineStr"/>
-      <c r="AG220" s="14" t="inlineStr"/>
+      <c r="AE220" s="14" t="n">
+        <v>22504.32</v>
+      </c>
+      <c r="AF220" s="14" t="n"/>
+      <c r="AG220" s="14" t="n">
+        <v>0.005219</v>
+      </c>
       <c r="AH220" s="14" t="inlineStr"/>
       <c r="AI220" s="14" t="inlineStr">
         <is>
@@ -32404,9 +32490,13 @@
       <c r="AD221" s="14" t="n">
         <v>0.9723000000000001</v>
       </c>
-      <c r="AE221" s="14" t="inlineStr"/>
-      <c r="AF221" s="14" t="inlineStr"/>
-      <c r="AG221" s="14" t="inlineStr"/>
+      <c r="AE221" s="14" t="n">
+        <v>58851.03</v>
+      </c>
+      <c r="AF221" s="14" t="n"/>
+      <c r="AG221" s="14" t="n">
+        <v>0.015257</v>
+      </c>
       <c r="AH221" s="14" t="inlineStr"/>
       <c r="AI221" s="14" t="inlineStr">
         <is>
@@ -32562,9 +32652,13 @@
       <c r="AD222" s="14" t="n">
         <v>0.8143</v>
       </c>
-      <c r="AE222" s="14" t="inlineStr"/>
-      <c r="AF222" s="14" t="inlineStr"/>
-      <c r="AG222" s="14" t="inlineStr"/>
+      <c r="AE222" s="14" t="n">
+        <v>13101.86</v>
+      </c>
+      <c r="AF222" s="14" t="n"/>
+      <c r="AG222" s="14" t="n">
+        <v>0.003338</v>
+      </c>
       <c r="AH222" s="14" t="inlineStr"/>
       <c r="AI222" s="14" t="inlineStr">
         <is>
@@ -32724,9 +32818,13 @@
       <c r="AD223" s="14" t="n">
         <v>1.059</v>
       </c>
-      <c r="AE223" s="14" t="inlineStr"/>
-      <c r="AF223" s="14" t="inlineStr"/>
-      <c r="AG223" s="14" t="inlineStr"/>
+      <c r="AE223" s="14" t="n">
+        <v>36979.92</v>
+      </c>
+      <c r="AF223" s="14" t="n"/>
+      <c r="AG223" s="14" t="n">
+        <v>0.009686</v>
+      </c>
       <c r="AH223" s="14" t="inlineStr"/>
       <c r="AI223" s="14" t="inlineStr">
         <is>
@@ -32886,9 +32984,13 @@
       <c r="AD224" s="14" t="n">
         <v>0.9112</v>
       </c>
-      <c r="AE224" s="14" t="inlineStr"/>
-      <c r="AF224" s="14" t="inlineStr"/>
-      <c r="AG224" s="14" t="inlineStr"/>
+      <c r="AE224" s="14" t="n">
+        <v>14252.88</v>
+      </c>
+      <c r="AF224" s="14" t="n"/>
+      <c r="AG224" s="14" t="n">
+        <v>0.003679</v>
+      </c>
       <c r="AH224" s="14" t="inlineStr"/>
       <c r="AI224" s="14" t="inlineStr">
         <is>
@@ -33050,9 +33152,13 @@
       <c r="AD225" s="14" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="AE225" s="14" t="inlineStr"/>
-      <c r="AF225" s="14" t="inlineStr"/>
-      <c r="AG225" s="14" t="inlineStr"/>
+      <c r="AE225" s="14" t="n">
+        <v>11130.76</v>
+      </c>
+      <c r="AF225" s="14" t="n"/>
+      <c r="AG225" s="14" t="n">
+        <v>0.002774</v>
+      </c>
       <c r="AH225" s="14" t="inlineStr"/>
       <c r="AI225" s="14" t="inlineStr">
         <is>
@@ -33214,9 +33320,13 @@
       <c r="AD226" s="14" t="n">
         <v>0.8895</v>
       </c>
-      <c r="AE226" s="14" t="inlineStr"/>
-      <c r="AF226" s="14" t="inlineStr"/>
-      <c r="AG226" s="14" t="inlineStr"/>
+      <c r="AE226" s="14" t="n">
+        <v>38621.3</v>
+      </c>
+      <c r="AF226" s="14" t="n"/>
+      <c r="AG226" s="14" t="n">
+        <v>0.009865000000000001</v>
+      </c>
       <c r="AH226" s="14" t="inlineStr"/>
       <c r="AI226" s="14" t="inlineStr">
         <is>
@@ -33378,9 +33488,13 @@
       <c r="AD227" s="14" t="n">
         <v>0.8398</v>
       </c>
-      <c r="AE227" s="14" t="inlineStr"/>
-      <c r="AF227" s="14" t="inlineStr"/>
-      <c r="AG227" s="14" t="inlineStr"/>
+      <c r="AE227" s="14" t="n">
+        <v>23900.05</v>
+      </c>
+      <c r="AF227" s="14" t="n"/>
+      <c r="AG227" s="14" t="n">
+        <v>0.006092</v>
+      </c>
       <c r="AH227" s="14" t="inlineStr"/>
       <c r="AI227" s="14" t="inlineStr">
         <is>
@@ -33542,9 +33656,13 @@
       <c r="AD228" s="14" t="n">
         <v>0.8413</v>
       </c>
-      <c r="AE228" s="14" t="inlineStr"/>
-      <c r="AF228" s="14" t="inlineStr"/>
-      <c r="AG228" s="14" t="inlineStr"/>
+      <c r="AE228" s="14" t="n">
+        <v>50956.47</v>
+      </c>
+      <c r="AF228" s="14" t="n"/>
+      <c r="AG228" s="14" t="n">
+        <v>0.012832</v>
+      </c>
       <c r="AH228" s="14" t="inlineStr"/>
       <c r="AI228" s="14" t="inlineStr">
         <is>
@@ -33706,9 +33824,13 @@
       <c r="AD229" s="14" t="n">
         <v>0.8472</v>
       </c>
-      <c r="AE229" s="14" t="inlineStr"/>
-      <c r="AF229" s="14" t="inlineStr"/>
-      <c r="AG229" s="14" t="inlineStr"/>
+      <c r="AE229" s="14" t="n">
+        <v>77532.52</v>
+      </c>
+      <c r="AF229" s="14" t="n"/>
+      <c r="AG229" s="14" t="n">
+        <v>0.020571</v>
+      </c>
       <c r="AH229" s="14" t="inlineStr"/>
       <c r="AI229" s="14" t="inlineStr">
         <is>
@@ -33870,9 +33992,13 @@
       <c r="AD230" s="14" t="n">
         <v>0.7574</v>
       </c>
-      <c r="AE230" s="14" t="inlineStr"/>
-      <c r="AF230" s="14" t="inlineStr"/>
-      <c r="AG230" s="14" t="inlineStr"/>
+      <c r="AE230" s="14" t="n">
+        <v>114272.26</v>
+      </c>
+      <c r="AF230" s="14" t="n"/>
+      <c r="AG230" s="14" t="n">
+        <v>0.026167</v>
+      </c>
       <c r="AH230" s="14" t="inlineStr"/>
       <c r="AI230" s="14" t="inlineStr">
         <is>
@@ -34034,9 +34160,13 @@
       <c r="AD231" s="14" t="n">
         <v>0.7357</v>
       </c>
-      <c r="AE231" s="14" t="inlineStr"/>
-      <c r="AF231" s="14" t="inlineStr"/>
-      <c r="AG231" s="14" t="inlineStr"/>
+      <c r="AE231" s="14" t="n">
+        <v>259988.49</v>
+      </c>
+      <c r="AF231" s="14" t="n"/>
+      <c r="AG231" s="14" t="n">
+        <v>0.065498</v>
+      </c>
       <c r="AH231" s="14" t="inlineStr"/>
       <c r="AI231" s="14" t="inlineStr">
         <is>
@@ -34180,9 +34310,13 @@
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="14" t="inlineStr"/>
       <c r="AD232" s="14" t="inlineStr"/>
-      <c r="AE232" s="14" t="inlineStr"/>
-      <c r="AF232" s="14" t="inlineStr"/>
-      <c r="AG232" s="14" t="inlineStr"/>
+      <c r="AE232" s="14" t="n">
+        <v>427662.49</v>
+      </c>
+      <c r="AF232" s="14" t="n"/>
+      <c r="AG232" s="14" t="n">
+        <v>0.08670799999999999</v>
+      </c>
       <c r="AH232" s="14" t="inlineStr"/>
       <c r="AI232" s="14" t="inlineStr">
         <is>
@@ -34326,9 +34460,13 @@
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="14" t="inlineStr"/>
       <c r="AD233" s="14" t="inlineStr"/>
-      <c r="AE233" s="14" t="inlineStr"/>
-      <c r="AF233" s="14" t="inlineStr"/>
-      <c r="AG233" s="14" t="inlineStr"/>
+      <c r="AE233" s="14" t="n">
+        <v>1053263.05</v>
+      </c>
+      <c r="AF233" s="14" t="n"/>
+      <c r="AG233" s="14" t="n">
+        <v>0.202932</v>
+      </c>
       <c r="AH233" s="14" t="inlineStr"/>
       <c r="AI233" s="14" t="inlineStr">
         <is>

--- a/docs/case_files/CASE_GUA.xlsx
+++ b/docs/case_files/CASE_GUA.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GUAUSDT</t>
+          <t>GUA</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>fullyDelisted=False, offsell=False, offline=False</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>0xa5c8e1513b6a08334b479fe4d71f1253259469be</t>
+          <t>UNKNOWN — CAN OPERATOR</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>1000000000</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN — CAN OPERATOR</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN — CAN OPERATOR</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Co luc gom khong (khuon build-perp GOM-A/B/C)? HAY thuoc loai captive staged-pump (khuon ON/BTW) — neu vay dang stage nao? Cum vi co dau vet trung ON/BTW/AGT khong?</t>
+          <t>Cau hoi case: TBD — operator dien</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX233"/>
+  <dimension ref="A1:AX240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23493,25 +23493,15 @@
       <c r="U164" s="14" t="n">
         <v>0.93</v>
       </c>
-      <c r="V164" s="14" t="n">
-        <v>1.8807</v>
-      </c>
+      <c r="V164" s="14" t="inlineStr"/>
       <c r="W164" s="14" t="inlineStr"/>
       <c r="X164" s="14" t="inlineStr"/>
       <c r="Y164" s="14" t="inlineStr"/>
       <c r="Z164" s="14" t="inlineStr"/>
-      <c r="AA164" s="14" t="n">
-        <v>1.1999</v>
-      </c>
-      <c r="AB164" s="14" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="AC164" s="14" t="n">
-        <v>0.6493</v>
-      </c>
-      <c r="AD164" s="14" t="n">
-        <v>1.006278358097293</v>
-      </c>
+      <c r="AA164" s="14" t="inlineStr"/>
+      <c r="AB164" s="14" t="inlineStr"/>
+      <c r="AC164" s="14" t="inlineStr"/>
+      <c r="AD164" s="14" t="inlineStr"/>
       <c r="AE164" s="14" t="inlineStr"/>
       <c r="AF164" s="14" t="inlineStr"/>
       <c r="AG164" s="14" t="inlineStr"/>
@@ -23549,7 +23539,7 @@
       </c>
       <c r="AP164" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ164" s="14" t="inlineStr"/>
@@ -23645,25 +23635,15 @@
       <c r="U165" s="14" t="n">
         <v>0.48</v>
       </c>
-      <c r="V165" s="14" t="n">
-        <v>1.5685</v>
-      </c>
+      <c r="V165" s="14" t="inlineStr"/>
       <c r="W165" s="14" t="inlineStr"/>
       <c r="X165" s="14" t="inlineStr"/>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="inlineStr"/>
-      <c r="AA165" s="14" t="n">
-        <v>1.3334</v>
-      </c>
-      <c r="AB165" s="14" t="n">
-        <v>0.8501</v>
-      </c>
-      <c r="AC165" s="14" t="n">
-        <v>0.8192</v>
-      </c>
-      <c r="AD165" s="14" t="n">
-        <v>0.997638110110619</v>
-      </c>
+      <c r="AA165" s="14" t="inlineStr"/>
+      <c r="AB165" s="14" t="inlineStr"/>
+      <c r="AC165" s="14" t="inlineStr"/>
+      <c r="AD165" s="14" t="inlineStr"/>
       <c r="AE165" s="14" t="inlineStr"/>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -23701,7 +23681,7 @@
       </c>
       <c r="AP165" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ165" s="14" t="inlineStr"/>
@@ -23793,27 +23773,15 @@
       <c r="U166" s="14" t="n">
         <v>0.93</v>
       </c>
-      <c r="V166" s="14" t="n">
-        <v>1.8358</v>
-      </c>
-      <c r="W166" s="14" t="n">
-        <v>1.746</v>
-      </c>
+      <c r="V166" s="14" t="inlineStr"/>
+      <c r="W166" s="14" t="inlineStr"/>
       <c r="X166" s="14" t="inlineStr"/>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="inlineStr"/>
-      <c r="AA166" s="14" t="n">
-        <v>1.3267</v>
-      </c>
-      <c r="AB166" s="14" t="n">
-        <v>0.7227</v>
-      </c>
-      <c r="AC166" s="14" t="n">
-        <v>0.7117</v>
-      </c>
-      <c r="AD166" s="14" t="n">
-        <v>1.098962700400428</v>
-      </c>
+      <c r="AA166" s="14" t="inlineStr"/>
+      <c r="AB166" s="14" t="inlineStr"/>
+      <c r="AC166" s="14" t="inlineStr"/>
+      <c r="AD166" s="14" t="inlineStr"/>
       <c r="AE166" s="14" t="inlineStr"/>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -23851,7 +23819,7 @@
       </c>
       <c r="AP166" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ166" s="14" t="inlineStr"/>
@@ -23943,31 +23911,15 @@
       <c r="U167" s="14" t="n">
         <v>1.15</v>
       </c>
-      <c r="V167" s="14" t="n">
-        <v>1.9164</v>
-      </c>
-      <c r="W167" s="14" t="n">
-        <v>1.7601</v>
-      </c>
+      <c r="V167" s="14" t="inlineStr"/>
+      <c r="W167" s="14" t="inlineStr"/>
       <c r="X167" s="14" t="inlineStr"/>
-      <c r="Y167" s="14" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="Z167" s="14" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="AA167" s="14" t="n">
-        <v>1.3258</v>
-      </c>
-      <c r="AB167" s="14" t="n">
-        <v>0.6918</v>
-      </c>
-      <c r="AC167" s="14" t="n">
-        <v>0.7879</v>
-      </c>
-      <c r="AD167" s="14" t="n">
-        <v>1.023677201851654</v>
-      </c>
+      <c r="Y167" s="14" t="inlineStr"/>
+      <c r="Z167" s="14" t="inlineStr"/>
+      <c r="AA167" s="14" t="inlineStr"/>
+      <c r="AB167" s="14" t="inlineStr"/>
+      <c r="AC167" s="14" t="inlineStr"/>
+      <c r="AD167" s="14" t="inlineStr"/>
       <c r="AE167" s="14" t="inlineStr"/>
       <c r="AF167" s="14" t="inlineStr"/>
       <c r="AG167" s="14" t="inlineStr"/>
@@ -24005,7 +23957,7 @@
       </c>
       <c r="AP167" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ167" s="14" t="inlineStr"/>
@@ -24035,9 +23987,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX167" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX167" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -24101,31 +24053,15 @@
       <c r="U168" s="14" t="n">
         <v>0.57</v>
       </c>
-      <c r="V168" s="14" t="n">
-        <v>1.3371</v>
-      </c>
-      <c r="W168" s="14" t="n">
-        <v>1.6389</v>
-      </c>
+      <c r="V168" s="14" t="inlineStr"/>
+      <c r="W168" s="14" t="inlineStr"/>
       <c r="X168" s="14" t="inlineStr"/>
-      <c r="Y168" s="14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Z168" s="14" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="AA168" s="14" t="n">
-        <v>1.4814</v>
-      </c>
-      <c r="AB168" s="14" t="n">
-        <v>1.1079</v>
-      </c>
-      <c r="AC168" s="14" t="n">
-        <v>1.2302</v>
-      </c>
-      <c r="AD168" s="14" t="n">
-        <v>0.9560444903441954</v>
-      </c>
+      <c r="Y168" s="14" t="inlineStr"/>
+      <c r="Z168" s="14" t="inlineStr"/>
+      <c r="AA168" s="14" t="inlineStr"/>
+      <c r="AB168" s="14" t="inlineStr"/>
+      <c r="AC168" s="14" t="inlineStr"/>
+      <c r="AD168" s="14" t="inlineStr"/>
       <c r="AE168" s="14" t="inlineStr"/>
       <c r="AF168" s="14" t="inlineStr"/>
       <c r="AG168" s="14" t="inlineStr"/>
@@ -24163,7 +24099,7 @@
       </c>
       <c r="AP168" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ168" s="14" t="inlineStr"/>
@@ -24255,33 +24191,15 @@
       <c r="U169" s="14" t="n">
         <v>0.43</v>
       </c>
-      <c r="V169" s="14" t="n">
-        <v>1.1049</v>
-      </c>
-      <c r="W169" s="14" t="n">
-        <v>1.3841</v>
-      </c>
-      <c r="X169" s="14" t="n">
-        <v>2.0159</v>
-      </c>
-      <c r="Y169" s="14" t="n">
-        <v>-5.63</v>
-      </c>
-      <c r="Z169" s="14" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="AA169" s="14" t="n">
-        <v>1.252</v>
-      </c>
-      <c r="AB169" s="14" t="n">
-        <v>1.1331</v>
-      </c>
-      <c r="AC169" s="14" t="n">
-        <v>1.3089</v>
-      </c>
-      <c r="AD169" s="14" t="n">
-        <v>0.9249504515184508</v>
-      </c>
+      <c r="V169" s="14" t="inlineStr"/>
+      <c r="W169" s="14" t="inlineStr"/>
+      <c r="X169" s="14" t="inlineStr"/>
+      <c r="Y169" s="14" t="inlineStr"/>
+      <c r="Z169" s="14" t="inlineStr"/>
+      <c r="AA169" s="14" t="inlineStr"/>
+      <c r="AB169" s="14" t="inlineStr"/>
+      <c r="AC169" s="14" t="inlineStr"/>
+      <c r="AD169" s="14" t="inlineStr"/>
       <c r="AE169" s="14" t="inlineStr"/>
       <c r="AF169" s="14" t="inlineStr"/>
       <c r="AG169" s="14" t="inlineStr"/>
@@ -24319,7 +24237,7 @@
       </c>
       <c r="AP169" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ169" s="14" t="inlineStr"/>
@@ -24345,9 +24263,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX169" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX169" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -24411,33 +24329,15 @@
       <c r="U170" s="14" t="n">
         <v>0.39</v>
       </c>
-      <c r="V170" s="14" t="n">
-        <v>0.9757</v>
-      </c>
-      <c r="W170" s="14" t="n">
-        <v>1.1338</v>
-      </c>
-      <c r="X170" s="14" t="n">
-        <v>1.6741</v>
-      </c>
-      <c r="Y170" s="14" t="n">
-        <v>-10.45</v>
-      </c>
-      <c r="Z170" s="14" t="n">
-        <v>75.89</v>
-      </c>
-      <c r="AA170" s="14" t="n">
-        <v>1.1872</v>
-      </c>
-      <c r="AB170" s="14" t="n">
-        <v>1.2168</v>
-      </c>
-      <c r="AC170" s="14" t="n">
-        <v>1.3714</v>
-      </c>
-      <c r="AD170" s="14" t="n">
-        <v>0.8785524503762218</v>
-      </c>
+      <c r="V170" s="14" t="inlineStr"/>
+      <c r="W170" s="14" t="inlineStr"/>
+      <c r="X170" s="14" t="inlineStr"/>
+      <c r="Y170" s="14" t="inlineStr"/>
+      <c r="Z170" s="14" t="inlineStr"/>
+      <c r="AA170" s="14" t="inlineStr"/>
+      <c r="AB170" s="14" t="inlineStr"/>
+      <c r="AC170" s="14" t="inlineStr"/>
+      <c r="AD170" s="14" t="inlineStr"/>
       <c r="AE170" s="14" t="inlineStr"/>
       <c r="AF170" s="14" t="inlineStr"/>
       <c r="AG170" s="14" t="inlineStr"/>
@@ -24475,7 +24375,7 @@
       </c>
       <c r="AP170" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ170" s="14" t="inlineStr"/>
@@ -24567,33 +24467,15 @@
       <c r="U171" s="14" t="n">
         <v>0.31</v>
       </c>
-      <c r="V171" s="14" t="n">
-        <v>1.1249</v>
-      </c>
-      <c r="W171" s="14" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="X171" s="14" t="n">
-        <v>1.6548</v>
-      </c>
-      <c r="Y171" s="14" t="n">
-        <v>-19.56</v>
-      </c>
-      <c r="Z171" s="14" t="n">
-        <v>-4.39</v>
-      </c>
-      <c r="AA171" s="14" t="n">
-        <v>1.1916</v>
-      </c>
-      <c r="AB171" s="14" t="n">
-        <v>1.0593</v>
-      </c>
-      <c r="AC171" s="14" t="n">
-        <v>1.1777</v>
-      </c>
-      <c r="AD171" s="14" t="n">
-        <v>1.030208612312772</v>
-      </c>
+      <c r="V171" s="14" t="inlineStr"/>
+      <c r="W171" s="14" t="inlineStr"/>
+      <c r="X171" s="14" t="inlineStr"/>
+      <c r="Y171" s="14" t="inlineStr"/>
+      <c r="Z171" s="14" t="inlineStr"/>
+      <c r="AA171" s="14" t="inlineStr"/>
+      <c r="AB171" s="14" t="inlineStr"/>
+      <c r="AC171" s="14" t="inlineStr"/>
+      <c r="AD171" s="14" t="inlineStr"/>
       <c r="AE171" s="14" t="inlineStr"/>
       <c r="AF171" s="14" t="inlineStr"/>
       <c r="AG171" s="14" t="inlineStr"/>
@@ -24631,7 +24513,7 @@
       </c>
       <c r="AP171" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ171" s="14" t="inlineStr"/>
@@ -24727,33 +24609,15 @@
       <c r="U172" s="14" t="n">
         <v>0.74</v>
       </c>
-      <c r="V172" s="14" t="n">
-        <v>1.0733</v>
-      </c>
-      <c r="W172" s="14" t="n">
-        <v>1.0538</v>
-      </c>
-      <c r="X172" s="14" t="n">
-        <v>1.3434</v>
-      </c>
-      <c r="Y172" s="14" t="n">
-        <v>-12.64</v>
-      </c>
-      <c r="Z172" s="14" t="n">
-        <v>-10.07</v>
-      </c>
-      <c r="AA172" s="14" t="n">
-        <v>1.0937</v>
-      </c>
-      <c r="AB172" s="14" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="AC172" s="14" t="n">
-        <v>1.0585</v>
-      </c>
-      <c r="AD172" s="14" t="n">
-        <v>0.9436565682097204</v>
-      </c>
+      <c r="V172" s="14" t="inlineStr"/>
+      <c r="W172" s="14" t="inlineStr"/>
+      <c r="X172" s="14" t="inlineStr"/>
+      <c r="Y172" s="14" t="inlineStr"/>
+      <c r="Z172" s="14" t="inlineStr"/>
+      <c r="AA172" s="14" t="inlineStr"/>
+      <c r="AB172" s="14" t="inlineStr"/>
+      <c r="AC172" s="14" t="inlineStr"/>
+      <c r="AD172" s="14" t="inlineStr"/>
       <c r="AE172" s="14" t="inlineStr"/>
       <c r="AF172" s="14" t="inlineStr"/>
       <c r="AG172" s="14" t="inlineStr"/>
@@ -24791,7 +24655,7 @@
       </c>
       <c r="AP172" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ172" s="14" t="inlineStr"/>
@@ -24883,33 +24747,15 @@
       <c r="U173" s="14" t="n">
         <v>1.37</v>
       </c>
-      <c r="V173" s="14" t="n">
-        <v>0.7517</v>
-      </c>
-      <c r="W173" s="14" t="n">
-        <v>0.9721</v>
-      </c>
-      <c r="X173" s="14" t="n">
-        <v>1.0184</v>
-      </c>
-      <c r="Y173" s="14" t="n">
-        <v>-23.88</v>
-      </c>
-      <c r="Z173" s="14" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AA173" s="14" t="n">
-        <v>0.9036999999999999</v>
-      </c>
-      <c r="AB173" s="14" t="n">
-        <v>1.2022</v>
-      </c>
-      <c r="AC173" s="14" t="n">
-        <v>1.2528</v>
-      </c>
-      <c r="AD173" s="14" t="n">
-        <v>0.9488633662249772</v>
-      </c>
+      <c r="V173" s="14" t="inlineStr"/>
+      <c r="W173" s="14" t="inlineStr"/>
+      <c r="X173" s="14" t="inlineStr"/>
+      <c r="Y173" s="14" t="inlineStr"/>
+      <c r="Z173" s="14" t="inlineStr"/>
+      <c r="AA173" s="14" t="inlineStr"/>
+      <c r="AB173" s="14" t="inlineStr"/>
+      <c r="AC173" s="14" t="inlineStr"/>
+      <c r="AD173" s="14" t="inlineStr"/>
       <c r="AE173" s="14" t="inlineStr"/>
       <c r="AF173" s="14" t="inlineStr"/>
       <c r="AG173" s="14" t="inlineStr"/>
@@ -24947,7 +24793,7 @@
       </c>
       <c r="AP173" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ173" s="14" t="inlineStr"/>
@@ -24973,9 +24819,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX173" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX173" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -25039,33 +24885,15 @@
       <c r="U174" s="14" t="n">
         <v>0.29</v>
       </c>
-      <c r="V174" s="14" t="n">
-        <v>0.9292</v>
-      </c>
-      <c r="W174" s="14" t="n">
-        <v>0.9085</v>
-      </c>
-      <c r="X174" s="14" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="Y174" s="14" t="n">
-        <v>-22.49</v>
-      </c>
-      <c r="Z174" s="14" t="n">
-        <v>-6.16</v>
-      </c>
-      <c r="AA174" s="14" t="n">
-        <v>0.9236</v>
-      </c>
-      <c r="AB174" s="14" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="AC174" s="14" t="n">
-        <v>0.9673</v>
-      </c>
-      <c r="AD174" s="14" t="n">
-        <v>0.8838981727733921</v>
-      </c>
+      <c r="V174" s="14" t="inlineStr"/>
+      <c r="W174" s="14" t="inlineStr"/>
+      <c r="X174" s="14" t="inlineStr"/>
+      <c r="Y174" s="14" t="inlineStr"/>
+      <c r="Z174" s="14" t="inlineStr"/>
+      <c r="AA174" s="14" t="inlineStr"/>
+      <c r="AB174" s="14" t="inlineStr"/>
+      <c r="AC174" s="14" t="inlineStr"/>
+      <c r="AD174" s="14" t="inlineStr"/>
       <c r="AE174" s="14" t="inlineStr"/>
       <c r="AF174" s="14" t="inlineStr"/>
       <c r="AG174" s="14" t="inlineStr"/>
@@ -25103,7 +24931,7 @@
       </c>
       <c r="AP174" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ174" s="14" t="inlineStr"/>
@@ -25195,33 +25023,15 @@
       <c r="U175" s="14" t="n">
         <v>0.19</v>
       </c>
-      <c r="V175" s="14" t="n">
-        <v>0.8399</v>
-      </c>
-      <c r="W175" s="14" t="n">
-        <v>0.8345</v>
-      </c>
-      <c r="X175" s="14" t="n">
-        <v>0.7292</v>
-      </c>
-      <c r="Y175" s="14" t="n">
-        <v>-20.01</v>
-      </c>
-      <c r="Z175" s="14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AA175" s="14" t="n">
-        <v>0.8748</v>
-      </c>
-      <c r="AB175" s="14" t="n">
-        <v>1.0416</v>
-      </c>
-      <c r="AC175" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD175" s="14" t="n">
-        <v>0.9071292254483037</v>
-      </c>
+      <c r="V175" s="14" t="inlineStr"/>
+      <c r="W175" s="14" t="inlineStr"/>
+      <c r="X175" s="14" t="inlineStr"/>
+      <c r="Y175" s="14" t="inlineStr"/>
+      <c r="Z175" s="14" t="inlineStr"/>
+      <c r="AA175" s="14" t="inlineStr"/>
+      <c r="AB175" s="14" t="inlineStr"/>
+      <c r="AC175" s="14" t="inlineStr"/>
+      <c r="AD175" s="14" t="inlineStr"/>
       <c r="AE175" s="14" t="inlineStr"/>
       <c r="AF175" s="14" t="inlineStr"/>
       <c r="AG175" s="14" t="inlineStr"/>
@@ -25259,7 +25069,7 @@
       </c>
       <c r="AP175" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ175" s="14" t="inlineStr"/>
@@ -25351,33 +25161,15 @@
       <c r="U176" s="14" t="n">
         <v>0.18</v>
       </c>
-      <c r="V176" s="14" t="n">
-        <v>0.8011</v>
-      </c>
-      <c r="W176" s="14" t="n">
-        <v>0.8549</v>
-      </c>
-      <c r="X176" s="14" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="Y176" s="14" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="Z176" s="14" t="n">
-        <v>-10.14</v>
-      </c>
-      <c r="AA176" s="14" t="n">
-        <v>0.8653999999999999</v>
-      </c>
-      <c r="AB176" s="14" t="n">
-        <v>1.0803</v>
-      </c>
-      <c r="AC176" s="14" t="n">
-        <v>1.0929</v>
-      </c>
-      <c r="AD176" s="14" t="n">
-        <v>0.917277126539524</v>
-      </c>
+      <c r="V176" s="14" t="inlineStr"/>
+      <c r="W176" s="14" t="inlineStr"/>
+      <c r="X176" s="14" t="inlineStr"/>
+      <c r="Y176" s="14" t="inlineStr"/>
+      <c r="Z176" s="14" t="inlineStr"/>
+      <c r="AA176" s="14" t="inlineStr"/>
+      <c r="AB176" s="14" t="inlineStr"/>
+      <c r="AC176" s="14" t="inlineStr"/>
+      <c r="AD176" s="14" t="inlineStr"/>
       <c r="AE176" s="14" t="inlineStr"/>
       <c r="AF176" s="14" t="inlineStr"/>
       <c r="AG176" s="14" t="inlineStr"/>
@@ -25415,7 +25207,7 @@
       </c>
       <c r="AP176" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ176" s="14" t="inlineStr"/>
@@ -25507,33 +25299,15 @@
       <c r="U177" s="14" t="n">
         <v>0.18</v>
       </c>
-      <c r="V177" s="14" t="n">
-        <v>0.7668</v>
-      </c>
-      <c r="W177" s="14" t="n">
-        <v>0.8016</v>
-      </c>
-      <c r="X177" s="14" t="n">
-        <v>1.0396</v>
-      </c>
-      <c r="Y177" s="14" t="n">
-        <v>-6.34</v>
-      </c>
-      <c r="Z177" s="14" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="AA177" s="14" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="AB177" s="14" t="n">
-        <v>1.1281</v>
-      </c>
-      <c r="AC177" s="14" t="n">
-        <v>1.1004</v>
-      </c>
-      <c r="AD177" s="14" t="n">
-        <v>1.022122261897228</v>
-      </c>
+      <c r="V177" s="14" t="inlineStr"/>
+      <c r="W177" s="14" t="inlineStr"/>
+      <c r="X177" s="14" t="inlineStr"/>
+      <c r="Y177" s="14" t="inlineStr"/>
+      <c r="Z177" s="14" t="inlineStr"/>
+      <c r="AA177" s="14" t="inlineStr"/>
+      <c r="AB177" s="14" t="inlineStr"/>
+      <c r="AC177" s="14" t="inlineStr"/>
+      <c r="AD177" s="14" t="inlineStr"/>
       <c r="AE177" s="14" t="inlineStr"/>
       <c r="AF177" s="14" t="inlineStr"/>
       <c r="AG177" s="14" t="inlineStr"/>
@@ -25571,7 +25345,7 @@
       </c>
       <c r="AP177" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ177" s="14" t="inlineStr"/>
@@ -25663,33 +25437,15 @@
       <c r="U178" s="14" t="n">
         <v>0.43</v>
       </c>
-      <c r="V178" s="14" t="n">
-        <v>0.7682</v>
-      </c>
-      <c r="W178" s="14" t="n">
-        <v>0.7784</v>
-      </c>
-      <c r="X178" s="14" t="n">
-        <v>0.8801</v>
-      </c>
-      <c r="Y178" s="14" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="Z178" s="14" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="AA178" s="14" t="n">
-        <v>0.8659</v>
-      </c>
-      <c r="AB178" s="14" t="n">
-        <v>1.1272</v>
-      </c>
-      <c r="AC178" s="14" t="n">
-        <v>1.1026</v>
-      </c>
-      <c r="AD178" s="14" t="n">
-        <v>0.8848712415584942</v>
-      </c>
+      <c r="V178" s="14" t="inlineStr"/>
+      <c r="W178" s="14" t="inlineStr"/>
+      <c r="X178" s="14" t="inlineStr"/>
+      <c r="Y178" s="14" t="inlineStr"/>
+      <c r="Z178" s="14" t="inlineStr"/>
+      <c r="AA178" s="14" t="inlineStr"/>
+      <c r="AB178" s="14" t="inlineStr"/>
+      <c r="AC178" s="14" t="inlineStr"/>
+      <c r="AD178" s="14" t="inlineStr"/>
       <c r="AE178" s="14" t="inlineStr"/>
       <c r="AF178" s="14" t="inlineStr"/>
       <c r="AG178" s="14" t="inlineStr"/>
@@ -25727,7 +25483,7 @@
       </c>
       <c r="AP178" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ178" s="14" t="inlineStr"/>
@@ -25819,33 +25575,15 @@
       <c r="U179" s="14" t="n">
         <v>0.93</v>
       </c>
-      <c r="V179" s="14" t="n">
-        <v>0.7314000000000001</v>
-      </c>
-      <c r="W179" s="14" t="n">
-        <v>0.7554</v>
-      </c>
-      <c r="X179" s="14" t="n">
-        <v>1.1752</v>
-      </c>
-      <c r="Y179" s="14" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="Z179" s="14" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="AA179" s="14" t="n">
-        <v>0.8358</v>
-      </c>
-      <c r="AB179" s="14" t="n">
-        <v>1.1427</v>
-      </c>
-      <c r="AC179" s="14" t="n">
-        <v>1.1368</v>
-      </c>
-      <c r="AD179" s="14" t="n">
-        <v>1.033474842742971</v>
-      </c>
+      <c r="V179" s="14" t="inlineStr"/>
+      <c r="W179" s="14" t="inlineStr"/>
+      <c r="X179" s="14" t="inlineStr"/>
+      <c r="Y179" s="14" t="inlineStr"/>
+      <c r="Z179" s="14" t="inlineStr"/>
+      <c r="AA179" s="14" t="inlineStr"/>
+      <c r="AB179" s="14" t="inlineStr"/>
+      <c r="AC179" s="14" t="inlineStr"/>
+      <c r="AD179" s="14" t="inlineStr"/>
       <c r="AE179" s="14" t="inlineStr"/>
       <c r="AF179" s="14" t="inlineStr"/>
       <c r="AG179" s="14" t="inlineStr"/>
@@ -25883,7 +25621,7 @@
       </c>
       <c r="AP179" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ179" s="14" t="inlineStr"/>
@@ -25975,33 +25713,15 @@
       <c r="U180" s="14" t="n">
         <v>1.14</v>
       </c>
-      <c r="V180" s="14" t="n">
-        <v>0.6414</v>
-      </c>
-      <c r="W180" s="14" t="n">
-        <v>0.7112000000000001</v>
-      </c>
-      <c r="X180" s="14" t="n">
-        <v>1.4044</v>
-      </c>
-      <c r="Y180" s="14" t="n">
-        <v>-7.06</v>
-      </c>
-      <c r="Z180" s="14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AA180" s="14" t="n">
-        <v>0.8038999999999999</v>
-      </c>
-      <c r="AB180" s="14" t="n">
-        <v>1.2533</v>
-      </c>
-      <c r="AC180" s="14" t="n">
-        <v>1.4044</v>
-      </c>
-      <c r="AD180" s="14" t="n">
-        <v>1.13672287903969</v>
-      </c>
+      <c r="V180" s="14" t="inlineStr"/>
+      <c r="W180" s="14" t="inlineStr"/>
+      <c r="X180" s="14" t="inlineStr"/>
+      <c r="Y180" s="14" t="inlineStr"/>
+      <c r="Z180" s="14" t="inlineStr"/>
+      <c r="AA180" s="14" t="inlineStr"/>
+      <c r="AB180" s="14" t="inlineStr"/>
+      <c r="AC180" s="14" t="inlineStr"/>
+      <c r="AD180" s="14" t="inlineStr"/>
       <c r="AE180" s="14" t="inlineStr"/>
       <c r="AF180" s="14" t="inlineStr"/>
       <c r="AG180" s="14" t="inlineStr"/>
@@ -26039,7 +25759,7 @@
       </c>
       <c r="AP180" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ180" s="14" t="inlineStr"/>
@@ -26131,33 +25851,15 @@
       <c r="U181" s="14" t="n">
         <v>2.11</v>
       </c>
-      <c r="V181" s="14" t="n">
-        <v>0.6593</v>
-      </c>
-      <c r="W181" s="14" t="n">
-        <v>0.6756</v>
-      </c>
-      <c r="X181" s="14" t="n">
-        <v>1.4414</v>
-      </c>
-      <c r="Y181" s="14" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="Z181" s="14" t="n">
-        <v>14.53</v>
-      </c>
-      <c r="AA181" s="14" t="n">
-        <v>0.8511</v>
-      </c>
-      <c r="AB181" s="14" t="n">
-        <v>1.291</v>
-      </c>
-      <c r="AC181" s="14" t="n">
-        <v>1.5753</v>
-      </c>
-      <c r="AD181" s="14" t="n">
-        <v>1.049031468825295</v>
-      </c>
+      <c r="V181" s="14" t="inlineStr"/>
+      <c r="W181" s="14" t="inlineStr"/>
+      <c r="X181" s="14" t="inlineStr"/>
+      <c r="Y181" s="14" t="inlineStr"/>
+      <c r="Z181" s="14" t="inlineStr"/>
+      <c r="AA181" s="14" t="inlineStr"/>
+      <c r="AB181" s="14" t="inlineStr"/>
+      <c r="AC181" s="14" t="inlineStr"/>
+      <c r="AD181" s="14" t="inlineStr"/>
       <c r="AE181" s="14" t="inlineStr"/>
       <c r="AF181" s="14" t="inlineStr"/>
       <c r="AG181" s="14" t="inlineStr"/>
@@ -26195,7 +25897,7 @@
       </c>
       <c r="AP181" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ181" s="14" t="inlineStr"/>
@@ -26287,33 +25989,15 @@
       <c r="U182" s="14" t="n">
         <v>1.98</v>
       </c>
-      <c r="V182" s="14" t="n">
-        <v>0.9276</v>
-      </c>
-      <c r="W182" s="14" t="n">
-        <v>0.7215</v>
-      </c>
-      <c r="X182" s="14" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="Y182" s="14" t="n">
-        <v>-2.64</v>
-      </c>
-      <c r="Z182" s="14" t="n">
-        <v>-23.23</v>
-      </c>
-      <c r="AA182" s="14" t="n">
-        <v>0.8137</v>
-      </c>
-      <c r="AB182" s="14" t="n">
-        <v>0.8772</v>
-      </c>
-      <c r="AC182" s="14" t="n">
-        <v>1.0825</v>
-      </c>
-      <c r="AD182" s="14" t="n">
-        <v>0.9588693883500672</v>
-      </c>
+      <c r="V182" s="14" t="inlineStr"/>
+      <c r="W182" s="14" t="inlineStr"/>
+      <c r="X182" s="14" t="inlineStr"/>
+      <c r="Y182" s="14" t="inlineStr"/>
+      <c r="Z182" s="14" t="inlineStr"/>
+      <c r="AA182" s="14" t="inlineStr"/>
+      <c r="AB182" s="14" t="inlineStr"/>
+      <c r="AC182" s="14" t="inlineStr"/>
+      <c r="AD182" s="14" t="inlineStr"/>
       <c r="AE182" s="14" t="inlineStr"/>
       <c r="AF182" s="14" t="inlineStr"/>
       <c r="AG182" s="14" t="inlineStr"/>
@@ -26351,7 +26035,7 @@
       </c>
       <c r="AP182" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ182" s="14" t="inlineStr"/>
@@ -26443,33 +26127,15 @@
       <c r="U183" s="14" t="n">
         <v>3.8</v>
       </c>
-      <c r="V183" s="14" t="n">
-        <v>0.6637999999999999</v>
-      </c>
-      <c r="W183" s="14" t="n">
-        <v>0.7304</v>
-      </c>
-      <c r="X183" s="14" t="n">
-        <v>1.4451</v>
-      </c>
-      <c r="Y183" s="14" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Z183" s="14" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="AA183" s="14" t="n">
-        <v>0.8084</v>
-      </c>
-      <c r="AB183" s="14" t="n">
-        <v>1.2178</v>
-      </c>
-      <c r="AC183" s="14" t="n">
-        <v>1.5934</v>
-      </c>
-      <c r="AD183" s="14" t="n">
-        <v>0.97539272465367</v>
-      </c>
+      <c r="V183" s="14" t="inlineStr"/>
+      <c r="W183" s="14" t="inlineStr"/>
+      <c r="X183" s="14" t="inlineStr"/>
+      <c r="Y183" s="14" t="inlineStr"/>
+      <c r="Z183" s="14" t="inlineStr"/>
+      <c r="AA183" s="14" t="inlineStr"/>
+      <c r="AB183" s="14" t="inlineStr"/>
+      <c r="AC183" s="14" t="inlineStr"/>
+      <c r="AD183" s="14" t="inlineStr"/>
       <c r="AE183" s="14" t="inlineStr"/>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -26507,7 +26173,7 @@
       </c>
       <c r="AP183" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ183" s="14" t="inlineStr"/>
@@ -26533,9 +26199,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX183" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX183" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -26599,33 +26265,15 @@
       <c r="U184" s="14" t="n">
         <v>1.14</v>
       </c>
-      <c r="V184" s="14" t="n">
-        <v>0.6589</v>
-      </c>
-      <c r="W184" s="14" t="n">
-        <v>0.7295</v>
-      </c>
-      <c r="X184" s="14" t="n">
-        <v>1.3553</v>
-      </c>
-      <c r="Y184" s="14" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="Z184" s="14" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AA184" s="14" t="n">
-        <v>0.8767</v>
-      </c>
-      <c r="AB184" s="14" t="n">
-        <v>1.3305</v>
-      </c>
-      <c r="AC184" s="14" t="n">
-        <v>1.5407</v>
-      </c>
-      <c r="AD184" s="14" t="n">
-        <v>0.8892645603001489</v>
-      </c>
+      <c r="V184" s="14" t="inlineStr"/>
+      <c r="W184" s="14" t="inlineStr"/>
+      <c r="X184" s="14" t="inlineStr"/>
+      <c r="Y184" s="14" t="inlineStr"/>
+      <c r="Z184" s="14" t="inlineStr"/>
+      <c r="AA184" s="14" t="inlineStr"/>
+      <c r="AB184" s="14" t="inlineStr"/>
+      <c r="AC184" s="14" t="inlineStr"/>
+      <c r="AD184" s="14" t="inlineStr"/>
       <c r="AE184" s="14" t="inlineStr"/>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -26663,7 +26311,7 @@
       </c>
       <c r="AP184" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ184" s="14" t="inlineStr"/>
@@ -26755,33 +26403,15 @@
       <c r="U185" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="V185" s="14" t="n">
-        <v>0.8154</v>
-      </c>
-      <c r="W185" s="14" t="n">
-        <v>0.7075</v>
-      </c>
-      <c r="X185" s="14" t="n">
-        <v>0.7953</v>
-      </c>
-      <c r="Y185" s="14" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="Z185" s="14" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="AA185" s="14" t="n">
-        <v>0.8901</v>
-      </c>
-      <c r="AB185" s="14" t="n">
-        <v>1.0916</v>
-      </c>
-      <c r="AC185" s="14" t="n">
-        <v>1.1169</v>
-      </c>
-      <c r="AD185" s="14" t="n">
-        <v>0.8567525361013272</v>
-      </c>
+      <c r="V185" s="14" t="inlineStr"/>
+      <c r="W185" s="14" t="inlineStr"/>
+      <c r="X185" s="14" t="inlineStr"/>
+      <c r="Y185" s="14" t="inlineStr"/>
+      <c r="Z185" s="14" t="inlineStr"/>
+      <c r="AA185" s="14" t="inlineStr"/>
+      <c r="AB185" s="14" t="inlineStr"/>
+      <c r="AC185" s="14" t="inlineStr"/>
+      <c r="AD185" s="14" t="inlineStr"/>
       <c r="AE185" s="14" t="inlineStr"/>
       <c r="AF185" s="14" t="inlineStr"/>
       <c r="AG185" s="14" t="inlineStr"/>
@@ -26819,7 +26449,7 @@
       </c>
       <c r="AP185" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ185" s="14" t="inlineStr"/>
@@ -26911,33 +26541,15 @@
       <c r="U186" s="14" t="n">
         <v>1.49</v>
       </c>
-      <c r="V186" s="14" t="n">
-        <v>0.9241</v>
-      </c>
-      <c r="W186" s="14" t="n">
-        <v>0.7863</v>
-      </c>
-      <c r="X186" s="14" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="Y186" s="14" t="n">
-        <v>14.23</v>
-      </c>
-      <c r="Z186" s="14" t="n">
-        <v>-17.95</v>
-      </c>
-      <c r="AA186" s="14" t="n">
-        <v>0.9234</v>
-      </c>
-      <c r="AB186" s="14" t="n">
-        <v>0.9992</v>
-      </c>
-      <c r="AC186" s="14" t="n">
-        <v>0.9153</v>
-      </c>
-      <c r="AD186" s="14" t="n">
-        <v>0.9018538622771508</v>
-      </c>
+      <c r="V186" s="14" t="inlineStr"/>
+      <c r="W186" s="14" t="inlineStr"/>
+      <c r="X186" s="14" t="inlineStr"/>
+      <c r="Y186" s="14" t="inlineStr"/>
+      <c r="Z186" s="14" t="inlineStr"/>
+      <c r="AA186" s="14" t="inlineStr"/>
+      <c r="AB186" s="14" t="inlineStr"/>
+      <c r="AC186" s="14" t="inlineStr"/>
+      <c r="AD186" s="14" t="inlineStr"/>
       <c r="AE186" s="14" t="inlineStr"/>
       <c r="AF186" s="14" t="inlineStr"/>
       <c r="AG186" s="14" t="inlineStr"/>
@@ -26975,7 +26587,7 @@
       </c>
       <c r="AP186" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ186" s="14" t="inlineStr"/>
@@ -27067,33 +26679,15 @@
       <c r="U187" s="14" t="n">
         <v>1.08</v>
       </c>
-      <c r="V187" s="14" t="n">
-        <v>0.9288</v>
-      </c>
-      <c r="W187" s="14" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="X187" s="14" t="n">
-        <v>0.9267</v>
-      </c>
-      <c r="Y187" s="14" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="Z187" s="14" t="n">
-        <v>-20.67</v>
-      </c>
-      <c r="AA187" s="14" t="n">
-        <v>0.9802999999999999</v>
-      </c>
-      <c r="AB187" s="14" t="n">
-        <v>1.0555</v>
-      </c>
-      <c r="AC187" s="14" t="n">
-        <v>1.0032</v>
-      </c>
-      <c r="AD187" s="14" t="n">
-        <v>0.8985882502598999</v>
-      </c>
+      <c r="V187" s="14" t="inlineStr"/>
+      <c r="W187" s="14" t="inlineStr"/>
+      <c r="X187" s="14" t="inlineStr"/>
+      <c r="Y187" s="14" t="inlineStr"/>
+      <c r="Z187" s="14" t="inlineStr"/>
+      <c r="AA187" s="14" t="inlineStr"/>
+      <c r="AB187" s="14" t="inlineStr"/>
+      <c r="AC187" s="14" t="inlineStr"/>
+      <c r="AD187" s="14" t="inlineStr"/>
       <c r="AE187" s="14" t="inlineStr"/>
       <c r="AF187" s="14" t="inlineStr"/>
       <c r="AG187" s="14" t="inlineStr"/>
@@ -27131,7 +26725,7 @@
       </c>
       <c r="AP187" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ187" s="14" t="inlineStr"/>
@@ -27157,9 +26751,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX187" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX187" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -27223,30 +26817,14 @@
       <c r="U188" s="14" t="n">
         <v>1.24</v>
       </c>
-      <c r="V188" s="14" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="W188" s="14" t="n">
-        <v>0.9489</v>
-      </c>
-      <c r="X188" s="14" t="n">
-        <v>0.6561</v>
-      </c>
-      <c r="Y188" s="14" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="Z188" s="14" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA188" s="14" t="n">
-        <v>1.1181</v>
-      </c>
-      <c r="AB188" s="14" t="n">
-        <v>1.1299</v>
-      </c>
-      <c r="AC188" s="14" t="n">
-        <v>1.0454</v>
-      </c>
+      <c r="V188" s="14" t="inlineStr"/>
+      <c r="W188" s="14" t="inlineStr"/>
+      <c r="X188" s="14" t="inlineStr"/>
+      <c r="Y188" s="14" t="inlineStr"/>
+      <c r="Z188" s="14" t="inlineStr"/>
+      <c r="AA188" s="14" t="inlineStr"/>
+      <c r="AB188" s="14" t="inlineStr"/>
+      <c r="AC188" s="14" t="inlineStr"/>
       <c r="AD188" s="14" t="inlineStr"/>
       <c r="AE188" s="14" t="inlineStr"/>
       <c r="AF188" s="14" t="inlineStr"/>
@@ -27285,7 +26863,7 @@
       </c>
       <c r="AP188" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ188" s="14" t="inlineStr"/>
@@ -27311,9 +26889,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX188" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX188" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -27515,31 +27093,15 @@
       <c r="U190" s="14" t="n">
         <v>0.97</v>
       </c>
-      <c r="V190" s="14" t="n">
-        <v>0.9356</v>
-      </c>
+      <c r="V190" s="14" t="inlineStr"/>
       <c r="W190" s="14" t="inlineStr"/>
-      <c r="X190" s="14" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="Y190" s="14" t="n">
-        <v>14.91</v>
-      </c>
-      <c r="Z190" s="14" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="AA190" s="14" t="n">
-        <v>1.1265</v>
-      </c>
-      <c r="AB190" s="14" t="n">
-        <v>1.2041</v>
-      </c>
-      <c r="AC190" s="14" t="n">
-        <v>1.0934</v>
-      </c>
-      <c r="AD190" s="14" t="n">
-        <v>0.8119162305722145</v>
-      </c>
+      <c r="X190" s="14" t="inlineStr"/>
+      <c r="Y190" s="14" t="inlineStr"/>
+      <c r="Z190" s="14" t="inlineStr"/>
+      <c r="AA190" s="14" t="inlineStr"/>
+      <c r="AB190" s="14" t="inlineStr"/>
+      <c r="AC190" s="14" t="inlineStr"/>
+      <c r="AD190" s="14" t="inlineStr"/>
       <c r="AE190" s="14" t="inlineStr"/>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -27577,7 +27139,7 @@
       </c>
       <c r="AP190" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ190" s="14" t="inlineStr"/>
@@ -27669,31 +27231,15 @@
       <c r="U191" s="14" t="n">
         <v>0.67</v>
       </c>
-      <c r="V191" s="14" t="n">
-        <v>0.954</v>
-      </c>
+      <c r="V191" s="14" t="inlineStr"/>
       <c r="W191" s="14" t="inlineStr"/>
-      <c r="X191" s="14" t="n">
-        <v>1.295</v>
-      </c>
-      <c r="Y191" s="14" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="Z191" s="14" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="AA191" s="14" t="n">
-        <v>1.2471</v>
-      </c>
-      <c r="AB191" s="14" t="n">
-        <v>1.3073</v>
-      </c>
-      <c r="AC191" s="14" t="n">
-        <v>1.1853</v>
-      </c>
-      <c r="AD191" s="14" t="n">
-        <v>0.8331702243115301</v>
-      </c>
+      <c r="X191" s="14" t="inlineStr"/>
+      <c r="Y191" s="14" t="inlineStr"/>
+      <c r="Z191" s="14" t="inlineStr"/>
+      <c r="AA191" s="14" t="inlineStr"/>
+      <c r="AB191" s="14" t="inlineStr"/>
+      <c r="AC191" s="14" t="inlineStr"/>
+      <c r="AD191" s="14" t="inlineStr"/>
       <c r="AE191" s="14" t="inlineStr"/>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -27731,7 +27277,7 @@
       </c>
       <c r="AP191" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ191" s="14" t="inlineStr"/>
@@ -27823,29 +27369,15 @@
       <c r="U192" s="14" t="n">
         <v>1.08</v>
       </c>
-      <c r="V192" s="14" t="n">
-        <v>0.9431</v>
-      </c>
-      <c r="W192" s="14" t="n">
-        <v>0.9444</v>
-      </c>
-      <c r="X192" s="14" t="n">
-        <v>1.1697</v>
-      </c>
+      <c r="V192" s="14" t="inlineStr"/>
+      <c r="W192" s="14" t="inlineStr"/>
+      <c r="X192" s="14" t="inlineStr"/>
       <c r="Y192" s="14" t="inlineStr"/>
       <c r="Z192" s="14" t="inlineStr"/>
-      <c r="AA192" s="14" t="n">
-        <v>1.3077</v>
-      </c>
-      <c r="AB192" s="14" t="n">
-        <v>1.3866</v>
-      </c>
-      <c r="AC192" s="14" t="n">
-        <v>1.1734</v>
-      </c>
-      <c r="AD192" s="14" t="n">
-        <v>0.8277561437524656</v>
-      </c>
+      <c r="AA192" s="14" t="inlineStr"/>
+      <c r="AB192" s="14" t="inlineStr"/>
+      <c r="AC192" s="14" t="inlineStr"/>
+      <c r="AD192" s="14" t="inlineStr"/>
       <c r="AE192" s="14" t="inlineStr"/>
       <c r="AF192" s="14" t="inlineStr"/>
       <c r="AG192" s="14" t="inlineStr"/>
@@ -27883,7 +27415,7 @@
       </c>
       <c r="AP192" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ192" s="14" t="inlineStr"/>
@@ -27975,33 +27507,15 @@
       <c r="U193" s="14" t="n">
         <v>0.38</v>
       </c>
-      <c r="V193" s="14" t="n">
-        <v>0.9059</v>
-      </c>
-      <c r="W193" s="14" t="n">
-        <v>0.9336</v>
-      </c>
-      <c r="X193" s="14" t="n">
-        <v>1.2032</v>
-      </c>
-      <c r="Y193" s="14" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="Z193" s="14" t="n">
-        <v>18.82</v>
-      </c>
-      <c r="AA193" s="14" t="n">
-        <v>1.296</v>
-      </c>
-      <c r="AB193" s="14" t="n">
-        <v>1.4307</v>
-      </c>
-      <c r="AC193" s="14" t="n">
-        <v>1.2578</v>
-      </c>
-      <c r="AD193" s="14" t="n">
-        <v>0.7712381484075153</v>
-      </c>
+      <c r="V193" s="14" t="inlineStr"/>
+      <c r="W193" s="14" t="inlineStr"/>
+      <c r="X193" s="14" t="inlineStr"/>
+      <c r="Y193" s="14" t="inlineStr"/>
+      <c r="Z193" s="14" t="inlineStr"/>
+      <c r="AA193" s="14" t="inlineStr"/>
+      <c r="AB193" s="14" t="inlineStr"/>
+      <c r="AC193" s="14" t="inlineStr"/>
+      <c r="AD193" s="14" t="inlineStr"/>
       <c r="AE193" s="14" t="inlineStr"/>
       <c r="AF193" s="14" t="inlineStr"/>
       <c r="AG193" s="14" t="inlineStr"/>
@@ -28039,7 +27553,7 @@
       </c>
       <c r="AP193" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ193" s="14" t="inlineStr"/>
@@ -28065,9 +27579,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX193" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX193" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -28131,31 +27645,15 @@
       <c r="U194" s="14" t="n">
         <v>0.38</v>
       </c>
-      <c r="V194" s="14" t="n">
-        <v>0.8287</v>
-      </c>
-      <c r="W194" s="14" t="n">
-        <v>0.8915</v>
-      </c>
+      <c r="V194" s="14" t="inlineStr"/>
+      <c r="W194" s="14" t="inlineStr"/>
       <c r="X194" s="14" t="inlineStr"/>
-      <c r="Y194" s="14" t="n">
-        <v>-2.74</v>
-      </c>
-      <c r="Z194" s="14" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="AA194" s="14" t="n">
-        <v>1.2129</v>
-      </c>
-      <c r="AB194" s="14" t="n">
-        <v>1.4637</v>
-      </c>
-      <c r="AC194" s="14" t="n">
-        <v>1.2462</v>
-      </c>
-      <c r="AD194" s="14" t="n">
-        <v>0.7679312376206273</v>
-      </c>
+      <c r="Y194" s="14" t="inlineStr"/>
+      <c r="Z194" s="14" t="inlineStr"/>
+      <c r="AA194" s="14" t="inlineStr"/>
+      <c r="AB194" s="14" t="inlineStr"/>
+      <c r="AC194" s="14" t="inlineStr"/>
+      <c r="AD194" s="14" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
         <v>133763.5</v>
       </c>
@@ -28195,7 +27693,7 @@
       </c>
       <c r="AP194" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ194" s="14" t="inlineStr"/>
@@ -28287,33 +27785,15 @@
       <c r="U195" s="14" t="n">
         <v>4.07</v>
       </c>
-      <c r="V195" s="14" t="n">
-        <v>0.7305</v>
-      </c>
-      <c r="W195" s="14" t="n">
-        <v>0.8181</v>
-      </c>
-      <c r="X195" s="14" t="n">
-        <v>1.2339</v>
-      </c>
-      <c r="Y195" s="14" t="n">
-        <v>-10.16</v>
-      </c>
-      <c r="Z195" s="14" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="AA195" s="14" t="n">
-        <v>1.1748</v>
-      </c>
-      <c r="AB195" s="14" t="n">
-        <v>1.6082</v>
-      </c>
-      <c r="AC195" s="14" t="n">
-        <v>1.3491</v>
-      </c>
-      <c r="AD195" s="14" t="n">
-        <v>0.8870390275210638</v>
-      </c>
+      <c r="V195" s="14" t="inlineStr"/>
+      <c r="W195" s="14" t="inlineStr"/>
+      <c r="X195" s="14" t="inlineStr"/>
+      <c r="Y195" s="14" t="inlineStr"/>
+      <c r="Z195" s="14" t="inlineStr"/>
+      <c r="AA195" s="14" t="inlineStr"/>
+      <c r="AB195" s="14" t="inlineStr"/>
+      <c r="AC195" s="14" t="inlineStr"/>
+      <c r="AD195" s="14" t="inlineStr"/>
       <c r="AE195" s="14" t="n">
         <v>2782883.09</v>
       </c>
@@ -28353,7 +27833,7 @@
       </c>
       <c r="AP195" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ195" s="14" t="inlineStr"/>
@@ -28379,9 +27859,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX195" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX195" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -28445,33 +27925,15 @@
       <c r="U196" s="14" t="n">
         <v>2.96</v>
       </c>
-      <c r="V196" s="14" t="n">
-        <v>0.5038</v>
-      </c>
-      <c r="W196" s="14" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="X196" s="14" t="n">
-        <v>1.6883</v>
-      </c>
-      <c r="Y196" s="14" t="n">
-        <v>-18.04</v>
-      </c>
-      <c r="Z196" s="14" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="AA196" s="14" t="n">
-        <v>1.0622</v>
-      </c>
-      <c r="AB196" s="14" t="n">
-        <v>2.1085</v>
-      </c>
-      <c r="AC196" s="14" t="n">
-        <v>2.0012</v>
-      </c>
-      <c r="AD196" s="14" t="n">
-        <v>0.901265524513426</v>
-      </c>
+      <c r="V196" s="14" t="inlineStr"/>
+      <c r="W196" s="14" t="inlineStr"/>
+      <c r="X196" s="14" t="inlineStr"/>
+      <c r="Y196" s="14" t="inlineStr"/>
+      <c r="Z196" s="14" t="inlineStr"/>
+      <c r="AA196" s="14" t="inlineStr"/>
+      <c r="AB196" s="14" t="inlineStr"/>
+      <c r="AC196" s="14" t="inlineStr"/>
+      <c r="AD196" s="14" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
         <v>424020.27</v>
       </c>
@@ -28511,7 +27973,7 @@
       </c>
       <c r="AP196" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ196" s="14" t="inlineStr"/>
@@ -28603,33 +28065,15 @@
       <c r="U197" s="14" t="n">
         <v>0.55</v>
       </c>
-      <c r="V197" s="14" t="n">
-        <v>0.4462</v>
-      </c>
-      <c r="W197" s="14" t="n">
-        <v>0.5414</v>
-      </c>
-      <c r="X197" s="14" t="n">
-        <v>1.8845</v>
-      </c>
-      <c r="Y197" s="14" t="n">
-        <v>-13.13</v>
-      </c>
-      <c r="Z197" s="14" t="n">
-        <v>61.32</v>
-      </c>
-      <c r="AA197" s="14" t="n">
-        <v>1.0536</v>
-      </c>
-      <c r="AB197" s="14" t="n">
-        <v>2.3613</v>
-      </c>
-      <c r="AC197" s="14" t="n">
-        <v>2.2113</v>
-      </c>
-      <c r="AD197" s="14" t="n">
-        <v>0.8702244940145547</v>
-      </c>
+      <c r="V197" s="14" t="inlineStr"/>
+      <c r="W197" s="14" t="inlineStr"/>
+      <c r="X197" s="14" t="inlineStr"/>
+      <c r="Y197" s="14" t="inlineStr"/>
+      <c r="Z197" s="14" t="inlineStr"/>
+      <c r="AA197" s="14" t="inlineStr"/>
+      <c r="AB197" s="14" t="inlineStr"/>
+      <c r="AC197" s="14" t="inlineStr"/>
+      <c r="AD197" s="14" t="inlineStr"/>
       <c r="AE197" s="14" t="n">
         <v>112152</v>
       </c>
@@ -28669,7 +28113,7 @@
       </c>
       <c r="AP197" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ197" s="14" t="inlineStr"/>
@@ -28761,33 +28205,15 @@
       <c r="U198" s="14" t="n">
         <v>0.53</v>
       </c>
-      <c r="V198" s="14" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="W198" s="14" t="n">
-        <v>0.4753</v>
-      </c>
-      <c r="X198" s="14" t="n">
-        <v>1.7507</v>
-      </c>
-      <c r="Y198" s="14" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="Z198" s="14" t="n">
-        <v>46.83</v>
-      </c>
-      <c r="AA198" s="14" t="n">
-        <v>1.131</v>
-      </c>
-      <c r="AB198" s="14" t="n">
-        <v>2.3613</v>
-      </c>
-      <c r="AC198" s="14" t="n">
-        <v>2.202</v>
-      </c>
-      <c r="AD198" s="14" t="n">
-        <v>0.8665818841929512</v>
-      </c>
+      <c r="V198" s="14" t="inlineStr"/>
+      <c r="W198" s="14" t="inlineStr"/>
+      <c r="X198" s="14" t="inlineStr"/>
+      <c r="Y198" s="14" t="inlineStr"/>
+      <c r="Z198" s="14" t="inlineStr"/>
+      <c r="AA198" s="14" t="inlineStr"/>
+      <c r="AB198" s="14" t="inlineStr"/>
+      <c r="AC198" s="14" t="inlineStr"/>
+      <c r="AD198" s="14" t="inlineStr"/>
       <c r="AE198" s="14" t="n">
         <v>41359.21</v>
       </c>
@@ -28827,7 +28253,7 @@
       </c>
       <c r="AP198" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ198" s="14" t="inlineStr"/>
@@ -28850,7 +28276,7 @@
       </c>
       <c r="AW198" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX198" s="14" t="inlineStr">
@@ -28919,33 +28345,15 @@
       <c r="U199" s="14" t="n">
         <v>0.45</v>
       </c>
-      <c r="V199" s="14" t="n">
-        <v>0.4945</v>
-      </c>
-      <c r="W199" s="14" t="n">
-        <v>0.4729</v>
-      </c>
-      <c r="X199" s="14" t="n">
-        <v>1.6343</v>
-      </c>
-      <c r="Y199" s="14" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="Z199" s="14" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="AA199" s="14" t="n">
-        <v>1.1126</v>
-      </c>
-      <c r="AB199" s="14" t="n">
-        <v>2.2499</v>
-      </c>
-      <c r="AC199" s="14" t="n">
-        <v>2.0367</v>
-      </c>
-      <c r="AD199" s="14" t="n">
-        <v>0.8760104412928778</v>
-      </c>
+      <c r="V199" s="14" t="inlineStr"/>
+      <c r="W199" s="14" t="inlineStr"/>
+      <c r="X199" s="14" t="inlineStr"/>
+      <c r="Y199" s="14" t="inlineStr"/>
+      <c r="Z199" s="14" t="inlineStr"/>
+      <c r="AA199" s="14" t="inlineStr"/>
+      <c r="AB199" s="14" t="inlineStr"/>
+      <c r="AC199" s="14" t="inlineStr"/>
+      <c r="AD199" s="14" t="inlineStr"/>
       <c r="AE199" s="14" t="n">
         <v>41513.48</v>
       </c>
@@ -28985,7 +28393,7 @@
       </c>
       <c r="AP199" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ199" s="14" t="inlineStr"/>
@@ -29008,7 +28416,7 @@
       </c>
       <c r="AW199" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX199" s="14" t="inlineStr">
@@ -29077,33 +28485,15 @@
       <c r="U200" s="14" t="n">
         <v>0.65</v>
       </c>
-      <c r="V200" s="14" t="n">
-        <v>0.5078</v>
-      </c>
-      <c r="W200" s="14" t="n">
-        <v>0.4931</v>
-      </c>
-      <c r="X200" s="14" t="n">
-        <v>1.3333</v>
-      </c>
-      <c r="Y200" s="14" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="Z200" s="14" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="AA200" s="14" t="n">
-        <v>1.0504</v>
-      </c>
-      <c r="AB200" s="14" t="n">
-        <v>2.0684</v>
-      </c>
-      <c r="AC200" s="14" t="n">
-        <v>1.7988</v>
-      </c>
-      <c r="AD200" s="14" t="n">
-        <v>0.7505972657923646</v>
-      </c>
+      <c r="V200" s="14" t="inlineStr"/>
+      <c r="W200" s="14" t="inlineStr"/>
+      <c r="X200" s="14" t="inlineStr"/>
+      <c r="Y200" s="14" t="inlineStr"/>
+      <c r="Z200" s="14" t="inlineStr"/>
+      <c r="AA200" s="14" t="inlineStr"/>
+      <c r="AB200" s="14" t="inlineStr"/>
+      <c r="AC200" s="14" t="inlineStr"/>
+      <c r="AD200" s="14" t="inlineStr"/>
       <c r="AE200" s="14" t="n">
         <v>85372.74000000001</v>
       </c>
@@ -29143,7 +28533,7 @@
       </c>
       <c r="AP200" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ200" s="14" t="inlineStr"/>
@@ -29166,7 +28556,7 @@
       </c>
       <c r="AW200" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX200" s="14" t="inlineStr">
@@ -29235,33 +28625,15 @@
       <c r="U201" s="14" t="n">
         <v>0.39</v>
       </c>
-      <c r="V201" s="14" t="n">
-        <v>0.5161</v>
-      </c>
-      <c r="W201" s="14" t="n">
-        <v>0.5056</v>
-      </c>
-      <c r="X201" s="14" t="n">
-        <v>0.8283</v>
-      </c>
-      <c r="Y201" s="14" t="n">
-        <v>-11.58</v>
-      </c>
-      <c r="Z201" s="14" t="n">
-        <v>-17.94</v>
-      </c>
-      <c r="AA201" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB201" s="14" t="n">
-        <v>1.9377</v>
-      </c>
-      <c r="AC201" s="14" t="n">
-        <v>1.6575</v>
-      </c>
-      <c r="AD201" s="14" t="n">
-        <v>0.920264352053598</v>
-      </c>
+      <c r="V201" s="14" t="inlineStr"/>
+      <c r="W201" s="14" t="inlineStr"/>
+      <c r="X201" s="14" t="inlineStr"/>
+      <c r="Y201" s="14" t="inlineStr"/>
+      <c r="Z201" s="14" t="inlineStr"/>
+      <c r="AA201" s="14" t="inlineStr"/>
+      <c r="AB201" s="14" t="inlineStr"/>
+      <c r="AC201" s="14" t="inlineStr"/>
+      <c r="AD201" s="14" t="inlineStr"/>
       <c r="AE201" s="14" t="n">
         <v>39359.1</v>
       </c>
@@ -29301,7 +28673,7 @@
       </c>
       <c r="AP201" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ201" s="14" t="inlineStr"/>
@@ -29393,33 +28765,15 @@
       <c r="U202" s="14" t="n">
         <v>0.87</v>
       </c>
-      <c r="V202" s="14" t="n">
-        <v>0.5403</v>
-      </c>
-      <c r="W202" s="14" t="n">
-        <v>0.5206</v>
-      </c>
-      <c r="X202" s="14" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="Y202" s="14" t="n">
-        <v>-13.67</v>
-      </c>
-      <c r="Z202" s="14" t="n">
-        <v>-20.98</v>
-      </c>
-      <c r="AA202" s="14" t="n">
-        <v>0.9605</v>
-      </c>
-      <c r="AB202" s="14" t="n">
-        <v>1.7778</v>
-      </c>
-      <c r="AC202" s="14" t="n">
-        <v>1.5589</v>
-      </c>
-      <c r="AD202" s="14" t="n">
-        <v>0.8849337530411966</v>
-      </c>
+      <c r="V202" s="14" t="inlineStr"/>
+      <c r="W202" s="14" t="inlineStr"/>
+      <c r="X202" s="14" t="inlineStr"/>
+      <c r="Y202" s="14" t="inlineStr"/>
+      <c r="Z202" s="14" t="inlineStr"/>
+      <c r="AA202" s="14" t="inlineStr"/>
+      <c r="AB202" s="14" t="inlineStr"/>
+      <c r="AC202" s="14" t="inlineStr"/>
+      <c r="AD202" s="14" t="inlineStr"/>
       <c r="AE202" s="14" t="n">
         <v>31739.83</v>
       </c>
@@ -29459,7 +28813,7 @@
       </c>
       <c r="AP202" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ202" s="14" t="inlineStr"/>
@@ -29551,33 +28905,15 @@
       <c r="U203" s="14" t="n">
         <v>0.76</v>
       </c>
-      <c r="V203" s="14" t="n">
-        <v>0.5467</v>
-      </c>
-      <c r="W203" s="14" t="n">
-        <v>0.5337</v>
-      </c>
-      <c r="X203" s="14" t="n">
-        <v>0.6886</v>
-      </c>
-      <c r="Y203" s="14" t="n">
-        <v>-10.42</v>
-      </c>
-      <c r="Z203" s="14" t="n">
-        <v>-16.79</v>
-      </c>
-      <c r="AA203" s="14" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="AB203" s="14" t="n">
-        <v>1.7211</v>
-      </c>
-      <c r="AC203" s="14" t="n">
-        <v>1.5164</v>
-      </c>
-      <c r="AD203" s="14" t="n">
-        <v>0.9552042842085368</v>
-      </c>
+      <c r="V203" s="14" t="inlineStr"/>
+      <c r="W203" s="14" t="inlineStr"/>
+      <c r="X203" s="14" t="inlineStr"/>
+      <c r="Y203" s="14" t="inlineStr"/>
+      <c r="Z203" s="14" t="inlineStr"/>
+      <c r="AA203" s="14" t="inlineStr"/>
+      <c r="AB203" s="14" t="inlineStr"/>
+      <c r="AC203" s="14" t="inlineStr"/>
+      <c r="AD203" s="14" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
         <v>707702.4</v>
       </c>
@@ -29617,7 +28953,7 @@
       </c>
       <c r="AP203" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ203" s="14" t="inlineStr"/>
@@ -29709,33 +29045,15 @@
       <c r="U204" s="14" t="n">
         <v>0.43</v>
       </c>
-      <c r="V204" s="14" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="W204" s="14" t="n">
-        <v>0.5389</v>
-      </c>
-      <c r="X204" s="14" t="n">
-        <v>0.9019</v>
-      </c>
-      <c r="Y204" s="14" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="Z204" s="14" t="n">
-        <v>19.96</v>
-      </c>
-      <c r="AA204" s="14" t="n">
-        <v>1.2367</v>
-      </c>
-      <c r="AB204" s="14" t="n">
-        <v>2.3245</v>
-      </c>
-      <c r="AC204" s="14" t="n">
-        <v>1.8369</v>
-      </c>
-      <c r="AD204" s="14" t="n">
-        <v>0.9636193042356076</v>
-      </c>
+      <c r="V204" s="14" t="inlineStr"/>
+      <c r="W204" s="14" t="inlineStr"/>
+      <c r="X204" s="14" t="inlineStr"/>
+      <c r="Y204" s="14" t="inlineStr"/>
+      <c r="Z204" s="14" t="inlineStr"/>
+      <c r="AA204" s="14" t="inlineStr"/>
+      <c r="AB204" s="14" t="inlineStr"/>
+      <c r="AC204" s="14" t="inlineStr"/>
+      <c r="AD204" s="14" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
         <v>205184.69</v>
       </c>
@@ -29775,7 +29093,7 @@
       </c>
       <c r="AP204" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ204" s="14" t="inlineStr"/>
@@ -29846,12 +29164,8 @@
       <c r="L205" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M205" s="14" t="n">
-        <v>4473114.069589</v>
-      </c>
-      <c r="N205" s="14" t="n">
-        <v>86437822</v>
-      </c>
+      <c r="M205" s="14" t="inlineStr"/>
+      <c r="N205" s="14" t="inlineStr"/>
       <c r="O205" s="14" t="b">
         <v>1</v>
       </c>
@@ -29871,40 +29185,20 @@
       <c r="U205" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="V205" s="14" t="n">
-        <v>0.5707</v>
-      </c>
-      <c r="W205" s="14" t="n">
-        <v>0.5499000000000001</v>
-      </c>
-      <c r="X205" s="14" t="n">
-        <v>0.9978</v>
-      </c>
-      <c r="Y205" s="14" t="n">
-        <v>34.44</v>
-      </c>
-      <c r="Z205" s="14" t="n">
-        <v>27.27</v>
-      </c>
-      <c r="AA205" s="14" t="n">
-        <v>1.2913</v>
-      </c>
-      <c r="AB205" s="14" t="n">
-        <v>2.2626</v>
-      </c>
-      <c r="AC205" s="14" t="n">
-        <v>1.7949</v>
-      </c>
-      <c r="AD205" s="14" t="n">
-        <v>0.8727540911224712</v>
-      </c>
+      <c r="V205" s="14" t="inlineStr"/>
+      <c r="W205" s="14" t="inlineStr"/>
+      <c r="X205" s="14" t="inlineStr"/>
+      <c r="Y205" s="14" t="inlineStr"/>
+      <c r="Z205" s="14" t="inlineStr"/>
+      <c r="AA205" s="14" t="inlineStr"/>
+      <c r="AB205" s="14" t="inlineStr"/>
+      <c r="AC205" s="14" t="inlineStr"/>
+      <c r="AD205" s="14" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
         <v>136096.67</v>
       </c>
       <c r="AF205" s="14" t="n"/>
-      <c r="AG205" s="14" t="n">
-        <v>0.030425</v>
-      </c>
+      <c r="AG205" s="14" t="n"/>
       <c r="AH205" s="14" t="inlineStr"/>
       <c r="AI205" s="14" t="inlineStr">
         <is>
@@ -29939,7 +29233,7 @@
       </c>
       <c r="AP205" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ205" s="14" t="inlineStr"/>
@@ -30010,12 +29304,8 @@
       <c r="L206" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M206" s="14" t="n">
-        <v>4368376.0753</v>
-      </c>
-      <c r="N206" s="14" t="n">
-        <v>84971330</v>
-      </c>
+      <c r="M206" s="14" t="inlineStr"/>
+      <c r="N206" s="14" t="inlineStr"/>
       <c r="O206" s="14" t="b">
         <v>1</v>
       </c>
@@ -30035,40 +29325,20 @@
       <c r="U206" s="14" t="n">
         <v>0.36</v>
       </c>
-      <c r="V206" s="14" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="W206" s="14" t="n">
-        <v>0.5355</v>
-      </c>
-      <c r="X206" s="14" t="n">
-        <v>1.196</v>
-      </c>
-      <c r="Y206" s="14" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="Z206" s="14" t="n">
-        <v>45.69</v>
-      </c>
-      <c r="AA206" s="14" t="n">
-        <v>1.2713</v>
-      </c>
-      <c r="AB206" s="14" t="n">
-        <v>2.5075</v>
-      </c>
-      <c r="AC206" s="14" t="n">
-        <v>1.9824</v>
-      </c>
-      <c r="AD206" s="14" t="n">
-        <v>0.8911021333131565</v>
-      </c>
+      <c r="V206" s="14" t="inlineStr"/>
+      <c r="W206" s="14" t="inlineStr"/>
+      <c r="X206" s="14" t="inlineStr"/>
+      <c r="Y206" s="14" t="inlineStr"/>
+      <c r="Z206" s="14" t="inlineStr"/>
+      <c r="AA206" s="14" t="inlineStr"/>
+      <c r="AB206" s="14" t="inlineStr"/>
+      <c r="AC206" s="14" t="inlineStr"/>
+      <c r="AD206" s="14" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
         <v>53541.13</v>
       </c>
       <c r="AF206" s="14" t="n"/>
-      <c r="AG206" s="14" t="n">
-        <v>0.012257</v>
-      </c>
+      <c r="AG206" s="14" t="n"/>
       <c r="AH206" s="14" t="inlineStr"/>
       <c r="AI206" s="14" t="inlineStr">
         <is>
@@ -30103,7 +29373,7 @@
       </c>
       <c r="AP206" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ206" s="14" t="inlineStr"/>
@@ -30129,9 +29399,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX206" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX206" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -30174,12 +29444,8 @@
       <c r="L207" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M207" s="14" t="n">
-        <v>4020252.93176824</v>
-      </c>
-      <c r="N207" s="14" t="n">
-        <v>83160533</v>
-      </c>
+      <c r="M207" s="14" t="inlineStr"/>
+      <c r="N207" s="14" t="inlineStr"/>
       <c r="O207" s="14" t="b">
         <v>1</v>
       </c>
@@ -30199,40 +29465,20 @@
       <c r="U207" s="14" t="n">
         <v>0.24</v>
       </c>
-      <c r="V207" s="14" t="n">
-        <v>0.5076000000000001</v>
-      </c>
-      <c r="W207" s="14" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="X207" s="14" t="n">
-        <v>1.3154</v>
-      </c>
-      <c r="Y207" s="14" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="Z207" s="14" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA207" s="14" t="n">
-        <v>1.2779</v>
-      </c>
-      <c r="AB207" s="14" t="n">
-        <v>2.5174</v>
-      </c>
-      <c r="AC207" s="14" t="n">
-        <v>2.0506</v>
-      </c>
-      <c r="AD207" s="14" t="n">
-        <v>0.9460859440335908</v>
-      </c>
+      <c r="V207" s="14" t="inlineStr"/>
+      <c r="W207" s="14" t="inlineStr"/>
+      <c r="X207" s="14" t="inlineStr"/>
+      <c r="Y207" s="14" t="inlineStr"/>
+      <c r="Z207" s="14" t="inlineStr"/>
+      <c r="AA207" s="14" t="inlineStr"/>
+      <c r="AB207" s="14" t="inlineStr"/>
+      <c r="AC207" s="14" t="inlineStr"/>
+      <c r="AD207" s="14" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
         <v>11110</v>
       </c>
       <c r="AF207" s="14" t="n"/>
-      <c r="AG207" s="14" t="n">
-        <v>0.002764</v>
-      </c>
+      <c r="AG207" s="14" t="n"/>
       <c r="AH207" s="14" t="inlineStr"/>
       <c r="AI207" s="14" t="inlineStr">
         <is>
@@ -30267,7 +29513,7 @@
       </c>
       <c r="AP207" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ207" s="14" t="inlineStr"/>
@@ -30338,12 +29584,8 @@
       <c r="L208" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M208" s="14" t="n">
-        <v>4127475.92468776</v>
-      </c>
-      <c r="N208" s="14" t="n">
-        <v>82065692</v>
-      </c>
+      <c r="M208" s="14" t="inlineStr"/>
+      <c r="N208" s="14" t="inlineStr"/>
       <c r="O208" s="14" t="b">
         <v>1</v>
       </c>
@@ -30363,40 +29605,20 @@
       <c r="U208" s="14" t="n">
         <v>0.23</v>
       </c>
-      <c r="V208" s="14" t="n">
-        <v>0.4918</v>
-      </c>
-      <c r="W208" s="14" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="X208" s="14" t="n">
-        <v>1.4617</v>
-      </c>
-      <c r="Y208" s="14" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z208" s="14" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="AA208" s="14" t="n">
-        <v>1.3024</v>
-      </c>
-      <c r="AB208" s="14" t="n">
-        <v>2.6483</v>
-      </c>
-      <c r="AC208" s="14" t="n">
-        <v>2.2165</v>
-      </c>
-      <c r="AD208" s="14" t="n">
-        <v>1.063482696234339</v>
-      </c>
+      <c r="V208" s="14" t="inlineStr"/>
+      <c r="W208" s="14" t="inlineStr"/>
+      <c r="X208" s="14" t="inlineStr"/>
+      <c r="Y208" s="14" t="inlineStr"/>
+      <c r="Z208" s="14" t="inlineStr"/>
+      <c r="AA208" s="14" t="inlineStr"/>
+      <c r="AB208" s="14" t="inlineStr"/>
+      <c r="AC208" s="14" t="inlineStr"/>
+      <c r="AD208" s="14" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
         <v>19383.96</v>
       </c>
       <c r="AF208" s="14" t="n"/>
-      <c r="AG208" s="14" t="n">
-        <v>0.004696</v>
-      </c>
+      <c r="AG208" s="14" t="n"/>
       <c r="AH208" s="14" t="inlineStr"/>
       <c r="AI208" s="14" t="inlineStr">
         <is>
@@ -30431,7 +29653,7 @@
       </c>
       <c r="AP208" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ208" s="14" t="inlineStr"/>
@@ -30502,12 +29724,8 @@
       <c r="L209" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M209" s="14" t="n">
-        <v>4221431.37792</v>
-      </c>
-      <c r="N209" s="14" t="n">
-        <v>82538496</v>
-      </c>
+      <c r="M209" s="14" t="inlineStr"/>
+      <c r="N209" s="14" t="inlineStr"/>
       <c r="O209" s="14" t="b">
         <v>1</v>
       </c>
@@ -30527,40 +29745,20 @@
       <c r="U209" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="V209" s="14" t="n">
-        <v>0.3435</v>
-      </c>
-      <c r="W209" s="14" t="n">
-        <v>0.4335</v>
-      </c>
-      <c r="X209" s="14" t="n">
-        <v>1.7536</v>
-      </c>
-      <c r="Y209" s="14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z209" s="14" t="n">
-        <v>50.84</v>
-      </c>
-      <c r="AA209" s="14" t="n">
-        <v>1.2991</v>
-      </c>
-      <c r="AB209" s="14" t="n">
-        <v>3.7824</v>
-      </c>
-      <c r="AC209" s="14" t="n">
-        <v>3.2212</v>
-      </c>
-      <c r="AD209" s="14" t="n">
-        <v>0.9881075041911432</v>
-      </c>
+      <c r="V209" s="14" t="inlineStr"/>
+      <c r="W209" s="14" t="inlineStr"/>
+      <c r="X209" s="14" t="inlineStr"/>
+      <c r="Y209" s="14" t="inlineStr"/>
+      <c r="Z209" s="14" t="inlineStr"/>
+      <c r="AA209" s="14" t="inlineStr"/>
+      <c r="AB209" s="14" t="inlineStr"/>
+      <c r="AC209" s="14" t="inlineStr"/>
+      <c r="AD209" s="14" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
         <v>57855.69</v>
       </c>
       <c r="AF209" s="14" t="n"/>
-      <c r="AG209" s="14" t="n">
-        <v>0.013705</v>
-      </c>
+      <c r="AG209" s="14" t="n"/>
       <c r="AH209" s="14" t="inlineStr"/>
       <c r="AI209" s="14" t="inlineStr">
         <is>
@@ -30595,7 +29793,7 @@
       </c>
       <c r="AP209" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ209" s="14" t="inlineStr"/>
@@ -30618,7 +29816,7 @@
       </c>
       <c r="AW209" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX209" s="14" t="inlineStr">
@@ -30666,12 +29864,8 @@
       <c r="L210" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M210" s="14" t="n">
-        <v>4601833.86173025</v>
-      </c>
-      <c r="N210" s="14" t="n">
-        <v>83415925</v>
-      </c>
+      <c r="M210" s="14" t="inlineStr"/>
+      <c r="N210" s="14" t="inlineStr"/>
       <c r="O210" s="14" t="b">
         <v>1</v>
       </c>
@@ -30691,40 +29885,20 @@
       <c r="U210" s="14" t="n">
         <v>0.37</v>
       </c>
-      <c r="V210" s="14" t="n">
-        <v>0.3004</v>
-      </c>
-      <c r="W210" s="14" t="n">
-        <v>0.3629</v>
-      </c>
-      <c r="X210" s="14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y210" s="14" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Z210" s="14" t="n">
-        <v>70.34</v>
-      </c>
-      <c r="AA210" s="14" t="n">
-        <v>1.2882</v>
-      </c>
-      <c r="AB210" s="14" t="n">
-        <v>4.2882</v>
-      </c>
-      <c r="AC210" s="14" t="n">
-        <v>3.6795</v>
-      </c>
-      <c r="AD210" s="14" t="n">
-        <v>0.921254476412496</v>
-      </c>
+      <c r="V210" s="14" t="inlineStr"/>
+      <c r="W210" s="14" t="inlineStr"/>
+      <c r="X210" s="14" t="inlineStr"/>
+      <c r="Y210" s="14" t="inlineStr"/>
+      <c r="Z210" s="14" t="inlineStr"/>
+      <c r="AA210" s="14" t="inlineStr"/>
+      <c r="AB210" s="14" t="inlineStr"/>
+      <c r="AC210" s="14" t="inlineStr"/>
+      <c r="AD210" s="14" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
         <v>29601.74</v>
       </c>
       <c r="AF210" s="14" t="n"/>
-      <c r="AG210" s="14" t="n">
-        <v>0.006433</v>
-      </c>
+      <c r="AG210" s="14" t="n"/>
       <c r="AH210" s="14" t="inlineStr"/>
       <c r="AI210" s="14" t="inlineStr">
         <is>
@@ -30759,7 +29933,7 @@
       </c>
       <c r="AP210" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ210" s="14" t="inlineStr"/>
@@ -30782,12 +29956,12 @@
       </c>
       <c r="AW210" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AX210" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX210" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -30830,12 +30004,8 @@
       <c r="L211" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M211" s="14" t="n">
-        <v>4319702.7438</v>
-      </c>
-      <c r="N211" s="14" t="n">
-        <v>81967794</v>
-      </c>
+      <c r="M211" s="14" t="inlineStr"/>
+      <c r="N211" s="14" t="inlineStr"/>
       <c r="O211" s="14" t="b">
         <v>1</v>
       </c>
@@ -30855,40 +30025,20 @@
       <c r="U211" s="14" t="n">
         <v>0.46</v>
       </c>
-      <c r="V211" s="14" t="n">
-        <v>0.2984</v>
-      </c>
-      <c r="W211" s="14" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="X211" s="14" t="n">
-        <v>1.7895</v>
-      </c>
-      <c r="Y211" s="14" t="n">
-        <v>-3.46</v>
-      </c>
-      <c r="Z211" s="14" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="AA211" s="14" t="n">
-        <v>1.2573</v>
-      </c>
-      <c r="AB211" s="14" t="n">
-        <v>4.2138</v>
-      </c>
-      <c r="AC211" s="14" t="n">
-        <v>3.5475</v>
-      </c>
-      <c r="AD211" s="14" t="n">
-        <v>0.9358800562021976</v>
-      </c>
+      <c r="V211" s="14" t="inlineStr"/>
+      <c r="W211" s="14" t="inlineStr"/>
+      <c r="X211" s="14" t="inlineStr"/>
+      <c r="Y211" s="14" t="inlineStr"/>
+      <c r="Z211" s="14" t="inlineStr"/>
+      <c r="AA211" s="14" t="inlineStr"/>
+      <c r="AB211" s="14" t="inlineStr"/>
+      <c r="AC211" s="14" t="inlineStr"/>
+      <c r="AD211" s="14" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
         <v>32022.5</v>
       </c>
       <c r="AF211" s="14" t="n"/>
-      <c r="AG211" s="14" t="n">
-        <v>0.007413</v>
-      </c>
+      <c r="AG211" s="14" t="n"/>
       <c r="AH211" s="14" t="inlineStr"/>
       <c r="AI211" s="14" t="inlineStr">
         <is>
@@ -30923,7 +30073,7 @@
       </c>
       <c r="AP211" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ211" s="14" t="inlineStr"/>
@@ -30946,7 +30096,7 @@
       </c>
       <c r="AW211" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX211" s="14" t="inlineStr">
@@ -31015,39 +30165,19 @@
       <c r="S212" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T212" s="14" t="n">
-        <v>1.046</v>
-      </c>
+      <c r="T212" s="14" t="inlineStr"/>
       <c r="U212" s="14" t="n">
         <v>1.27</v>
       </c>
-      <c r="V212" s="14" t="n">
-        <v>0.3034</v>
-      </c>
-      <c r="W212" s="14" t="n">
-        <v>0.3007</v>
-      </c>
-      <c r="X212" s="14" t="n">
-        <v>1.6962</v>
-      </c>
-      <c r="Y212" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Z212" s="14" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="AA212" s="14" t="n">
-        <v>1.301</v>
-      </c>
-      <c r="AB212" s="14" t="n">
-        <v>4.2882</v>
-      </c>
-      <c r="AC212" s="14" t="n">
-        <v>3.4783</v>
-      </c>
-      <c r="AD212" s="14" t="n">
-        <v>0.926058610223794</v>
-      </c>
+      <c r="V212" s="14" t="inlineStr"/>
+      <c r="W212" s="14" t="inlineStr"/>
+      <c r="X212" s="14" t="inlineStr"/>
+      <c r="Y212" s="14" t="inlineStr"/>
+      <c r="Z212" s="14" t="inlineStr"/>
+      <c r="AA212" s="14" t="inlineStr"/>
+      <c r="AB212" s="14" t="inlineStr"/>
+      <c r="AC212" s="14" t="inlineStr"/>
+      <c r="AD212" s="14" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
         <v>95765.56</v>
       </c>
@@ -31089,7 +30219,7 @@
       </c>
       <c r="AP212" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ212" s="14" t="inlineStr"/>
@@ -31112,7 +30242,7 @@
       </c>
       <c r="AW212" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX212" s="14" t="inlineStr">
@@ -31181,39 +30311,19 @@
       <c r="S213" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T213" s="14" t="n">
-        <v>0.978</v>
-      </c>
+      <c r="T213" s="14" t="inlineStr"/>
       <c r="U213" s="14" t="n">
         <v>0.52</v>
       </c>
-      <c r="V213" s="14" t="n">
-        <v>0.3161</v>
-      </c>
-      <c r="W213" s="14" t="n">
-        <v>0.3059</v>
-      </c>
-      <c r="X213" s="14" t="n">
-        <v>1.5198</v>
-      </c>
-      <c r="Y213" s="14" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Z213" s="14" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="AA213" s="14" t="n">
-        <v>1.331</v>
-      </c>
-      <c r="AB213" s="14" t="n">
-        <v>4.211</v>
-      </c>
-      <c r="AC213" s="14" t="n">
-        <v>3.3687</v>
-      </c>
-      <c r="AD213" s="14" t="n">
-        <v>0.9353820249988504</v>
-      </c>
+      <c r="V213" s="14" t="inlineStr"/>
+      <c r="W213" s="14" t="inlineStr"/>
+      <c r="X213" s="14" t="inlineStr"/>
+      <c r="Y213" s="14" t="inlineStr"/>
+      <c r="Z213" s="14" t="inlineStr"/>
+      <c r="AA213" s="14" t="inlineStr"/>
+      <c r="AB213" s="14" t="inlineStr"/>
+      <c r="AC213" s="14" t="inlineStr"/>
+      <c r="AD213" s="14" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
         <v>53425.59</v>
       </c>
@@ -31255,7 +30365,7 @@
       </c>
       <c r="AP213" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ213" s="14" t="inlineStr"/>
@@ -31278,7 +30388,7 @@
       </c>
       <c r="AW213" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX213" s="14" t="inlineStr">
@@ -31347,39 +30457,19 @@
       <c r="S214" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T214" s="14" t="n">
-        <v>0.977</v>
-      </c>
+      <c r="T214" s="14" t="inlineStr"/>
       <c r="U214" s="14" t="n">
         <v>0.55</v>
       </c>
-      <c r="V214" s="14" t="n">
-        <v>0.2847</v>
-      </c>
-      <c r="W214" s="14" t="n">
-        <v>0.3009</v>
-      </c>
-      <c r="X214" s="14" t="n">
-        <v>1.1756</v>
-      </c>
-      <c r="Y214" s="14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Z214" s="14" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="AA214" s="14" t="n">
-        <v>1.3032</v>
-      </c>
-      <c r="AB214" s="14" t="n">
-        <v>4.5772</v>
-      </c>
-      <c r="AC214" s="14" t="n">
-        <v>3.787</v>
-      </c>
-      <c r="AD214" s="14" t="n">
-        <v>1.009504528995584</v>
-      </c>
+      <c r="V214" s="14" t="inlineStr"/>
+      <c r="W214" s="14" t="inlineStr"/>
+      <c r="X214" s="14" t="inlineStr"/>
+      <c r="Y214" s="14" t="inlineStr"/>
+      <c r="Z214" s="14" t="inlineStr"/>
+      <c r="AA214" s="14" t="inlineStr"/>
+      <c r="AB214" s="14" t="inlineStr"/>
+      <c r="AC214" s="14" t="inlineStr"/>
+      <c r="AD214" s="14" t="inlineStr"/>
       <c r="AE214" s="14" t="n">
         <v>44008.16</v>
       </c>
@@ -31421,12 +30511,10 @@
       </c>
       <c r="AP214" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
-        </is>
-      </c>
-      <c r="AQ214" s="14" t="n">
-        <v>0.3453</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ214" s="14" t="inlineStr"/>
       <c r="AR214" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -31446,7 +30534,7 @@
       </c>
       <c r="AW214" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX214" s="14" t="inlineStr">
@@ -31515,39 +30603,19 @@
       <c r="S215" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T215" s="14" t="n">
-        <v>1.013</v>
-      </c>
+      <c r="T215" s="14" t="inlineStr"/>
       <c r="U215" s="14" t="n">
         <v>0.46</v>
       </c>
-      <c r="V215" s="14" t="n">
-        <v>0.2814</v>
-      </c>
-      <c r="W215" s="14" t="n">
-        <v>0.2933</v>
-      </c>
-      <c r="X215" s="14" t="n">
-        <v>1.1386</v>
-      </c>
-      <c r="Y215" s="14" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="Z215" s="14" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="AA215" s="14" t="n">
-        <v>1.3434</v>
-      </c>
-      <c r="AB215" s="14" t="n">
-        <v>4.7737</v>
-      </c>
-      <c r="AC215" s="14" t="n">
-        <v>4.1894</v>
-      </c>
-      <c r="AD215" s="14" t="n">
-        <v>0.9791226188321752</v>
-      </c>
+      <c r="V215" s="14" t="inlineStr"/>
+      <c r="W215" s="14" t="inlineStr"/>
+      <c r="X215" s="14" t="inlineStr"/>
+      <c r="Y215" s="14" t="inlineStr"/>
+      <c r="Z215" s="14" t="inlineStr"/>
+      <c r="AA215" s="14" t="inlineStr"/>
+      <c r="AB215" s="14" t="inlineStr"/>
+      <c r="AC215" s="14" t="inlineStr"/>
+      <c r="AD215" s="14" t="inlineStr"/>
       <c r="AE215" s="14" t="n">
         <v>11469.32</v>
       </c>
@@ -31589,12 +30657,10 @@
       </c>
       <c r="AP215" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
-        </is>
-      </c>
-      <c r="AQ215" s="14" t="n">
-        <v>0.5494</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ215" s="14" t="inlineStr"/>
       <c r="AR215" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -31614,7 +30680,7 @@
       </c>
       <c r="AW215" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX215" s="14" t="inlineStr">
@@ -31683,39 +30749,19 @@
       <c r="S216" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T216" s="14" t="n">
-        <v>1.006</v>
-      </c>
+      <c r="T216" s="14" t="inlineStr"/>
       <c r="U216" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="V216" s="14" t="n">
-        <v>0.2878</v>
-      </c>
-      <c r="W216" s="14" t="n">
-        <v>0.2848</v>
-      </c>
-      <c r="X216" s="14" t="n">
-        <v>1.3107</v>
-      </c>
-      <c r="Y216" s="14" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="Z216" s="14" t="n">
-        <v>26.84</v>
-      </c>
-      <c r="AA216" s="14" t="n">
-        <v>1.5374</v>
-      </c>
-      <c r="AB216" s="14" t="n">
-        <v>5.3412</v>
-      </c>
-      <c r="AC216" s="14" t="n">
-        <v>4.6497</v>
-      </c>
-      <c r="AD216" s="14" t="n">
-        <v>0.948862942852872</v>
-      </c>
+      <c r="V216" s="14" t="inlineStr"/>
+      <c r="W216" s="14" t="inlineStr"/>
+      <c r="X216" s="14" t="inlineStr"/>
+      <c r="Y216" s="14" t="inlineStr"/>
+      <c r="Z216" s="14" t="inlineStr"/>
+      <c r="AA216" s="14" t="inlineStr"/>
+      <c r="AB216" s="14" t="inlineStr"/>
+      <c r="AC216" s="14" t="inlineStr"/>
+      <c r="AD216" s="14" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
         <v>30876.93</v>
       </c>
@@ -31757,12 +30803,10 @@
       </c>
       <c r="AP216" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
-        </is>
-      </c>
-      <c r="AQ216" s="14" t="n">
-        <v>0.5601</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ216" s="14" t="inlineStr"/>
       <c r="AR216" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -31782,7 +30826,7 @@
       </c>
       <c r="AW216" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX216" s="14" t="inlineStr">
@@ -31851,9 +30895,7 @@
       <c r="S217" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T217" s="14" t="n">
-        <v>1.003</v>
-      </c>
+      <c r="T217" s="14" t="inlineStr"/>
       <c r="U217" s="14" t="n">
         <v>0.6</v>
       </c>
@@ -31907,12 +30949,10 @@
       </c>
       <c r="AP217" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
-        </is>
-      </c>
-      <c r="AQ217" s="14" t="n">
-        <v>0.5548999999999999</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ217" s="14" t="inlineStr"/>
       <c r="AR217" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -32001,9 +31041,7 @@
       <c r="S218" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T218" s="14" t="n">
-        <v>0.962</v>
-      </c>
+      <c r="T218" s="14" t="inlineStr"/>
       <c r="U218" s="14" t="n">
         <v>0.48</v>
       </c>
@@ -32057,12 +31095,10 @@
       </c>
       <c r="AP218" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
-        </is>
-      </c>
-      <c r="AQ218" s="14" t="n">
-        <v>0.2686</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ218" s="14" t="inlineStr"/>
       <c r="AR218" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -32152,7 +31188,7 @@
         <v>0</v>
       </c>
       <c r="T219" s="14" t="n">
-        <v>1.021</v>
+        <v>1.018</v>
       </c>
       <c r="U219" s="14" t="n">
         <v>0.4</v>
@@ -32207,12 +31243,10 @@
       </c>
       <c r="AP219" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
-        </is>
-      </c>
-      <c r="AQ219" s="14" t="n">
-        <v>0.6865</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ219" s="14" t="inlineStr"/>
       <c r="AR219" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -32302,32 +31336,20 @@
         <v>0</v>
       </c>
       <c r="T220" s="14" t="n">
-        <v>0.996</v>
+        <v>0.993</v>
       </c>
       <c r="U220" s="14" t="n">
         <v>0.91</v>
       </c>
-      <c r="V220" s="14" t="n">
-        <v>0.2396</v>
-      </c>
+      <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="inlineStr"/>
-      <c r="X220" s="14" t="n">
-        <v>1.3033</v>
-      </c>
+      <c r="X220" s="14" t="inlineStr"/>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="inlineStr"/>
-      <c r="AA220" s="14" t="n">
-        <v>1.5157</v>
-      </c>
-      <c r="AB220" s="14" t="n">
-        <v>6.326</v>
-      </c>
-      <c r="AC220" s="14" t="n">
-        <v>5.4599</v>
-      </c>
-      <c r="AD220" s="14" t="n">
-        <v>0.8959</v>
-      </c>
+      <c r="AA220" s="14" t="inlineStr"/>
+      <c r="AB220" s="14" t="inlineStr"/>
+      <c r="AC220" s="14" t="inlineStr"/>
+      <c r="AD220" s="14" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
         <v>22504.32</v>
       </c>
@@ -32369,12 +31391,10 @@
       </c>
       <c r="AP220" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
-        </is>
-      </c>
-      <c r="AQ220" s="14" t="n">
-        <v>0.5022</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ220" s="14" t="inlineStr"/>
       <c r="AR220" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -32464,32 +31484,20 @@
         <v>0</v>
       </c>
       <c r="T221" s="14" t="n">
-        <v>0.894</v>
+        <v>0.889</v>
       </c>
       <c r="U221" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="V221" s="14" t="n">
-        <v>0.2725</v>
-      </c>
+      <c r="V221" s="14" t="inlineStr"/>
       <c r="W221" s="14" t="inlineStr"/>
-      <c r="X221" s="14" t="n">
-        <v>1.1158</v>
-      </c>
+      <c r="X221" s="14" t="inlineStr"/>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="inlineStr"/>
-      <c r="AA221" s="14" t="n">
-        <v>1.5063</v>
-      </c>
-      <c r="AB221" s="14" t="n">
-        <v>5.5274</v>
-      </c>
-      <c r="AC221" s="14" t="n">
-        <v>5.1881</v>
-      </c>
-      <c r="AD221" s="14" t="n">
-        <v>0.9723000000000001</v>
-      </c>
+      <c r="AA221" s="14" t="inlineStr"/>
+      <c r="AB221" s="14" t="inlineStr"/>
+      <c r="AC221" s="14" t="inlineStr"/>
+      <c r="AD221" s="14" t="inlineStr"/>
       <c r="AE221" s="14" t="n">
         <v>58851.03</v>
       </c>
@@ -32531,7 +31539,7 @@
       </c>
       <c r="AP221" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ221" s="14" t="n">
@@ -32626,32 +31634,20 @@
         <v>0</v>
       </c>
       <c r="T222" s="14" t="n">
-        <v>0.909</v>
+        <v>0.907</v>
       </c>
       <c r="U222" s="14" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="V222" s="14" t="n">
-        <v>0.2331</v>
-      </c>
-      <c r="W222" s="14" t="n">
-        <v>0.2476</v>
-      </c>
+      <c r="V222" s="14" t="inlineStr"/>
+      <c r="W222" s="14" t="inlineStr"/>
       <c r="X222" s="14" t="inlineStr"/>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="inlineStr"/>
-      <c r="AA222" s="14" t="n">
-        <v>1.4063</v>
-      </c>
-      <c r="AB222" s="14" t="n">
-        <v>6.0323</v>
-      </c>
-      <c r="AC222" s="14" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="AD222" s="14" t="n">
-        <v>0.8143</v>
-      </c>
+      <c r="AA222" s="14" t="inlineStr"/>
+      <c r="AB222" s="14" t="inlineStr"/>
+      <c r="AC222" s="14" t="inlineStr"/>
+      <c r="AD222" s="14" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
         <v>13101.86</v>
       </c>
@@ -32693,11 +31689,11 @@
       </c>
       <c r="AP222" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ222" s="14" t="n">
-        <v>0.0912</v>
+        <v>0.1027</v>
       </c>
       <c r="AR222" s="14" t="inlineStr">
         <is>
@@ -32718,12 +31714,12 @@
       </c>
       <c r="AW222" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AX222" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX222" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -32793,31 +31789,15 @@
       <c r="U223" s="14" t="n">
         <v>0.67</v>
       </c>
-      <c r="V223" s="14" t="n">
-        <v>0.2379</v>
-      </c>
-      <c r="W223" s="14" t="n">
-        <v>0.2471</v>
-      </c>
+      <c r="V223" s="14" t="inlineStr"/>
+      <c r="W223" s="14" t="inlineStr"/>
       <c r="X223" s="14" t="inlineStr"/>
-      <c r="Y223" s="14" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="Z223" s="14" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="AA223" s="14" t="n">
-        <v>1.4389</v>
-      </c>
-      <c r="AB223" s="14" t="n">
-        <v>6.0472</v>
-      </c>
-      <c r="AC223" s="14" t="n">
-        <v>5.8074</v>
-      </c>
-      <c r="AD223" s="14" t="n">
-        <v>1.059</v>
-      </c>
+      <c r="Y223" s="14" t="inlineStr"/>
+      <c r="Z223" s="14" t="inlineStr"/>
+      <c r="AA223" s="14" t="inlineStr"/>
+      <c r="AB223" s="14" t="inlineStr"/>
+      <c r="AC223" s="14" t="inlineStr"/>
+      <c r="AD223" s="14" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
         <v>36979.92</v>
       </c>
@@ -32859,7 +31839,7 @@
       </c>
       <c r="AP223" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ223" s="14" t="n">
@@ -32884,7 +31864,7 @@
       </c>
       <c r="AW223" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX223" s="14" t="inlineStr">
@@ -32954,36 +31934,20 @@
         <v>0</v>
       </c>
       <c r="T224" s="14" t="n">
-        <v>0.898</v>
+        <v>0.905</v>
       </c>
       <c r="U224" s="14" t="n">
         <v>0.71</v>
       </c>
-      <c r="V224" s="14" t="n">
-        <v>0.2261</v>
-      </c>
-      <c r="W224" s="14" t="n">
-        <v>0.2324</v>
-      </c>
+      <c r="V224" s="14" t="inlineStr"/>
+      <c r="W224" s="14" t="inlineStr"/>
       <c r="X224" s="14" t="inlineStr"/>
-      <c r="Y224" s="14" t="n">
-        <v>-8.27</v>
-      </c>
-      <c r="Z224" s="14" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="AA224" s="14" t="n">
-        <v>1.3818</v>
-      </c>
-      <c r="AB224" s="14" t="n">
-        <v>6.1124</v>
-      </c>
-      <c r="AC224" s="14" t="n">
-        <v>5.9348</v>
-      </c>
-      <c r="AD224" s="14" t="n">
-        <v>0.9112</v>
-      </c>
+      <c r="Y224" s="14" t="inlineStr"/>
+      <c r="Z224" s="14" t="inlineStr"/>
+      <c r="AA224" s="14" t="inlineStr"/>
+      <c r="AB224" s="14" t="inlineStr"/>
+      <c r="AC224" s="14" t="inlineStr"/>
+      <c r="AD224" s="14" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
         <v>14252.88</v>
       </c>
@@ -33025,11 +31989,11 @@
       </c>
       <c r="AP224" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ224" s="14" t="n">
-        <v>0.0723</v>
+        <v>0.0809</v>
       </c>
       <c r="AR224" s="14" t="inlineStr">
         <is>
@@ -33050,7 +32014,7 @@
       </c>
       <c r="AW224" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX224" s="14" t="inlineStr">
@@ -33120,38 +32084,20 @@
         <v>0</v>
       </c>
       <c r="T225" s="14" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.945</v>
       </c>
       <c r="U225" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="V225" s="14" t="n">
-        <v>0.2282</v>
-      </c>
-      <c r="W225" s="14" t="n">
-        <v>0.2307</v>
-      </c>
-      <c r="X225" s="14" t="n">
-        <v>1.056</v>
-      </c>
-      <c r="Y225" s="14" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="Z225" s="14" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="AA225" s="14" t="n">
-        <v>1.3662</v>
-      </c>
-      <c r="AB225" s="14" t="n">
-        <v>5.9881</v>
-      </c>
-      <c r="AC225" s="14" t="n">
-        <v>5.7659</v>
-      </c>
-      <c r="AD225" s="14" t="n">
-        <v>0.7979000000000001</v>
-      </c>
+      <c r="V225" s="14" t="inlineStr"/>
+      <c r="W225" s="14" t="inlineStr"/>
+      <c r="X225" s="14" t="inlineStr"/>
+      <c r="Y225" s="14" t="inlineStr"/>
+      <c r="Z225" s="14" t="inlineStr"/>
+      <c r="AA225" s="14" t="inlineStr"/>
+      <c r="AB225" s="14" t="inlineStr"/>
+      <c r="AC225" s="14" t="inlineStr"/>
+      <c r="AD225" s="14" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
         <v>11130.76</v>
       </c>
@@ -33193,11 +32139,11 @@
       </c>
       <c r="AP225" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ225" s="14" t="n">
-        <v>0.2486</v>
+        <v>0.2781</v>
       </c>
       <c r="AR225" s="14" t="inlineStr">
         <is>
@@ -33218,7 +32164,7 @@
       </c>
       <c r="AW225" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX225" s="14" t="inlineStr">
@@ -33293,33 +32239,15 @@
       <c r="U226" s="14" t="n">
         <v>1.08</v>
       </c>
-      <c r="V226" s="14" t="n">
-        <v>0.2211</v>
-      </c>
-      <c r="W226" s="14" t="n">
-        <v>0.2251</v>
-      </c>
-      <c r="X226" s="14" t="n">
-        <v>1.1247</v>
-      </c>
-      <c r="Y226" s="14" t="n">
-        <v>-7.67</v>
-      </c>
-      <c r="Z226" s="14" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="AA226" s="14" t="n">
-        <v>1.3286</v>
-      </c>
-      <c r="AB226" s="14" t="n">
-        <v>6.0077</v>
-      </c>
-      <c r="AC226" s="14" t="n">
-        <v>5.8353</v>
-      </c>
-      <c r="AD226" s="14" t="n">
-        <v>0.8895</v>
-      </c>
+      <c r="V226" s="14" t="inlineStr"/>
+      <c r="W226" s="14" t="inlineStr"/>
+      <c r="X226" s="14" t="inlineStr"/>
+      <c r="Y226" s="14" t="inlineStr"/>
+      <c r="Z226" s="14" t="inlineStr"/>
+      <c r="AA226" s="14" t="inlineStr"/>
+      <c r="AB226" s="14" t="inlineStr"/>
+      <c r="AC226" s="14" t="inlineStr"/>
+      <c r="AD226" s="14" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
         <v>38621.3</v>
       </c>
@@ -33361,11 +32289,11 @@
       </c>
       <c r="AP226" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ226" s="14" t="n">
-        <v>0.1238</v>
+        <v>0.1385</v>
       </c>
       <c r="AR226" s="14" t="inlineStr">
         <is>
@@ -33386,7 +32314,7 @@
       </c>
       <c r="AW226" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX226" s="14" t="inlineStr">
@@ -33461,33 +32389,15 @@
       <c r="U227" s="14" t="n">
         <v>1.27</v>
       </c>
-      <c r="V227" s="14" t="n">
-        <v>0.2505</v>
-      </c>
-      <c r="W227" s="14" t="n">
-        <v>0.2325</v>
-      </c>
-      <c r="X227" s="14" t="n">
-        <v>0.8801</v>
-      </c>
-      <c r="Y227" s="14" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="Z227" s="14" t="n">
-        <v>-13.66</v>
-      </c>
-      <c r="AA227" s="14" t="n">
-        <v>1.3219</v>
-      </c>
-      <c r="AB227" s="14" t="n">
-        <v>5.2775</v>
-      </c>
-      <c r="AC227" s="14" t="n">
-        <v>5.2189</v>
-      </c>
-      <c r="AD227" s="14" t="n">
-        <v>0.8398</v>
-      </c>
+      <c r="V227" s="14" t="inlineStr"/>
+      <c r="W227" s="14" t="inlineStr"/>
+      <c r="X227" s="14" t="inlineStr"/>
+      <c r="Y227" s="14" t="inlineStr"/>
+      <c r="Z227" s="14" t="inlineStr"/>
+      <c r="AA227" s="14" t="inlineStr"/>
+      <c r="AB227" s="14" t="inlineStr"/>
+      <c r="AC227" s="14" t="inlineStr"/>
+      <c r="AD227" s="14" t="inlineStr"/>
       <c r="AE227" s="14" t="n">
         <v>23900.05</v>
       </c>
@@ -33529,11 +32439,11 @@
       </c>
       <c r="AP227" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ227" s="14" t="n">
-        <v>0.1342</v>
+        <v>0.1501</v>
       </c>
       <c r="AR227" s="14" t="inlineStr">
         <is>
@@ -33554,7 +32464,7 @@
       </c>
       <c r="AW227" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX227" s="14" t="inlineStr">
@@ -33629,33 +32539,15 @@
       <c r="U228" s="14" t="n">
         <v>1.85</v>
       </c>
-      <c r="V228" s="14" t="n">
-        <v>0.2335</v>
-      </c>
-      <c r="W228" s="14" t="n">
-        <v>0.2344</v>
-      </c>
-      <c r="X228" s="14" t="n">
-        <v>0.9108000000000001</v>
-      </c>
-      <c r="Y228" s="14" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="Z228" s="14" t="n">
-        <v>-7.34</v>
-      </c>
-      <c r="AA228" s="14" t="n">
-        <v>1.2955</v>
-      </c>
-      <c r="AB228" s="14" t="n">
-        <v>5.5488</v>
-      </c>
-      <c r="AC228" s="14" t="n">
-        <v>5.2893</v>
-      </c>
-      <c r="AD228" s="14" t="n">
-        <v>0.8413</v>
-      </c>
+      <c r="V228" s="14" t="inlineStr"/>
+      <c r="W228" s="14" t="inlineStr"/>
+      <c r="X228" s="14" t="inlineStr"/>
+      <c r="Y228" s="14" t="inlineStr"/>
+      <c r="Z228" s="14" t="inlineStr"/>
+      <c r="AA228" s="14" t="inlineStr"/>
+      <c r="AB228" s="14" t="inlineStr"/>
+      <c r="AC228" s="14" t="inlineStr"/>
+      <c r="AD228" s="14" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
         <v>50956.47</v>
       </c>
@@ -33697,11 +32589,11 @@
       </c>
       <c r="AP228" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ228" s="14" t="n">
-        <v>0.1956</v>
+        <v>0.2188</v>
       </c>
       <c r="AR228" s="14" t="inlineStr">
         <is>
@@ -33722,12 +32614,12 @@
       </c>
       <c r="AW228" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AX228" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX228" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -33797,33 +32689,15 @@
       <c r="U229" s="14" t="n">
         <v>3.05</v>
       </c>
-      <c r="V229" s="14" t="n">
-        <v>0.2451</v>
-      </c>
-      <c r="W229" s="14" t="n">
-        <v>0.2429</v>
-      </c>
-      <c r="X229" s="14" t="n">
-        <v>0.8303</v>
-      </c>
-      <c r="Y229" s="14" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="Z229" s="14" t="n">
-        <v>-10.62</v>
-      </c>
-      <c r="AA229" s="14" t="n">
-        <v>1.3158</v>
-      </c>
-      <c r="AB229" s="14" t="n">
-        <v>5.3694</v>
-      </c>
-      <c r="AC229" s="14" t="n">
-        <v>4.9277</v>
-      </c>
-      <c r="AD229" s="14" t="n">
-        <v>0.8472</v>
-      </c>
+      <c r="V229" s="14" t="inlineStr"/>
+      <c r="W229" s="14" t="inlineStr"/>
+      <c r="X229" s="14" t="inlineStr"/>
+      <c r="Y229" s="14" t="inlineStr"/>
+      <c r="Z229" s="14" t="inlineStr"/>
+      <c r="AA229" s="14" t="inlineStr"/>
+      <c r="AB229" s="14" t="inlineStr"/>
+      <c r="AC229" s="14" t="inlineStr"/>
+      <c r="AD229" s="14" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
         <v>77532.52</v>
       </c>
@@ -33865,7 +32739,7 @@
       </c>
       <c r="AP229" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ229" s="14" t="n">
@@ -33890,7 +32764,7 @@
       </c>
       <c r="AW229" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX229" s="14" t="inlineStr">
@@ -33965,33 +32839,15 @@
       <c r="U230" s="14" t="n">
         <v>4.07</v>
       </c>
-      <c r="V230" s="14" t="n">
-        <v>0.3928</v>
-      </c>
-      <c r="W230" s="14" t="n">
-        <v>0.2764</v>
-      </c>
-      <c r="X230" s="14" t="n">
-        <v>0.5974</v>
-      </c>
-      <c r="Y230" s="14" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="Z230" s="14" t="n">
-        <v>-33.71</v>
-      </c>
-      <c r="AA230" s="14" t="n">
-        <v>1.374</v>
-      </c>
-      <c r="AB230" s="14" t="n">
-        <v>3.4984</v>
-      </c>
-      <c r="AC230" s="14" t="n">
-        <v>3.4444</v>
-      </c>
-      <c r="AD230" s="14" t="n">
-        <v>0.7574</v>
-      </c>
+      <c r="V230" s="14" t="inlineStr"/>
+      <c r="W230" s="14" t="inlineStr"/>
+      <c r="X230" s="14" t="inlineStr"/>
+      <c r="Y230" s="14" t="inlineStr"/>
+      <c r="Z230" s="14" t="inlineStr"/>
+      <c r="AA230" s="14" t="inlineStr"/>
+      <c r="AB230" s="14" t="inlineStr"/>
+      <c r="AC230" s="14" t="inlineStr"/>
+      <c r="AD230" s="14" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
         <v>114272.26</v>
       </c>
@@ -34033,11 +32889,11 @@
       </c>
       <c r="AP230" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ230" s="14" t="n">
-        <v>0.7181</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="AR230" s="14" t="inlineStr">
         <is>
@@ -34058,7 +32914,7 @@
       </c>
       <c r="AW230" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX230" s="14" t="inlineStr">
@@ -34133,33 +32989,15 @@
       <c r="U231" s="14" t="n">
         <v>7.49</v>
       </c>
-      <c r="V231" s="14" t="n">
-        <v>0.4412</v>
-      </c>
-      <c r="W231" s="14" t="n">
-        <v>0.3361</v>
-      </c>
-      <c r="X231" s="14" t="n">
-        <v>0.4926</v>
-      </c>
-      <c r="Y231" s="14" t="n">
-        <v>-5.88</v>
-      </c>
-      <c r="Z231" s="14" t="n">
-        <v>-50.19</v>
-      </c>
-      <c r="AA231" s="14" t="n">
-        <v>1.2193</v>
-      </c>
-      <c r="AB231" s="14" t="n">
-        <v>2.7636</v>
-      </c>
-      <c r="AC231" s="14" t="n">
-        <v>2.8745</v>
-      </c>
-      <c r="AD231" s="14" t="n">
-        <v>0.7357</v>
-      </c>
+      <c r="V231" s="14" t="inlineStr"/>
+      <c r="W231" s="14" t="inlineStr"/>
+      <c r="X231" s="14" t="inlineStr"/>
+      <c r="Y231" s="14" t="inlineStr"/>
+      <c r="Z231" s="14" t="inlineStr"/>
+      <c r="AA231" s="14" t="inlineStr"/>
+      <c r="AB231" s="14" t="inlineStr"/>
+      <c r="AC231" s="14" t="inlineStr"/>
+      <c r="AD231" s="14" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
         <v>259988.49</v>
       </c>
@@ -34201,11 +33039,11 @@
       </c>
       <c r="AP231" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ231" s="14" t="n">
-        <v>0.2407</v>
+        <v>0.2674</v>
       </c>
       <c r="AR231" s="14" t="inlineStr">
         <is>
@@ -34226,7 +33064,7 @@
       </c>
       <c r="AW231" s="14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>false</t>
         </is>
       </c>
       <c r="AX231" s="14" t="inlineStr">
@@ -34351,7 +33189,7 @@
       </c>
       <c r="AP232" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ232" s="14" t="n">
@@ -34501,7 +33339,7 @@
       </c>
       <c r="AP233" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ233" s="14" t="n">
@@ -34530,6 +33368,1042 @@
         </is>
       </c>
       <c r="AX233" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B234" s="14" t="n">
+        <v>0.05895333</v>
+      </c>
+      <c r="C234" s="14" t="n">
+        <v>0.03759</v>
+      </c>
+      <c r="D234" s="14" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="E234" s="14" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="F234" s="14" t="n">
+        <v>0.06365999999999999</v>
+      </c>
+      <c r="G234" s="14" t="n">
+        <v>180568553.24</v>
+      </c>
+      <c r="H234" s="14" t="inlineStr"/>
+      <c r="I234" s="14" t="n">
+        <v>0.00102893</v>
+      </c>
+      <c r="J234" s="14" t="n">
+        <v>0.0008258300000000001</v>
+      </c>
+      <c r="K234" s="14" t="n">
+        <v>0.00115317</v>
+      </c>
+      <c r="L234" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M234" s="14" t="n">
+        <v>5432446.87396</v>
+      </c>
+      <c r="N234" s="14" t="n">
+        <v>144556862</v>
+      </c>
+      <c r="O234" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P234" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q234" s="14" t="n">
+        <v>69.39861629000001</v>
+      </c>
+      <c r="R234" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T234" s="14" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="U234" s="14" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="V234" s="14" t="inlineStr"/>
+      <c r="W234" s="14" t="inlineStr"/>
+      <c r="X234" s="14" t="inlineStr"/>
+      <c r="Y234" s="14" t="inlineStr"/>
+      <c r="Z234" s="14" t="inlineStr"/>
+      <c r="AA234" s="14" t="inlineStr"/>
+      <c r="AB234" s="14" t="inlineStr"/>
+      <c r="AC234" s="14" t="inlineStr"/>
+      <c r="AD234" s="14" t="inlineStr"/>
+      <c r="AE234" s="14" t="n">
+        <v>2894411.87</v>
+      </c>
+      <c r="AF234" s="14" t="n"/>
+      <c r="AG234" s="14" t="n">
+        <v>0.532801</v>
+      </c>
+      <c r="AH234" s="14" t="inlineStr"/>
+      <c r="AI234" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ234" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK234" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL234" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM234" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN234" s="14" t="inlineStr"/>
+      <c r="AO234" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP234" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ234" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR234" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS234" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT234" s="14" t="inlineStr"/>
+      <c r="AU234" s="14" t="inlineStr"/>
+      <c r="AV234" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW234" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX234" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B235" s="14" t="n">
+        <v>0.05265333</v>
+      </c>
+      <c r="C235" s="14" t="n">
+        <v>0.06371</v>
+      </c>
+      <c r="D235" s="14" t="n">
+        <v>0.06622</v>
+      </c>
+      <c r="E235" s="14" t="n">
+        <v>0.04449</v>
+      </c>
+      <c r="F235" s="14" t="n">
+        <v>0.04725</v>
+      </c>
+      <c r="G235" s="14" t="n">
+        <v>61111916.15</v>
+      </c>
+      <c r="H235" s="14" t="inlineStr"/>
+      <c r="I235" s="14" t="n">
+        <v>0.00030027</v>
+      </c>
+      <c r="J235" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K235" s="14" t="n">
+        <v>0.00094067</v>
+      </c>
+      <c r="L235" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M235" s="14" t="n">
+        <v>10271802.6796</v>
+      </c>
+      <c r="N235" s="14" t="n">
+        <v>161000042</v>
+      </c>
+      <c r="O235" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P235" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q235" s="14" t="n">
+        <v>-25.77756833</v>
+      </c>
+      <c r="R235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T235" s="14" t="n">
+        <v>2.602</v>
+      </c>
+      <c r="U235" s="14" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="V235" s="14" t="inlineStr"/>
+      <c r="W235" s="14" t="inlineStr"/>
+      <c r="X235" s="14" t="inlineStr"/>
+      <c r="Y235" s="14" t="inlineStr"/>
+      <c r="Z235" s="14" t="inlineStr"/>
+      <c r="AA235" s="14" t="inlineStr"/>
+      <c r="AB235" s="14" t="inlineStr"/>
+      <c r="AC235" s="14" t="inlineStr"/>
+      <c r="AD235" s="14" t="inlineStr"/>
+      <c r="AE235" s="14" t="n">
+        <v>1299216.09</v>
+      </c>
+      <c r="AF235" s="14" t="n"/>
+      <c r="AG235" s="14" t="n">
+        <v>0.126484</v>
+      </c>
+      <c r="AH235" s="14" t="inlineStr"/>
+      <c r="AI235" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ235" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK235" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL235" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM235" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN235" s="14" t="inlineStr"/>
+      <c r="AO235" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP235" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ235" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR235" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS235" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT235" s="14" t="inlineStr"/>
+      <c r="AU235" s="14" t="inlineStr"/>
+      <c r="AV235" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW235" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX235" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B236" s="14" t="n">
+        <v>0.05002</v>
+      </c>
+      <c r="C236" s="14" t="n">
+        <v>0.04725</v>
+      </c>
+      <c r="D236" s="14" t="n">
+        <v>0.05563</v>
+      </c>
+      <c r="E236" s="14" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="F236" s="14" t="n">
+        <v>0.05104</v>
+      </c>
+      <c r="G236" s="14" t="n">
+        <v>14995370.24</v>
+      </c>
+      <c r="H236" s="14" t="inlineStr"/>
+      <c r="I236" s="14" t="n">
+        <v>7.608e-05</v>
+      </c>
+      <c r="J236" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K236" s="14" t="n">
+        <v>0.00011297</v>
+      </c>
+      <c r="L236" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M236" s="14" t="n">
+        <v>6908277.8188088</v>
+      </c>
+      <c r="N236" s="14" t="n">
+        <v>146211920</v>
+      </c>
+      <c r="O236" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P236" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q236" s="14" t="n">
+        <v>8.021164020000001</v>
+      </c>
+      <c r="R236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T236" s="14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U236" s="14" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="V236" s="14" t="inlineStr"/>
+      <c r="W236" s="14" t="inlineStr"/>
+      <c r="X236" s="14" t="inlineStr"/>
+      <c r="Y236" s="14" t="inlineStr"/>
+      <c r="Z236" s="14" t="inlineStr"/>
+      <c r="AA236" s="14" t="inlineStr"/>
+      <c r="AB236" s="14" t="inlineStr"/>
+      <c r="AC236" s="14" t="inlineStr"/>
+      <c r="AD236" s="14" t="inlineStr"/>
+      <c r="AE236" s="14" t="n">
+        <v>820699.12</v>
+      </c>
+      <c r="AF236" s="14" t="n"/>
+      <c r="AG236" s="14" t="n">
+        <v>0.118799</v>
+      </c>
+      <c r="AH236" s="14" t="inlineStr"/>
+      <c r="AI236" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ236" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK236" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL236" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM236" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN236" s="14" t="inlineStr"/>
+      <c r="AO236" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP236" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ236" s="14" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="AR236" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS236" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT236" s="14" t="inlineStr"/>
+      <c r="AU236" s="14" t="inlineStr"/>
+      <c r="AV236" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW236" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX236" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B237" s="14" t="n">
+        <v>0.04727667</v>
+      </c>
+      <c r="C237" s="14" t="n">
+        <v>0.05099</v>
+      </c>
+      <c r="D237" s="14" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="E237" s="14" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="F237" s="14" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="G237" s="14" t="n">
+        <v>5049679.38</v>
+      </c>
+      <c r="H237" s="14" t="inlineStr"/>
+      <c r="I237" s="14" t="n">
+        <v>0.00016883</v>
+      </c>
+      <c r="J237" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K237" s="14" t="n">
+        <v>0.00036302</v>
+      </c>
+      <c r="L237" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M237" s="14" t="n">
+        <v>7103478.31624928</v>
+      </c>
+      <c r="N237" s="14" t="n">
+        <v>139243699</v>
+      </c>
+      <c r="O237" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P237" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q237" s="14" t="n">
+        <v>-11.63793103</v>
+      </c>
+      <c r="R237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T237" s="14" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="U237" s="14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V237" s="14" t="inlineStr"/>
+      <c r="W237" s="14" t="inlineStr"/>
+      <c r="X237" s="14" t="inlineStr"/>
+      <c r="Y237" s="14" t="inlineStr"/>
+      <c r="Z237" s="14" t="inlineStr"/>
+      <c r="AA237" s="14" t="inlineStr"/>
+      <c r="AB237" s="14" t="inlineStr"/>
+      <c r="AC237" s="14" t="inlineStr"/>
+      <c r="AD237" s="14" t="inlineStr"/>
+      <c r="AE237" s="14" t="n">
+        <v>407637.62</v>
+      </c>
+      <c r="AF237" s="14" t="n"/>
+      <c r="AG237" s="14" t="n">
+        <v>0.057386</v>
+      </c>
+      <c r="AH237" s="14" t="inlineStr"/>
+      <c r="AI237" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ237" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK237" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL237" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM237" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN237" s="14" t="inlineStr"/>
+      <c r="AO237" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP237" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ237" s="14" t="n">
+        <v>0.5128</v>
+      </c>
+      <c r="AR237" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS237" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT237" s="14" t="inlineStr"/>
+      <c r="AU237" s="14" t="inlineStr"/>
+      <c r="AV237" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW237" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX237" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B238" s="14" t="n">
+        <v>0.04126667</v>
+      </c>
+      <c r="C238" s="14" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="D238" s="14" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="E238" s="14" t="n">
+        <v>0.03792</v>
+      </c>
+      <c r="F238" s="14" t="n">
+        <v>0.04038</v>
+      </c>
+      <c r="G238" s="14" t="n">
+        <v>4030883.67</v>
+      </c>
+      <c r="H238" s="14" t="inlineStr"/>
+      <c r="I238" s="14" t="n">
+        <v>0.00014848</v>
+      </c>
+      <c r="J238" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K238" s="14" t="n">
+        <v>0.00030069</v>
+      </c>
+      <c r="L238" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M238" s="14" t="n">
+        <v>5873695.0591</v>
+      </c>
+      <c r="N238" s="14" t="n">
+        <v>130237141</v>
+      </c>
+      <c r="O238" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P238" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q238" s="14" t="n">
+        <v>-10.46563193</v>
+      </c>
+      <c r="R238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T238" s="14" t="n">
+        <v>1.402</v>
+      </c>
+      <c r="U238" s="14" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="V238" s="14" t="inlineStr"/>
+      <c r="W238" s="14" t="inlineStr"/>
+      <c r="X238" s="14" t="inlineStr"/>
+      <c r="Y238" s="14" t="inlineStr"/>
+      <c r="Z238" s="14" t="inlineStr"/>
+      <c r="AA238" s="14" t="inlineStr"/>
+      <c r="AB238" s="14" t="inlineStr"/>
+      <c r="AC238" s="14" t="inlineStr"/>
+      <c r="AD238" s="14" t="inlineStr"/>
+      <c r="AE238" s="14" t="n">
+        <v>262020.9</v>
+      </c>
+      <c r="AF238" s="14" t="n"/>
+      <c r="AG238" s="14" t="n">
+        <v>0.044609</v>
+      </c>
+      <c r="AH238" s="14" t="inlineStr"/>
+      <c r="AI238" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ238" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK238" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL238" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM238" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN238" s="14" t="inlineStr"/>
+      <c r="AO238" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP238" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ238" s="14" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="AR238" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS238" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT238" s="14" t="inlineStr"/>
+      <c r="AU238" s="14" t="inlineStr"/>
+      <c r="AV238" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW238" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX238" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B239" s="14" t="n">
+        <v>0.04139667</v>
+      </c>
+      <c r="C239" s="14" t="n">
+        <v>0.04038</v>
+      </c>
+      <c r="D239" s="14" t="n">
+        <v>0.04286</v>
+      </c>
+      <c r="E239" s="14" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="F239" s="14" t="n">
+        <v>0.04154</v>
+      </c>
+      <c r="G239" s="14" t="n">
+        <v>2139960.6</v>
+      </c>
+      <c r="H239" s="14" t="inlineStr"/>
+      <c r="I239" s="14" t="n">
+        <v>0.0002513</v>
+      </c>
+      <c r="J239" s="14" t="n">
+        <v>6.063e-05</v>
+      </c>
+      <c r="K239" s="14" t="n">
+        <v>0.00047126</v>
+      </c>
+      <c r="L239" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M239" s="14" t="n">
+        <v>5339698.24056</v>
+      </c>
+      <c r="N239" s="14" t="n">
+        <v>132236212</v>
+      </c>
+      <c r="O239" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P239" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q239" s="14" t="n">
+        <v>2.87270926</v>
+      </c>
+      <c r="R239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T239" s="14" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="U239" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V239" s="14" t="inlineStr"/>
+      <c r="W239" s="14" t="inlineStr"/>
+      <c r="X239" s="14" t="inlineStr"/>
+      <c r="Y239" s="14" t="inlineStr"/>
+      <c r="Z239" s="14" t="inlineStr"/>
+      <c r="AA239" s="14" t="inlineStr"/>
+      <c r="AB239" s="14" t="inlineStr"/>
+      <c r="AC239" s="14" t="inlineStr"/>
+      <c r="AD239" s="14" t="inlineStr"/>
+      <c r="AE239" s="14" t="n">
+        <v>134566.39</v>
+      </c>
+      <c r="AF239" s="14" t="n"/>
+      <c r="AG239" s="14" t="n">
+        <v>0.025201</v>
+      </c>
+      <c r="AH239" s="14" t="inlineStr"/>
+      <c r="AI239" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ239" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK239" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL239" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM239" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN239" s="14" t="inlineStr"/>
+      <c r="AO239" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP239" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ239" s="14" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="AR239" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS239" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT239" s="14" t="inlineStr"/>
+      <c r="AU239" s="14" t="inlineStr"/>
+      <c r="AV239" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW239" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX239" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B240" s="14" t="n">
+        <v>0.04287333</v>
+      </c>
+      <c r="C240" s="14" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="D240" s="14" t="n">
+        <v>0.04477</v>
+      </c>
+      <c r="E240" s="14" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="F240" s="14" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="G240" s="14" t="n">
+        <v>3185451.18</v>
+      </c>
+      <c r="H240" s="14" t="inlineStr"/>
+      <c r="I240" s="14" t="n">
+        <v>0.00022522</v>
+      </c>
+      <c r="J240" s="14" t="n">
+        <v>6.698e-05</v>
+      </c>
+      <c r="K240" s="14" t="n">
+        <v>0.00034895</v>
+      </c>
+      <c r="L240" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M240" s="14" t="n">
+        <v>5434094.11095984</v>
+      </c>
+      <c r="N240" s="14" t="n">
+        <v>130843248</v>
+      </c>
+      <c r="O240" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P240" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q240" s="14" t="n">
+        <v>2.07029369</v>
+      </c>
+      <c r="R240" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T240" s="14" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="U240" s="14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V240" s="14" t="inlineStr"/>
+      <c r="W240" s="14" t="inlineStr"/>
+      <c r="X240" s="14" t="inlineStr"/>
+      <c r="Y240" s="14" t="inlineStr"/>
+      <c r="Z240" s="14" t="inlineStr"/>
+      <c r="AA240" s="14" t="inlineStr"/>
+      <c r="AB240" s="14" t="inlineStr"/>
+      <c r="AC240" s="14" t="inlineStr"/>
+      <c r="AD240" s="14" t="inlineStr"/>
+      <c r="AE240" s="14" t="n">
+        <v>234377.68</v>
+      </c>
+      <c r="AF240" s="14" t="n"/>
+      <c r="AG240" s="14" t="n">
+        <v>0.043131</v>
+      </c>
+      <c r="AH240" s="14" t="inlineStr"/>
+      <c r="AI240" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ240" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK240" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL240" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM240" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN240" s="14" t="inlineStr"/>
+      <c r="AO240" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP240" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ240" s="14" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="AR240" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS240" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT240" s="14" t="inlineStr"/>
+      <c r="AU240" s="14" t="inlineStr"/>
+      <c r="AV240" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW240" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX240" s="14" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -34558,7 +34432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34598,7 +34472,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -34608,7 +34482,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>GUA listed on Binance Alpha (ALPHA_483)</t>
+          <t>GUA Alpha listing date unknown — CAN OPERATOR</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
@@ -34617,7 +34491,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -34627,7 +34501,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GUAUSDT perp listed on Binance fapi (onboardDate)</t>
+          <t>GUA perp onboard date unknown — CAN OPERATOR</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
@@ -35188,17 +35062,17 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>VOL_8X_MED14</t>
+          <t>DUMP_GT10PCT</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>vol_vs_med14=9.2x taker=47.4748 ret=13.491722%</t>
+          <t>ret_1d=-25.77756833% vol_vs_m=28.29 taker=None</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
@@ -35211,17 +35085,17 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>VOL_8X_MED14</t>
+          <t>DUMP_GT10PCT</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>vol_vs_med14=23.61x taker=51.4213 ret=27.778079%</t>
+          <t>ret_1d=-11.63793103% vol_vs_m=1.03 taker=None</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
@@ -35234,17 +35108,17 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>VOL_8X_MED14</t>
+          <t>DUMP_GT10PCT</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>vol_vs_med14=24.06x taker=51.5631 ret=1.939646%</t>
+          <t>ret_1d=-10.46563193% vol_vs_m=0.76 taker=None</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
@@ -35257,7 +35131,7 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -35267,7 +35141,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>vol_vs_med14=15.18x taker=50.5764 ret=-9.834291%</t>
+          <t>vol_vs_med14=9.2x taker=47.4748 ret=13.491722%</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
@@ -35280,7 +35154,7 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -35290,7 +35164,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>vol_vs_med14=12.71x taker=52.1656 ret=11.775317%</t>
+          <t>vol_vs_med14=23.61x taker=51.4213 ret=27.778079%</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
@@ -35303,7 +35177,7 @@
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -35313,7 +35187,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>vol_vs_med14=14.59x taker=50.3609 ret=32.535828%</t>
+          <t>vol_vs_med14=24.06x taker=51.5631 ret=1.939646%</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
@@ -35326,7 +35200,7 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
@@ -35336,7 +35210,7 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>vol_vs_med14=13.02x taker=51.0623 ret=-6.71284%</t>
+          <t>vol_vs_med14=15.18x taker=50.5764 ret=-9.834291%</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
@@ -35349,7 +35223,7 @@
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
@@ -35359,7 +35233,7 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>vol_vs_med14=11.05x taker=51.6516 ret=12.69377%</t>
+          <t>vol_vs_med14=12.71x taker=52.1656 ret=11.775317%</t>
         </is>
       </c>
       <c r="D35" s="18" t="inlineStr">
@@ -35372,25 +35246,140 @@
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=14.59x taker=50.3609 ret=32.535828%</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=13.02x taker=51.0623 ret=-6.71284%</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=11.05x taker=51.6516 ret=12.69377%</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>VOL_8X_MED14</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>vol_vs_med14=10.06x taker=49.2546 ret=-72.604611%</t>
         </is>
       </c>
-      <c r="D36" s="18" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr"/>
+      <c r="E39" s="18" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=98.49x taker=None ret=69.39861629%</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=28.29x taker=None ret=-25.77756833%</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/case_files/CASE_GUA.xlsx
+++ b/docs/case_files/CASE_GUA.xlsx
@@ -790,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX240"/>
+  <dimension ref="A1:AX241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1272,10 +1272,8 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW3" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW3" s="14" t="b">
+        <v>0</v>
       </c>
       <c r="AX3" s="14" t="inlineStr">
         <is>
@@ -1408,15 +1406,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW4" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX4" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW4" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1544,15 +1538,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW5" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX5" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW5" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1680,15 +1670,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW6" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX6" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW6" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1816,15 +1802,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW7" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX7" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW7" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1952,15 +1934,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW8" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX8" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW8" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2088,15 +2066,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW9" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX9" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW9" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2224,15 +2198,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW10" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX10" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW10" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2360,15 +2330,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW11" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX11" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW11" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2496,15 +2462,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW12" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX12" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW12" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2632,15 +2594,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW13" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX13" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW13" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2768,15 +2726,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW14" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX14" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW14" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2904,15 +2858,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW15" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX15" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW15" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3040,15 +2990,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW16" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX16" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW16" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3178,15 +3124,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW17" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX17" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW17" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3316,15 +3258,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW18" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX18" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW18" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3454,15 +3392,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW19" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX19" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW19" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX19" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3592,15 +3526,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW20" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX20" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW20" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX20" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3730,15 +3660,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW21" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX21" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW21" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3868,15 +3794,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW22" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX22" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW22" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX22" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4006,15 +3928,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW23" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX23" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW23" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX23" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4148,15 +4066,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW24" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX24" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW24" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX24" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4286,15 +4200,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW25" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX25" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW25" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX25" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -4428,15 +4338,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW26" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX26" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW26" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX26" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4566,15 +4472,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW27" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX27" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW27" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX27" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4704,15 +4606,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW28" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX28" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW28" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX28" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4842,15 +4740,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW29" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX29" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW29" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX29" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4980,15 +4874,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW30" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX30" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW30" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX30" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -5118,15 +5008,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW31" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX31" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW31" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX31" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -5256,15 +5142,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW32" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX32" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW32" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX32" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -5394,15 +5276,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW33" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX33" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW33" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX33" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -5532,15 +5410,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW34" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX34" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW34" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -5670,15 +5544,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW35" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX35" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW35" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX35" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -5808,15 +5678,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW36" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX36" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW36" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX36" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -5946,15 +5812,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW37" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX37" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW37" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX37" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -6084,15 +5946,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW38" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX38" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW38" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX38" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -6222,15 +6080,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW39" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX39" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW39" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX39" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -6360,15 +6214,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW40" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX40" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW40" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX40" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -6498,15 +6348,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW41" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX41" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW41" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX41" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -6636,15 +6482,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW42" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX42" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW42" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX42" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6774,15 +6616,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW43" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX43" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW43" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX43" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -6912,15 +6750,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW44" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX44" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW44" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX44" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -7050,15 +6884,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW45" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX45" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW45" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX45" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -7188,15 +7018,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW46" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX46" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW46" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX46" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -7326,15 +7152,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW47" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX47" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW47" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX47" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -7464,15 +7286,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW48" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX48" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW48" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX48" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7602,15 +7420,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW49" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX49" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW49" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX49" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -7740,15 +7554,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW50" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX50" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW50" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX50" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -7878,15 +7688,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW51" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX51" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW51" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX51" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -8016,15 +7822,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW52" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX52" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW52" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX52" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -8158,15 +7960,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW53" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX53" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW53" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX53" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -8296,15 +8094,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW54" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX54" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW54" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX54" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -8434,15 +8228,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW55" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX55" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW55" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX55" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -8576,15 +8366,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW56" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX56" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW56" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX56" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -8718,15 +8504,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW57" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX57" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW57" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX57" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -8856,15 +8638,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW58" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX58" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW58" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX58" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -8994,15 +8772,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW59" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX59" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW59" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX59" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -9132,15 +8906,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW60" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX60" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW60" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX60" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -9270,15 +9040,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW61" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX61" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW61" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX61" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -9408,15 +9174,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW62" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX62" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW62" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX62" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -9546,15 +9308,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW63" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX63" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW63" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX63" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -9688,15 +9446,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW64" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX64" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW64" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX64" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -9826,15 +9580,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW65" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX65" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW65" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX65" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -9964,15 +9714,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW66" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX66" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW66" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX66" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -10102,15 +9848,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW67" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX67" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW67" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX67" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -10240,15 +9982,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW68" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX68" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW68" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX68" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -10378,15 +10116,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW69" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX69" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW69" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX69" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -10520,15 +10254,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW70" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX70" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW70" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX70" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -10658,15 +10388,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW71" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX71" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW71" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX71" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -10796,15 +10522,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW72" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX72" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW72" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX72" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -10934,15 +10656,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW73" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX73" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW73" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX73" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11072,15 +10790,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW74" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX74" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW74" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX74" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -11210,15 +10924,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW75" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX75" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW75" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX75" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -11348,15 +11058,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW76" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX76" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW76" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX76" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -11486,15 +11192,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW77" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX77" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW77" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX77" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -11624,15 +11326,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW78" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX78" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW78" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX78" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -11766,15 +11464,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW79" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX79" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW79" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX79" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -11904,15 +11598,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW80" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX80" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW80" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX80" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -12042,15 +11732,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW81" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX81" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW81" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX81" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -12184,15 +11870,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW82" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX82" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW82" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX82" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -12322,15 +12004,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW83" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX83" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW83" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX83" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -12460,15 +12138,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW84" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX84" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW84" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX84" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -12598,15 +12272,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW85" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX85" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW85" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX85" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -12736,15 +12406,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW86" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX86" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW86" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX86" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -12874,15 +12540,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW87" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX87" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW87" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX87" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -13012,15 +12674,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW88" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX88" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW88" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX88" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -13154,15 +12812,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW89" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX89" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW89" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX89" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -13292,15 +12946,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW90" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX90" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW90" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX90" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -13430,15 +13080,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW91" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX91" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW91" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX91" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -13572,15 +13218,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW92" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX92" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW92" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX92" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -13710,15 +13352,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW93" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX93" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW93" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX93" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -13852,15 +13490,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW94" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX94" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW94" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX94" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -13990,15 +13624,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW95" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX95" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW95" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX95" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -14128,15 +13758,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW96" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX96" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW96" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX96" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -14266,15 +13892,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW97" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX97" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW97" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX97" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -14408,15 +14030,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW98" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX98" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW98" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX98" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -14546,15 +14164,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW99" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX99" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW99" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX99" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -14688,15 +14302,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW100" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX100" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW100" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX100" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -14826,15 +14436,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW101" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX101" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW101" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX101" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -14964,15 +14570,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW102" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX102" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW102" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX102" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -15102,15 +14704,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW103" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX103" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW103" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX103" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -15244,15 +14842,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW104" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX104" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW104" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX104" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -15382,15 +14976,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW105" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX105" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW105" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX105" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -15520,15 +15110,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW106" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX106" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW106" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX106" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -15658,15 +15244,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW107" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX107" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW107" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX107" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -15796,15 +15378,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW108" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX108" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW108" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX108" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -15938,15 +15516,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW109" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX109" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW109" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX109" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -16076,15 +15650,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW110" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX110" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW110" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX110" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -16214,15 +15784,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW111" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX111" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW111" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX111" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -16352,15 +15918,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW112" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX112" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW112" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX112" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -16490,15 +16052,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW113" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX113" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW113" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX113" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -16632,15 +16190,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW114" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX114" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW114" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX114" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -16770,15 +16324,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW115" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX115" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW115" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX115" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -16908,15 +16458,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW116" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX116" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW116" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX116" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -17046,15 +16592,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW117" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX117" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW117" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX117" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -17184,15 +16726,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW118" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX118" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW118" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX118" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -17326,15 +16864,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW119" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX119" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW119" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX119" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -17464,15 +16998,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW120" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX120" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW120" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX120" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -17602,15 +17132,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW121" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX121" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW121" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX121" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -17740,15 +17266,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW122" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX122" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW122" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX122" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -17878,15 +17400,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW123" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX123" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW123" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX123" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -18016,15 +17534,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW124" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX124" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW124" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX124" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -18154,15 +17668,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW125" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX125" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW125" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX125" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -18296,15 +17806,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW126" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX126" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW126" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX126" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -18434,15 +17940,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW127" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX127" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW127" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX127" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -18572,15 +18074,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW128" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX128" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW128" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX128" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -18710,15 +18208,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW129" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX129" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW129" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX129" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -18848,15 +18342,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW130" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX130" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW130" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX130" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -18986,15 +18476,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW131" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX131" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW131" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX131" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -19124,15 +18610,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW132" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX132" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW132" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX132" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -19262,15 +18744,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW133" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX133" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW133" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX133" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -19400,15 +18878,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW134" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX134" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW134" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX134" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -19538,15 +19012,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW135" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX135" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW135" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX135" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -19676,15 +19146,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW136" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX136" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW136" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX136" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -19814,15 +19280,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW137" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX137" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW137" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX137" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -19952,15 +19414,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW138" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX138" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW138" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX138" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -20090,15 +19548,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW139" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX139" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW139" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX139" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -20228,15 +19682,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW140" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX140" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW140" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX140" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -20366,15 +19816,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW141" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX141" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW141" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX141" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -20504,15 +19950,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW142" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX142" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW142" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX142" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -20642,15 +20084,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW143" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX143" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW143" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX143" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -20780,15 +20218,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW144" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX144" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW144" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX144" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -20922,15 +20356,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW145" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX145" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW145" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX145" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -21060,15 +20490,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW146" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX146" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW146" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX146" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -21198,15 +20624,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW147" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX147" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW147" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX147" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -21336,15 +20758,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW148" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX148" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW148" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX148" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -21474,15 +20892,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW149" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX149" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW149" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX149" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -21612,15 +21026,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW150" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX150" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW150" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX150" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -21754,15 +21164,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW151" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX151" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW151" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX151" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -21896,15 +21302,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW152" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX152" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW152" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX152" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -22034,15 +21436,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW153" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX153" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW153" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX153" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -22172,15 +21570,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW154" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX154" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW154" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX154" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -22310,15 +21704,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW155" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX155" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW155" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX155" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -22452,15 +21842,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW156" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX156" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW156" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX156" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -22590,15 +21976,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW157" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX157" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW157" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX157" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -22732,15 +22114,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW158" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX158" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW158" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX158" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -22870,15 +22248,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW159" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX159" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW159" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX159" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -23008,15 +22382,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW160" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX160" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW160" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX160" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -23146,15 +22516,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW161" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX161" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW161" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX161" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -23284,15 +22650,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW162" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX162" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW162" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX162" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -23422,15 +22784,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW163" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX163" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW163" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX163" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -23564,15 +22922,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW164" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX164" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW164" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX164" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -23702,15 +23056,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW165" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX165" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW165" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX165" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -23840,15 +23190,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW166" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX166" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW166" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX166" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -23982,15 +23328,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW167" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX167" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW167" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX167" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -24120,15 +23462,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW168" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX168" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW168" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX168" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -24258,15 +23596,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW169" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX169" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW169" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX169" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -24396,15 +23730,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW170" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX170" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW170" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX170" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -24538,15 +23868,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW171" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX171" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW171" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX171" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -24676,15 +24002,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW172" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX172" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW172" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX172" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -24814,15 +24136,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW173" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX173" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW173" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX173" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -24952,15 +24270,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW174" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX174" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW174" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX174" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -25090,15 +24404,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW175" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX175" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW175" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX175" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -25228,15 +24538,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW176" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX176" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW176" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX176" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -25366,15 +24672,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW177" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX177" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW177" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX177" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -25504,15 +24806,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW178" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX178" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW178" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX178" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -25642,15 +24940,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW179" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX179" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW179" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX179" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -25780,15 +25074,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW180" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX180" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW180" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX180" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -25918,15 +25208,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW181" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX181" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW181" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX181" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -26056,15 +25342,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW182" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX182" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW182" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX182" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -26194,15 +25476,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW183" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX183" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW183" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX183" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -26332,15 +25610,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW184" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX184" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW184" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX184" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -26470,15 +25744,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW185" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX185" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW185" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX185" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -26608,15 +25878,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW186" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX186" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW186" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX186" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -26746,15 +26012,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW187" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX187" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW187" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX187" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -26884,15 +26146,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW188" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX188" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW188" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX188" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -27022,15 +26280,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW189" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX189" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW189" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX189" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -27160,15 +26414,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW190" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX190" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW190" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX190" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -27298,15 +26548,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW191" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX191" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW191" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX191" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -27436,15 +26682,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW192" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX192" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW192" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX192" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -27574,15 +26816,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW193" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX193" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW193" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX193" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -27645,15 +26883,25 @@
       <c r="U194" s="14" t="n">
         <v>0.38</v>
       </c>
-      <c r="V194" s="14" t="inlineStr"/>
+      <c r="V194" s="14" t="n">
+        <v>0.8287</v>
+      </c>
       <c r="W194" s="14" t="inlineStr"/>
       <c r="X194" s="14" t="inlineStr"/>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="inlineStr"/>
-      <c r="AA194" s="14" t="inlineStr"/>
-      <c r="AB194" s="14" t="inlineStr"/>
-      <c r="AC194" s="14" t="inlineStr"/>
-      <c r="AD194" s="14" t="inlineStr"/>
+      <c r="AA194" s="14" t="n">
+        <v>1.2129</v>
+      </c>
+      <c r="AB194" s="14" t="n">
+        <v>1.4637</v>
+      </c>
+      <c r="AC194" s="14" t="n">
+        <v>1.2462</v>
+      </c>
+      <c r="AD194" s="14" t="n">
+        <v>0.7679312376206273</v>
+      </c>
       <c r="AE194" s="14" t="n">
         <v>133763.5</v>
       </c>
@@ -27693,7 +26941,7 @@
       </c>
       <c r="AP194" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ194" s="14" t="inlineStr"/>
@@ -27714,15 +26962,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW194" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX194" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW194" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX194" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -27785,15 +27029,25 @@
       <c r="U195" s="14" t="n">
         <v>4.07</v>
       </c>
-      <c r="V195" s="14" t="inlineStr"/>
+      <c r="V195" s="14" t="n">
+        <v>0.7305</v>
+      </c>
       <c r="W195" s="14" t="inlineStr"/>
       <c r="X195" s="14" t="inlineStr"/>
       <c r="Y195" s="14" t="inlineStr"/>
       <c r="Z195" s="14" t="inlineStr"/>
-      <c r="AA195" s="14" t="inlineStr"/>
-      <c r="AB195" s="14" t="inlineStr"/>
-      <c r="AC195" s="14" t="inlineStr"/>
-      <c r="AD195" s="14" t="inlineStr"/>
+      <c r="AA195" s="14" t="n">
+        <v>1.1748</v>
+      </c>
+      <c r="AB195" s="14" t="n">
+        <v>1.6082</v>
+      </c>
+      <c r="AC195" s="14" t="n">
+        <v>1.3491</v>
+      </c>
+      <c r="AD195" s="14" t="n">
+        <v>0.8870390275210638</v>
+      </c>
       <c r="AE195" s="14" t="n">
         <v>2782883.09</v>
       </c>
@@ -27833,7 +27087,7 @@
       </c>
       <c r="AP195" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ195" s="14" t="inlineStr"/>
@@ -27854,15 +27108,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW195" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX195" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW195" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX195" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -27925,15 +27175,27 @@
       <c r="U196" s="14" t="n">
         <v>2.96</v>
       </c>
-      <c r="V196" s="14" t="inlineStr"/>
-      <c r="W196" s="14" t="inlineStr"/>
+      <c r="V196" s="14" t="n">
+        <v>0.5038</v>
+      </c>
+      <c r="W196" s="14" t="n">
+        <v>0.666</v>
+      </c>
       <c r="X196" s="14" t="inlineStr"/>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="14" t="inlineStr"/>
-      <c r="AA196" s="14" t="inlineStr"/>
-      <c r="AB196" s="14" t="inlineStr"/>
-      <c r="AC196" s="14" t="inlineStr"/>
-      <c r="AD196" s="14" t="inlineStr"/>
+      <c r="AA196" s="14" t="n">
+        <v>1.0622</v>
+      </c>
+      <c r="AB196" s="14" t="n">
+        <v>2.1085</v>
+      </c>
+      <c r="AC196" s="14" t="n">
+        <v>2.0012</v>
+      </c>
+      <c r="AD196" s="14" t="n">
+        <v>0.901265524513426</v>
+      </c>
       <c r="AE196" s="14" t="n">
         <v>424020.27</v>
       </c>
@@ -27973,7 +27235,7 @@
       </c>
       <c r="AP196" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ196" s="14" t="inlineStr"/>
@@ -27994,15 +27256,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW196" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX196" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW196" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX196" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -28065,15 +27323,31 @@
       <c r="U197" s="14" t="n">
         <v>0.55</v>
       </c>
-      <c r="V197" s="14" t="inlineStr"/>
-      <c r="W197" s="14" t="inlineStr"/>
+      <c r="V197" s="14" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="W197" s="14" t="n">
+        <v>0.5414</v>
+      </c>
       <c r="X197" s="14" t="inlineStr"/>
-      <c r="Y197" s="14" t="inlineStr"/>
-      <c r="Z197" s="14" t="inlineStr"/>
-      <c r="AA197" s="14" t="inlineStr"/>
-      <c r="AB197" s="14" t="inlineStr"/>
-      <c r="AC197" s="14" t="inlineStr"/>
-      <c r="AD197" s="14" t="inlineStr"/>
+      <c r="Y197" s="14" t="n">
+        <v>-13.1338</v>
+      </c>
+      <c r="Z197" s="14" t="n">
+        <v>61.324</v>
+      </c>
+      <c r="AA197" s="14" t="n">
+        <v>1.0536</v>
+      </c>
+      <c r="AB197" s="14" t="n">
+        <v>2.3613</v>
+      </c>
+      <c r="AC197" s="14" t="n">
+        <v>2.2113</v>
+      </c>
+      <c r="AD197" s="14" t="n">
+        <v>0.8702244940145547</v>
+      </c>
       <c r="AE197" s="14" t="n">
         <v>112152</v>
       </c>
@@ -28113,7 +27387,7 @@
       </c>
       <c r="AP197" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ197" s="14" t="inlineStr"/>
@@ -28134,15 +27408,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW197" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX197" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW197" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX197" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -28205,15 +27475,31 @@
       <c r="U198" s="14" t="n">
         <v>0.53</v>
       </c>
-      <c r="V198" s="14" t="inlineStr"/>
-      <c r="W198" s="14" t="inlineStr"/>
+      <c r="V198" s="14" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="W198" s="14" t="n">
+        <v>0.4753</v>
+      </c>
       <c r="X198" s="14" t="inlineStr"/>
-      <c r="Y198" s="14" t="inlineStr"/>
-      <c r="Z198" s="14" t="inlineStr"/>
-      <c r="AA198" s="14" t="inlineStr"/>
-      <c r="AB198" s="14" t="inlineStr"/>
-      <c r="AC198" s="14" t="inlineStr"/>
-      <c r="AD198" s="14" t="inlineStr"/>
+      <c r="Y198" s="14" t="n">
+        <v>-3.7283</v>
+      </c>
+      <c r="Z198" s="14" t="n">
+        <v>46.8288</v>
+      </c>
+      <c r="AA198" s="14" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="AB198" s="14" t="n">
+        <v>2.3613</v>
+      </c>
+      <c r="AC198" s="14" t="n">
+        <v>2.202</v>
+      </c>
+      <c r="AD198" s="14" t="n">
+        <v>0.8665818841929512</v>
+      </c>
       <c r="AE198" s="14" t="n">
         <v>41359.21</v>
       </c>
@@ -28253,7 +27539,7 @@
       </c>
       <c r="AP198" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ198" s="14" t="inlineStr"/>
@@ -28274,15 +27560,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW198" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX198" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW198" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX198" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -28345,15 +27627,33 @@
       <c r="U199" s="14" t="n">
         <v>0.45</v>
       </c>
-      <c r="V199" s="14" t="inlineStr"/>
-      <c r="W199" s="14" t="inlineStr"/>
-      <c r="X199" s="14" t="inlineStr"/>
-      <c r="Y199" s="14" t="inlineStr"/>
-      <c r="Z199" s="14" t="inlineStr"/>
-      <c r="AA199" s="14" t="inlineStr"/>
-      <c r="AB199" s="14" t="inlineStr"/>
-      <c r="AC199" s="14" t="inlineStr"/>
-      <c r="AD199" s="14" t="inlineStr"/>
+      <c r="V199" s="14" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="W199" s="14" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="X199" s="14" t="n">
+        <v>1.6343</v>
+      </c>
+      <c r="Y199" s="14" t="n">
+        <v>4.7449</v>
+      </c>
+      <c r="Z199" s="14" t="n">
+        <v>6.7062</v>
+      </c>
+      <c r="AA199" s="14" t="n">
+        <v>1.1126</v>
+      </c>
+      <c r="AB199" s="14" t="n">
+        <v>2.2499</v>
+      </c>
+      <c r="AC199" s="14" t="n">
+        <v>2.0367</v>
+      </c>
+      <c r="AD199" s="14" t="n">
+        <v>0.8760104412928778</v>
+      </c>
       <c r="AE199" s="14" t="n">
         <v>41513.48</v>
       </c>
@@ -28393,7 +27693,7 @@
       </c>
       <c r="AP199" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ199" s="14" t="inlineStr"/>
@@ -28414,15 +27714,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW199" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX199" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW199" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX199" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -28485,15 +27781,33 @@
       <c r="U200" s="14" t="n">
         <v>0.65</v>
       </c>
-      <c r="V200" s="14" t="inlineStr"/>
-      <c r="W200" s="14" t="inlineStr"/>
-      <c r="X200" s="14" t="inlineStr"/>
-      <c r="Y200" s="14" t="inlineStr"/>
-      <c r="Z200" s="14" t="inlineStr"/>
-      <c r="AA200" s="14" t="inlineStr"/>
-      <c r="AB200" s="14" t="inlineStr"/>
-      <c r="AC200" s="14" t="inlineStr"/>
-      <c r="AD200" s="14" t="inlineStr"/>
+      <c r="V200" s="14" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="W200" s="14" t="n">
+        <v>0.4931</v>
+      </c>
+      <c r="X200" s="14" t="n">
+        <v>1.3333</v>
+      </c>
+      <c r="Y200" s="14" t="n">
+        <v>-0.3037</v>
+      </c>
+      <c r="Z200" s="14" t="n">
+        <v>-12.4042</v>
+      </c>
+      <c r="AA200" s="14" t="n">
+        <v>1.0504</v>
+      </c>
+      <c r="AB200" s="14" t="n">
+        <v>2.0684</v>
+      </c>
+      <c r="AC200" s="14" t="n">
+        <v>1.7988</v>
+      </c>
+      <c r="AD200" s="14" t="n">
+        <v>0.7505972657923646</v>
+      </c>
       <c r="AE200" s="14" t="n">
         <v>85372.74000000001</v>
       </c>
@@ -28533,7 +27847,7 @@
       </c>
       <c r="AP200" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ200" s="14" t="inlineStr"/>
@@ -28554,15 +27868,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW200" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX200" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW200" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX200" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -28625,15 +27935,33 @@
       <c r="U201" s="14" t="n">
         <v>0.39</v>
       </c>
-      <c r="V201" s="14" t="inlineStr"/>
-      <c r="W201" s="14" t="inlineStr"/>
-      <c r="X201" s="14" t="inlineStr"/>
-      <c r="Y201" s="14" t="inlineStr"/>
-      <c r="Z201" s="14" t="inlineStr"/>
-      <c r="AA201" s="14" t="inlineStr"/>
-      <c r="AB201" s="14" t="inlineStr"/>
-      <c r="AC201" s="14" t="inlineStr"/>
-      <c r="AD201" s="14" t="inlineStr"/>
+      <c r="V201" s="14" t="n">
+        <v>0.5161</v>
+      </c>
+      <c r="W201" s="14" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="X201" s="14" t="n">
+        <v>0.8283</v>
+      </c>
+      <c r="Y201" s="14" t="n">
+        <v>-11.5827</v>
+      </c>
+      <c r="Z201" s="14" t="n">
+        <v>-17.9393</v>
+      </c>
+      <c r="AA201" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB201" s="14" t="n">
+        <v>1.9377</v>
+      </c>
+      <c r="AC201" s="14" t="n">
+        <v>1.6575</v>
+      </c>
+      <c r="AD201" s="14" t="n">
+        <v>0.920264352053598</v>
+      </c>
       <c r="AE201" s="14" t="n">
         <v>39359.1</v>
       </c>
@@ -28673,7 +28001,7 @@
       </c>
       <c r="AP201" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ201" s="14" t="inlineStr"/>
@@ -28694,15 +28022,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW201" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX201" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW201" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX201" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -28765,15 +28089,33 @@
       <c r="U202" s="14" t="n">
         <v>0.87</v>
       </c>
-      <c r="V202" s="14" t="inlineStr"/>
-      <c r="W202" s="14" t="inlineStr"/>
-      <c r="X202" s="14" t="inlineStr"/>
-      <c r="Y202" s="14" t="inlineStr"/>
-      <c r="Z202" s="14" t="inlineStr"/>
-      <c r="AA202" s="14" t="inlineStr"/>
-      <c r="AB202" s="14" t="inlineStr"/>
-      <c r="AC202" s="14" t="inlineStr"/>
-      <c r="AD202" s="14" t="inlineStr"/>
+      <c r="V202" s="14" t="n">
+        <v>0.5403</v>
+      </c>
+      <c r="W202" s="14" t="n">
+        <v>0.5206</v>
+      </c>
+      <c r="X202" s="14" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="Y202" s="14" t="n">
+        <v>-13.6707</v>
+      </c>
+      <c r="Z202" s="14" t="n">
+        <v>-20.9832</v>
+      </c>
+      <c r="AA202" s="14" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="AB202" s="14" t="n">
+        <v>1.7778</v>
+      </c>
+      <c r="AC202" s="14" t="n">
+        <v>1.5589</v>
+      </c>
+      <c r="AD202" s="14" t="n">
+        <v>0.8849337530411966</v>
+      </c>
       <c r="AE202" s="14" t="n">
         <v>31739.83</v>
       </c>
@@ -28813,7 +28155,7 @@
       </c>
       <c r="AP202" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ202" s="14" t="inlineStr"/>
@@ -28834,15 +28176,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW202" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX202" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW202" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX202" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -28905,15 +28243,33 @@
       <c r="U203" s="14" t="n">
         <v>0.76</v>
       </c>
-      <c r="V203" s="14" t="inlineStr"/>
-      <c r="W203" s="14" t="inlineStr"/>
-      <c r="X203" s="14" t="inlineStr"/>
-      <c r="Y203" s="14" t="inlineStr"/>
-      <c r="Z203" s="14" t="inlineStr"/>
-      <c r="AA203" s="14" t="inlineStr"/>
-      <c r="AB203" s="14" t="inlineStr"/>
-      <c r="AC203" s="14" t="inlineStr"/>
-      <c r="AD203" s="14" t="inlineStr"/>
+      <c r="V203" s="14" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="W203" s="14" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="X203" s="14" t="n">
+        <v>0.6886</v>
+      </c>
+      <c r="Y203" s="14" t="n">
+        <v>-10.4151</v>
+      </c>
+      <c r="Z203" s="14" t="n">
+        <v>-16.7908</v>
+      </c>
+      <c r="AA203" s="14" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AB203" s="14" t="n">
+        <v>1.7211</v>
+      </c>
+      <c r="AC203" s="14" t="n">
+        <v>1.5164</v>
+      </c>
+      <c r="AD203" s="14" t="n">
+        <v>0.9552042842085368</v>
+      </c>
       <c r="AE203" s="14" t="n">
         <v>707702.4</v>
       </c>
@@ -28953,7 +28309,7 @@
       </c>
       <c r="AP203" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ203" s="14" t="inlineStr"/>
@@ -28974,15 +28330,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW203" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX203" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW203" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX203" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -29045,15 +28397,33 @@
       <c r="U204" s="14" t="n">
         <v>0.43</v>
       </c>
-      <c r="V204" s="14" t="inlineStr"/>
-      <c r="W204" s="14" t="inlineStr"/>
-      <c r="X204" s="14" t="inlineStr"/>
-      <c r="Y204" s="14" t="inlineStr"/>
-      <c r="Z204" s="14" t="inlineStr"/>
-      <c r="AA204" s="14" t="inlineStr"/>
-      <c r="AB204" s="14" t="inlineStr"/>
-      <c r="AC204" s="14" t="inlineStr"/>
-      <c r="AD204" s="14" t="inlineStr"/>
+      <c r="V204" s="14" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="W204" s="14" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="X204" s="14" t="n">
+        <v>0.9019</v>
+      </c>
+      <c r="Y204" s="14" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="Z204" s="14" t="n">
+        <v>19.9618</v>
+      </c>
+      <c r="AA204" s="14" t="n">
+        <v>1.2367</v>
+      </c>
+      <c r="AB204" s="14" t="n">
+        <v>2.3245</v>
+      </c>
+      <c r="AC204" s="14" t="n">
+        <v>1.8369</v>
+      </c>
+      <c r="AD204" s="14" t="n">
+        <v>0.9636193042356076</v>
+      </c>
       <c r="AE204" s="14" t="n">
         <v>205184.69</v>
       </c>
@@ -29093,7 +28463,7 @@
       </c>
       <c r="AP204" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ204" s="14" t="inlineStr"/>
@@ -29114,15 +28484,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW204" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX204" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW204" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX204" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -29185,15 +28551,33 @@
       <c r="U205" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="V205" s="14" t="inlineStr"/>
-      <c r="W205" s="14" t="inlineStr"/>
-      <c r="X205" s="14" t="inlineStr"/>
-      <c r="Y205" s="14" t="inlineStr"/>
-      <c r="Z205" s="14" t="inlineStr"/>
-      <c r="AA205" s="14" t="inlineStr"/>
-      <c r="AB205" s="14" t="inlineStr"/>
-      <c r="AC205" s="14" t="inlineStr"/>
-      <c r="AD205" s="14" t="inlineStr"/>
+      <c r="V205" s="14" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="W205" s="14" t="n">
+        <v>0.5499000000000001</v>
+      </c>
+      <c r="X205" s="14" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="Y205" s="14" t="n">
+        <v>34.4404</v>
+      </c>
+      <c r="Z205" s="14" t="n">
+        <v>27.2697</v>
+      </c>
+      <c r="AA205" s="14" t="n">
+        <v>1.2913</v>
+      </c>
+      <c r="AB205" s="14" t="n">
+        <v>2.2626</v>
+      </c>
+      <c r="AC205" s="14" t="n">
+        <v>1.7949</v>
+      </c>
+      <c r="AD205" s="14" t="n">
+        <v>0.8727540911224712</v>
+      </c>
       <c r="AE205" s="14" t="n">
         <v>136096.67</v>
       </c>
@@ -29233,7 +28617,7 @@
       </c>
       <c r="AP205" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ205" s="14" t="inlineStr"/>
@@ -29254,15 +28638,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW205" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX205" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW205" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX205" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -29325,15 +28705,33 @@
       <c r="U206" s="14" t="n">
         <v>0.36</v>
       </c>
-      <c r="V206" s="14" t="inlineStr"/>
-      <c r="W206" s="14" t="inlineStr"/>
-      <c r="X206" s="14" t="inlineStr"/>
-      <c r="Y206" s="14" t="inlineStr"/>
-      <c r="Z206" s="14" t="inlineStr"/>
-      <c r="AA206" s="14" t="inlineStr"/>
-      <c r="AB206" s="14" t="inlineStr"/>
-      <c r="AC206" s="14" t="inlineStr"/>
-      <c r="AD206" s="14" t="inlineStr"/>
+      <c r="V206" s="14" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="W206" s="14" t="n">
+        <v>0.5355</v>
+      </c>
+      <c r="X206" s="14" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="Y206" s="14" t="n">
+        <v>35.101</v>
+      </c>
+      <c r="Z206" s="14" t="n">
+        <v>45.6917</v>
+      </c>
+      <c r="AA206" s="14" t="n">
+        <v>1.2713</v>
+      </c>
+      <c r="AB206" s="14" t="n">
+        <v>2.5075</v>
+      </c>
+      <c r="AC206" s="14" t="n">
+        <v>1.9824</v>
+      </c>
+      <c r="AD206" s="14" t="n">
+        <v>0.8911021333131565</v>
+      </c>
       <c r="AE206" s="14" t="n">
         <v>53541.13</v>
       </c>
@@ -29373,7 +28771,7 @@
       </c>
       <c r="AP206" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ206" s="14" t="inlineStr"/>
@@ -29394,15 +28792,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW206" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX206" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW206" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX206" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -29465,15 +28859,33 @@
       <c r="U207" s="14" t="n">
         <v>0.24</v>
       </c>
-      <c r="V207" s="14" t="inlineStr"/>
-      <c r="W207" s="14" t="inlineStr"/>
-      <c r="X207" s="14" t="inlineStr"/>
-      <c r="Y207" s="14" t="inlineStr"/>
-      <c r="Z207" s="14" t="inlineStr"/>
-      <c r="AA207" s="14" t="inlineStr"/>
-      <c r="AB207" s="14" t="inlineStr"/>
-      <c r="AC207" s="14" t="inlineStr"/>
-      <c r="AD207" s="14" t="inlineStr"/>
+      <c r="V207" s="14" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="W207" s="14" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="X207" s="14" t="n">
+        <v>1.3154</v>
+      </c>
+      <c r="Y207" s="14" t="n">
+        <v>3.3314</v>
+      </c>
+      <c r="Z207" s="14" t="n">
+        <v>8.2986</v>
+      </c>
+      <c r="AA207" s="14" t="n">
+        <v>1.2779</v>
+      </c>
+      <c r="AB207" s="14" t="n">
+        <v>2.5174</v>
+      </c>
+      <c r="AC207" s="14" t="n">
+        <v>2.0506</v>
+      </c>
+      <c r="AD207" s="14" t="n">
+        <v>0.9460859440335908</v>
+      </c>
       <c r="AE207" s="14" t="n">
         <v>11110</v>
       </c>
@@ -29513,7 +28925,7 @@
       </c>
       <c r="AP207" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ207" s="14" t="inlineStr"/>
@@ -29534,15 +28946,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW207" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX207" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW207" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX207" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -29605,15 +29013,33 @@
       <c r="U208" s="14" t="n">
         <v>0.23</v>
       </c>
-      <c r="V208" s="14" t="inlineStr"/>
-      <c r="W208" s="14" t="inlineStr"/>
-      <c r="X208" s="14" t="inlineStr"/>
-      <c r="Y208" s="14" t="inlineStr"/>
-      <c r="Z208" s="14" t="inlineStr"/>
-      <c r="AA208" s="14" t="inlineStr"/>
-      <c r="AB208" s="14" t="inlineStr"/>
-      <c r="AC208" s="14" t="inlineStr"/>
-      <c r="AD208" s="14" t="inlineStr"/>
+      <c r="V208" s="14" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="W208" s="14" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="X208" s="14" t="n">
+        <v>1.4617</v>
+      </c>
+      <c r="Y208" s="14" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="Z208" s="14" t="n">
+        <v>17.0468</v>
+      </c>
+      <c r="AA208" s="14" t="n">
+        <v>1.3024</v>
+      </c>
+      <c r="AB208" s="14" t="n">
+        <v>2.6483</v>
+      </c>
+      <c r="AC208" s="14" t="n">
+        <v>2.2165</v>
+      </c>
+      <c r="AD208" s="14" t="n">
+        <v>1.063482696234339</v>
+      </c>
       <c r="AE208" s="14" t="n">
         <v>19383.96</v>
       </c>
@@ -29653,7 +29079,7 @@
       </c>
       <c r="AP208" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ208" s="14" t="inlineStr"/>
@@ -29674,15 +29100,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW208" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX208" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW208" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX208" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -29745,15 +29167,33 @@
       <c r="U209" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="V209" s="14" t="inlineStr"/>
-      <c r="W209" s="14" t="inlineStr"/>
-      <c r="X209" s="14" t="inlineStr"/>
-      <c r="Y209" s="14" t="inlineStr"/>
-      <c r="Z209" s="14" t="inlineStr"/>
-      <c r="AA209" s="14" t="inlineStr"/>
-      <c r="AB209" s="14" t="inlineStr"/>
-      <c r="AC209" s="14" t="inlineStr"/>
-      <c r="AD209" s="14" t="inlineStr"/>
+      <c r="V209" s="14" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="W209" s="14" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="X209" s="14" t="n">
+        <v>1.7536</v>
+      </c>
+      <c r="Y209" s="14" t="n">
+        <v>2.1867</v>
+      </c>
+      <c r="Z209" s="14" t="n">
+        <v>50.8435</v>
+      </c>
+      <c r="AA209" s="14" t="n">
+        <v>1.2991</v>
+      </c>
+      <c r="AB209" s="14" t="n">
+        <v>3.7824</v>
+      </c>
+      <c r="AC209" s="14" t="n">
+        <v>3.2212</v>
+      </c>
+      <c r="AD209" s="14" t="n">
+        <v>0.9881075041911432</v>
+      </c>
       <c r="AE209" s="14" t="n">
         <v>57855.69</v>
       </c>
@@ -29793,7 +29233,7 @@
       </c>
       <c r="AP209" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ209" s="14" t="inlineStr"/>
@@ -29814,15 +29254,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW209" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX209" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW209" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX209" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -29885,15 +29321,33 @@
       <c r="U210" s="14" t="n">
         <v>0.37</v>
       </c>
-      <c r="V210" s="14" t="inlineStr"/>
-      <c r="W210" s="14" t="inlineStr"/>
-      <c r="X210" s="14" t="inlineStr"/>
-      <c r="Y210" s="14" t="inlineStr"/>
-      <c r="Z210" s="14" t="inlineStr"/>
-      <c r="AA210" s="14" t="inlineStr"/>
-      <c r="AB210" s="14" t="inlineStr"/>
-      <c r="AC210" s="14" t="inlineStr"/>
-      <c r="AD210" s="14" t="inlineStr"/>
+      <c r="V210" s="14" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="W210" s="14" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="X210" s="14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y210" s="14" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="Z210" s="14" t="n">
+        <v>70.3424</v>
+      </c>
+      <c r="AA210" s="14" t="n">
+        <v>1.2882</v>
+      </c>
+      <c r="AB210" s="14" t="n">
+        <v>4.2882</v>
+      </c>
+      <c r="AC210" s="14" t="n">
+        <v>3.6795</v>
+      </c>
+      <c r="AD210" s="14" t="n">
+        <v>0.921254476412496</v>
+      </c>
       <c r="AE210" s="14" t="n">
         <v>29601.74</v>
       </c>
@@ -29933,7 +29387,7 @@
       </c>
       <c r="AP210" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ210" s="14" t="inlineStr"/>
@@ -29954,15 +29408,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW210" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX210" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW210" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX210" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -30025,15 +29475,33 @@
       <c r="U211" s="14" t="n">
         <v>0.46</v>
       </c>
-      <c r="V211" s="14" t="inlineStr"/>
-      <c r="W211" s="14" t="inlineStr"/>
-      <c r="X211" s="14" t="inlineStr"/>
-      <c r="Y211" s="14" t="inlineStr"/>
-      <c r="Z211" s="14" t="inlineStr"/>
-      <c r="AA211" s="14" t="inlineStr"/>
-      <c r="AB211" s="14" t="inlineStr"/>
-      <c r="AC211" s="14" t="inlineStr"/>
-      <c r="AD211" s="14" t="inlineStr"/>
+      <c r="V211" s="14" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="W211" s="14" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="X211" s="14" t="n">
+        <v>1.7895</v>
+      </c>
+      <c r="Y211" s="14" t="n">
+        <v>-3.4628</v>
+      </c>
+      <c r="Z211" s="14" t="n">
+        <v>59.1134</v>
+      </c>
+      <c r="AA211" s="14" t="n">
+        <v>1.2573</v>
+      </c>
+      <c r="AB211" s="14" t="n">
+        <v>4.2138</v>
+      </c>
+      <c r="AC211" s="14" t="n">
+        <v>3.5475</v>
+      </c>
+      <c r="AD211" s="14" t="n">
+        <v>0.9358800562021976</v>
+      </c>
       <c r="AE211" s="14" t="n">
         <v>32022.5</v>
       </c>
@@ -30073,7 +29541,7 @@
       </c>
       <c r="AP211" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ211" s="14" t="inlineStr"/>
@@ -30094,15 +29562,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW211" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX211" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW211" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX211" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -30169,15 +29633,33 @@
       <c r="U212" s="14" t="n">
         <v>1.27</v>
       </c>
-      <c r="V212" s="14" t="inlineStr"/>
-      <c r="W212" s="14" t="inlineStr"/>
-      <c r="X212" s="14" t="inlineStr"/>
-      <c r="Y212" s="14" t="inlineStr"/>
-      <c r="Z212" s="14" t="inlineStr"/>
-      <c r="AA212" s="14" t="inlineStr"/>
-      <c r="AB212" s="14" t="inlineStr"/>
-      <c r="AC212" s="14" t="inlineStr"/>
-      <c r="AD212" s="14" t="inlineStr"/>
+      <c r="V212" s="14" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="W212" s="14" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="X212" s="14" t="n">
+        <v>1.6962</v>
+      </c>
+      <c r="Y212" s="14" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="Z212" s="14" t="n">
+        <v>13.3725</v>
+      </c>
+      <c r="AA212" s="14" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="AB212" s="14" t="n">
+        <v>4.2882</v>
+      </c>
+      <c r="AC212" s="14" t="n">
+        <v>3.4783</v>
+      </c>
+      <c r="AD212" s="14" t="n">
+        <v>0.926058610223794</v>
+      </c>
       <c r="AE212" s="14" t="n">
         <v>95765.56</v>
       </c>
@@ -30219,7 +29701,7 @@
       </c>
       <c r="AP212" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ212" s="14" t="inlineStr"/>
@@ -30240,15 +29722,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW212" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX212" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW212" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX212" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -30315,15 +29793,33 @@
       <c r="U213" s="14" t="n">
         <v>0.52</v>
       </c>
-      <c r="V213" s="14" t="inlineStr"/>
-      <c r="W213" s="14" t="inlineStr"/>
-      <c r="X213" s="14" t="inlineStr"/>
-      <c r="Y213" s="14" t="inlineStr"/>
-      <c r="Z213" s="14" t="inlineStr"/>
-      <c r="AA213" s="14" t="inlineStr"/>
-      <c r="AB213" s="14" t="inlineStr"/>
-      <c r="AC213" s="14" t="inlineStr"/>
-      <c r="AD213" s="14" t="inlineStr"/>
+      <c r="V213" s="14" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="W213" s="14" t="n">
+        <v>0.3059</v>
+      </c>
+      <c r="X213" s="14" t="n">
+        <v>1.5198</v>
+      </c>
+      <c r="Y213" s="14" t="n">
+        <v>3.3225</v>
+      </c>
+      <c r="Z213" s="14" t="n">
+        <v>-1.8003</v>
+      </c>
+      <c r="AA213" s="14" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="AB213" s="14" t="n">
+        <v>4.211</v>
+      </c>
+      <c r="AC213" s="14" t="n">
+        <v>3.3687</v>
+      </c>
+      <c r="AD213" s="14" t="n">
+        <v>0.9353820249988504</v>
+      </c>
       <c r="AE213" s="14" t="n">
         <v>53425.59</v>
       </c>
@@ -30365,7 +29861,7 @@
       </c>
       <c r="AP213" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ213" s="14" t="inlineStr"/>
@@ -30386,15 +29882,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW213" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX213" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW213" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX213" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -30461,15 +29953,33 @@
       <c r="U214" s="14" t="n">
         <v>0.55</v>
       </c>
-      <c r="V214" s="14" t="inlineStr"/>
-      <c r="W214" s="14" t="inlineStr"/>
-      <c r="X214" s="14" t="inlineStr"/>
-      <c r="Y214" s="14" t="inlineStr"/>
-      <c r="Z214" s="14" t="inlineStr"/>
-      <c r="AA214" s="14" t="inlineStr"/>
-      <c r="AB214" s="14" t="inlineStr"/>
-      <c r="AC214" s="14" t="inlineStr"/>
-      <c r="AD214" s="14" t="inlineStr"/>
+      <c r="V214" s="14" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="W214" s="14" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="X214" s="14" t="n">
+        <v>1.1756</v>
+      </c>
+      <c r="Y214" s="14" t="n">
+        <v>3.6507</v>
+      </c>
+      <c r="Z214" s="14" t="n">
+        <v>8.624000000000001</v>
+      </c>
+      <c r="AA214" s="14" t="n">
+        <v>1.3032</v>
+      </c>
+      <c r="AB214" s="14" t="n">
+        <v>4.5772</v>
+      </c>
+      <c r="AC214" s="14" t="n">
+        <v>3.787</v>
+      </c>
+      <c r="AD214" s="14" t="n">
+        <v>1.009504528995584</v>
+      </c>
       <c r="AE214" s="14" t="n">
         <v>44008.16</v>
       </c>
@@ -30511,7 +30021,7 @@
       </c>
       <c r="AP214" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ214" s="14" t="inlineStr"/>
@@ -30532,15 +30042,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW214" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX214" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW214" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX214" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -30607,15 +30113,33 @@
       <c r="U215" s="14" t="n">
         <v>0.46</v>
       </c>
-      <c r="V215" s="14" t="inlineStr"/>
-      <c r="W215" s="14" t="inlineStr"/>
-      <c r="X215" s="14" t="inlineStr"/>
-      <c r="Y215" s="14" t="inlineStr"/>
-      <c r="Z215" s="14" t="inlineStr"/>
-      <c r="AA215" s="14" t="inlineStr"/>
-      <c r="AB215" s="14" t="inlineStr"/>
-      <c r="AC215" s="14" t="inlineStr"/>
-      <c r="AD215" s="14" t="inlineStr"/>
+      <c r="V215" s="14" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="W215" s="14" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="X215" s="14" t="n">
+        <v>1.1386</v>
+      </c>
+      <c r="Y215" s="14" t="n">
+        <v>3.259</v>
+      </c>
+      <c r="Z215" s="14" t="n">
+        <v>11.3218</v>
+      </c>
+      <c r="AA215" s="14" t="n">
+        <v>1.3434</v>
+      </c>
+      <c r="AB215" s="14" t="n">
+        <v>4.7737</v>
+      </c>
+      <c r="AC215" s="14" t="n">
+        <v>4.1894</v>
+      </c>
+      <c r="AD215" s="14" t="n">
+        <v>0.9791226188321752</v>
+      </c>
       <c r="AE215" s="14" t="n">
         <v>11469.32</v>
       </c>
@@ -30657,7 +30181,7 @@
       </c>
       <c r="AP215" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ215" s="14" t="inlineStr"/>
@@ -30678,15 +30202,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW215" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX215" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW215" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX215" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -30753,15 +30273,33 @@
       <c r="U216" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="V216" s="14" t="inlineStr"/>
-      <c r="W216" s="14" t="inlineStr"/>
-      <c r="X216" s="14" t="inlineStr"/>
-      <c r="Y216" s="14" t="inlineStr"/>
-      <c r="Z216" s="14" t="inlineStr"/>
-      <c r="AA216" s="14" t="inlineStr"/>
-      <c r="AB216" s="14" t="inlineStr"/>
-      <c r="AC216" s="14" t="inlineStr"/>
-      <c r="AD216" s="14" t="inlineStr"/>
+      <c r="V216" s="14" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="W216" s="14" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="X216" s="14" t="n">
+        <v>1.3107</v>
+      </c>
+      <c r="Y216" s="14" t="n">
+        <v>15.5071</v>
+      </c>
+      <c r="Z216" s="14" t="n">
+        <v>26.8392</v>
+      </c>
+      <c r="AA216" s="14" t="n">
+        <v>1.5374</v>
+      </c>
+      <c r="AB216" s="14" t="n">
+        <v>5.3412</v>
+      </c>
+      <c r="AC216" s="14" t="n">
+        <v>4.6497</v>
+      </c>
+      <c r="AD216" s="14" t="n">
+        <v>0.948862942852872</v>
+      </c>
       <c r="AE216" s="14" t="n">
         <v>30876.93</v>
       </c>
@@ -30803,7 +30341,7 @@
       </c>
       <c r="AP216" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ216" s="14" t="inlineStr"/>
@@ -30824,15 +30362,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW216" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX216" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW216" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX216" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -30970,15 +30504,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW217" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX217" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW217" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX217" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -31116,15 +30646,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW218" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX218" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW218" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX218" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -31264,15 +30790,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW219" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX219" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW219" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX219" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -31341,15 +30863,27 @@
       <c r="U220" s="14" t="n">
         <v>0.91</v>
       </c>
-      <c r="V220" s="14" t="inlineStr"/>
+      <c r="V220" s="14" t="n">
+        <v>0.2396</v>
+      </c>
       <c r="W220" s="14" t="inlineStr"/>
-      <c r="X220" s="14" t="inlineStr"/>
+      <c r="X220" s="14" t="n">
+        <v>1.3033</v>
+      </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="inlineStr"/>
-      <c r="AA220" s="14" t="inlineStr"/>
-      <c r="AB220" s="14" t="inlineStr"/>
-      <c r="AC220" s="14" t="inlineStr"/>
-      <c r="AD220" s="14" t="inlineStr"/>
+      <c r="AA220" s="14" t="n">
+        <v>1.5157</v>
+      </c>
+      <c r="AB220" s="14" t="n">
+        <v>6.326</v>
+      </c>
+      <c r="AC220" s="14" t="n">
+        <v>5.4599</v>
+      </c>
+      <c r="AD220" s="14" t="n">
+        <v>0.8959</v>
+      </c>
       <c r="AE220" s="14" t="n">
         <v>22504.32</v>
       </c>
@@ -31391,7 +30925,7 @@
       </c>
       <c r="AP220" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ220" s="14" t="inlineStr"/>
@@ -31412,15 +30946,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW220" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX220" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW220" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX220" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -31489,15 +31019,27 @@
       <c r="U221" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="V221" s="14" t="inlineStr"/>
+      <c r="V221" s="14" t="n">
+        <v>0.2725</v>
+      </c>
       <c r="W221" s="14" t="inlineStr"/>
-      <c r="X221" s="14" t="inlineStr"/>
+      <c r="X221" s="14" t="n">
+        <v>1.1158</v>
+      </c>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="inlineStr"/>
-      <c r="AA221" s="14" t="inlineStr"/>
-      <c r="AB221" s="14" t="inlineStr"/>
-      <c r="AC221" s="14" t="inlineStr"/>
-      <c r="AD221" s="14" t="inlineStr"/>
+      <c r="AA221" s="14" t="n">
+        <v>1.5063</v>
+      </c>
+      <c r="AB221" s="14" t="n">
+        <v>5.5274</v>
+      </c>
+      <c r="AC221" s="14" t="n">
+        <v>5.1881</v>
+      </c>
+      <c r="AD221" s="14" t="n">
+        <v>0.9723000000000001</v>
+      </c>
       <c r="AE221" s="14" t="n">
         <v>58851.03</v>
       </c>
@@ -31539,7 +31081,7 @@
       </c>
       <c r="AP221" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ221" s="14" t="n">
@@ -31562,15 +31104,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW221" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX221" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW221" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX221" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -31639,15 +31177,27 @@
       <c r="U222" s="14" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="V222" s="14" t="inlineStr"/>
-      <c r="W222" s="14" t="inlineStr"/>
+      <c r="V222" s="14" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="W222" s="14" t="n">
+        <v>0.2476</v>
+      </c>
       <c r="X222" s="14" t="inlineStr"/>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="inlineStr"/>
-      <c r="AA222" s="14" t="inlineStr"/>
-      <c r="AB222" s="14" t="inlineStr"/>
-      <c r="AC222" s="14" t="inlineStr"/>
-      <c r="AD222" s="14" t="inlineStr"/>
+      <c r="AA222" s="14" t="n">
+        <v>1.4063</v>
+      </c>
+      <c r="AB222" s="14" t="n">
+        <v>6.0323</v>
+      </c>
+      <c r="AC222" s="14" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AD222" s="14" t="n">
+        <v>0.8143</v>
+      </c>
       <c r="AE222" s="14" t="n">
         <v>13101.86</v>
       </c>
@@ -31689,7 +31239,7 @@
       </c>
       <c r="AP222" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ222" s="14" t="n">
@@ -31712,15 +31262,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW222" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX222" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW222" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX222" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -31789,15 +31335,31 @@
       <c r="U223" s="14" t="n">
         <v>0.67</v>
       </c>
-      <c r="V223" s="14" t="inlineStr"/>
-      <c r="W223" s="14" t="inlineStr"/>
+      <c r="V223" s="14" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="W223" s="14" t="n">
+        <v>0.2471</v>
+      </c>
       <c r="X223" s="14" t="inlineStr"/>
-      <c r="Y223" s="14" t="inlineStr"/>
-      <c r="Z223" s="14" t="inlineStr"/>
-      <c r="AA223" s="14" t="inlineStr"/>
-      <c r="AB223" s="14" t="inlineStr"/>
-      <c r="AC223" s="14" t="inlineStr"/>
-      <c r="AD223" s="14" t="inlineStr"/>
+      <c r="Y223" s="14" t="n">
+        <v>-5.067</v>
+      </c>
+      <c r="Z223" s="14" t="n">
+        <v>-4.4072</v>
+      </c>
+      <c r="AA223" s="14" t="n">
+        <v>1.4389</v>
+      </c>
+      <c r="AB223" s="14" t="n">
+        <v>6.0472</v>
+      </c>
+      <c r="AC223" s="14" t="n">
+        <v>5.8074</v>
+      </c>
+      <c r="AD223" s="14" t="n">
+        <v>1.059</v>
+      </c>
       <c r="AE223" s="14" t="n">
         <v>36979.92</v>
       </c>
@@ -31839,7 +31401,7 @@
       </c>
       <c r="AP223" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ223" s="14" t="n">
@@ -31862,15 +31424,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW223" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX223" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW223" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX223" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -31939,15 +31497,31 @@
       <c r="U224" s="14" t="n">
         <v>0.71</v>
       </c>
-      <c r="V224" s="14" t="inlineStr"/>
-      <c r="W224" s="14" t="inlineStr"/>
+      <c r="V224" s="14" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="W224" s="14" t="n">
+        <v>0.2324</v>
+      </c>
       <c r="X224" s="14" t="inlineStr"/>
-      <c r="Y224" s="14" t="inlineStr"/>
-      <c r="Z224" s="14" t="inlineStr"/>
-      <c r="AA224" s="14" t="inlineStr"/>
-      <c r="AB224" s="14" t="inlineStr"/>
-      <c r="AC224" s="14" t="inlineStr"/>
-      <c r="AD224" s="14" t="inlineStr"/>
+      <c r="Y224" s="14" t="n">
+        <v>-8.2653</v>
+      </c>
+      <c r="Z224" s="14" t="n">
+        <v>10.5836</v>
+      </c>
+      <c r="AA224" s="14" t="n">
+        <v>1.3818</v>
+      </c>
+      <c r="AB224" s="14" t="n">
+        <v>6.1124</v>
+      </c>
+      <c r="AC224" s="14" t="n">
+        <v>5.9348</v>
+      </c>
+      <c r="AD224" s="14" t="n">
+        <v>0.9112</v>
+      </c>
       <c r="AE224" s="14" t="n">
         <v>14252.88</v>
       </c>
@@ -31989,7 +31563,7 @@
       </c>
       <c r="AP224" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ224" s="14" t="n">
@@ -32012,15 +31586,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW224" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX224" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW224" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX224" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -32089,15 +31659,33 @@
       <c r="U225" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="V225" s="14" t="inlineStr"/>
-      <c r="W225" s="14" t="inlineStr"/>
-      <c r="X225" s="14" t="inlineStr"/>
-      <c r="Y225" s="14" t="inlineStr"/>
-      <c r="Z225" s="14" t="inlineStr"/>
-      <c r="AA225" s="14" t="inlineStr"/>
-      <c r="AB225" s="14" t="inlineStr"/>
-      <c r="AC225" s="14" t="inlineStr"/>
-      <c r="AD225" s="14" t="inlineStr"/>
+      <c r="V225" s="14" t="n">
+        <v>0.2282</v>
+      </c>
+      <c r="W225" s="14" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="X225" s="14" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="Y225" s="14" t="n">
+        <v>-2.8515</v>
+      </c>
+      <c r="Z225" s="14" t="n">
+        <v>-0.7327</v>
+      </c>
+      <c r="AA225" s="14" t="n">
+        <v>1.3662</v>
+      </c>
+      <c r="AB225" s="14" t="n">
+        <v>5.9881</v>
+      </c>
+      <c r="AC225" s="14" t="n">
+        <v>5.7659</v>
+      </c>
+      <c r="AD225" s="14" t="n">
+        <v>0.7979000000000001</v>
+      </c>
       <c r="AE225" s="14" t="n">
         <v>11130.76</v>
       </c>
@@ -32139,7 +31727,7 @@
       </c>
       <c r="AP225" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ225" s="14" t="n">
@@ -32162,15 +31750,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW225" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX225" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW225" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX225" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -32239,15 +31823,33 @@
       <c r="U226" s="14" t="n">
         <v>1.08</v>
       </c>
-      <c r="V226" s="14" t="inlineStr"/>
-      <c r="W226" s="14" t="inlineStr"/>
-      <c r="X226" s="14" t="inlineStr"/>
-      <c r="Y226" s="14" t="inlineStr"/>
-      <c r="Z226" s="14" t="inlineStr"/>
-      <c r="AA226" s="14" t="inlineStr"/>
-      <c r="AB226" s="14" t="inlineStr"/>
-      <c r="AC226" s="14" t="inlineStr"/>
-      <c r="AD226" s="14" t="inlineStr"/>
+      <c r="V226" s="14" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="W226" s="14" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="X226" s="14" t="n">
+        <v>1.1247</v>
+      </c>
+      <c r="Y226" s="14" t="n">
+        <v>-7.6656</v>
+      </c>
+      <c r="Z226" s="14" t="n">
+        <v>-0.6532</v>
+      </c>
+      <c r="AA226" s="14" t="n">
+        <v>1.3286</v>
+      </c>
+      <c r="AB226" s="14" t="n">
+        <v>6.0077</v>
+      </c>
+      <c r="AC226" s="14" t="n">
+        <v>5.8353</v>
+      </c>
+      <c r="AD226" s="14" t="n">
+        <v>0.8895</v>
+      </c>
       <c r="AE226" s="14" t="n">
         <v>38621.3</v>
       </c>
@@ -32289,7 +31891,7 @@
       </c>
       <c r="AP226" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ226" s="14" t="n">
@@ -32312,15 +31914,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW226" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX226" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW226" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX226" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -32389,15 +31987,33 @@
       <c r="U227" s="14" t="n">
         <v>1.27</v>
       </c>
-      <c r="V227" s="14" t="inlineStr"/>
-      <c r="W227" s="14" t="inlineStr"/>
-      <c r="X227" s="14" t="inlineStr"/>
-      <c r="Y227" s="14" t="inlineStr"/>
-      <c r="Z227" s="14" t="inlineStr"/>
-      <c r="AA227" s="14" t="inlineStr"/>
-      <c r="AB227" s="14" t="inlineStr"/>
-      <c r="AC227" s="14" t="inlineStr"/>
-      <c r="AD227" s="14" t="inlineStr"/>
+      <c r="V227" s="14" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="W227" s="14" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="X227" s="14" t="n">
+        <v>0.8801</v>
+      </c>
+      <c r="Y227" s="14" t="n">
+        <v>-4.3349</v>
+      </c>
+      <c r="Z227" s="14" t="n">
+        <v>-13.6591</v>
+      </c>
+      <c r="AA227" s="14" t="n">
+        <v>1.3219</v>
+      </c>
+      <c r="AB227" s="14" t="n">
+        <v>5.2775</v>
+      </c>
+      <c r="AC227" s="14" t="n">
+        <v>5.2189</v>
+      </c>
+      <c r="AD227" s="14" t="n">
+        <v>0.8398</v>
+      </c>
       <c r="AE227" s="14" t="n">
         <v>23900.05</v>
       </c>
@@ -32439,7 +32055,7 @@
       </c>
       <c r="AP227" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ227" s="14" t="n">
@@ -32462,15 +32078,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW227" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX227" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW227" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX227" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -32539,15 +32151,33 @@
       <c r="U228" s="14" t="n">
         <v>1.85</v>
       </c>
-      <c r="V228" s="14" t="inlineStr"/>
-      <c r="W228" s="14" t="inlineStr"/>
-      <c r="X228" s="14" t="inlineStr"/>
-      <c r="Y228" s="14" t="inlineStr"/>
-      <c r="Z228" s="14" t="inlineStr"/>
-      <c r="AA228" s="14" t="inlineStr"/>
-      <c r="AB228" s="14" t="inlineStr"/>
-      <c r="AC228" s="14" t="inlineStr"/>
-      <c r="AD228" s="14" t="inlineStr"/>
+      <c r="V228" s="14" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="W228" s="14" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="X228" s="14" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="Y228" s="14" t="n">
+        <v>-5.1749</v>
+      </c>
+      <c r="Z228" s="14" t="n">
+        <v>-7.3362</v>
+      </c>
+      <c r="AA228" s="14" t="n">
+        <v>1.2955</v>
+      </c>
+      <c r="AB228" s="14" t="n">
+        <v>5.5488</v>
+      </c>
+      <c r="AC228" s="14" t="n">
+        <v>5.2893</v>
+      </c>
+      <c r="AD228" s="14" t="n">
+        <v>0.8413</v>
+      </c>
       <c r="AE228" s="14" t="n">
         <v>50956.47</v>
       </c>
@@ -32589,7 +32219,7 @@
       </c>
       <c r="AP228" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ228" s="14" t="n">
@@ -32612,15 +32242,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW228" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX228" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW228" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX228" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -32689,15 +32315,33 @@
       <c r="U229" s="14" t="n">
         <v>3.05</v>
       </c>
-      <c r="V229" s="14" t="inlineStr"/>
-      <c r="W229" s="14" t="inlineStr"/>
-      <c r="X229" s="14" t="inlineStr"/>
-      <c r="Y229" s="14" t="inlineStr"/>
-      <c r="Z229" s="14" t="inlineStr"/>
-      <c r="AA229" s="14" t="inlineStr"/>
-      <c r="AB229" s="14" t="inlineStr"/>
-      <c r="AC229" s="14" t="inlineStr"/>
-      <c r="AD229" s="14" t="inlineStr"/>
+      <c r="V229" s="14" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="W229" s="14" t="n">
+        <v>0.2429</v>
+      </c>
+      <c r="X229" s="14" t="n">
+        <v>0.8303</v>
+      </c>
+      <c r="Y229" s="14" t="n">
+        <v>-0.9634</v>
+      </c>
+      <c r="Z229" s="14" t="n">
+        <v>-10.6247</v>
+      </c>
+      <c r="AA229" s="14" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="AB229" s="14" t="n">
+        <v>5.3694</v>
+      </c>
+      <c r="AC229" s="14" t="n">
+        <v>4.9277</v>
+      </c>
+      <c r="AD229" s="14" t="n">
+        <v>0.8472</v>
+      </c>
       <c r="AE229" s="14" t="n">
         <v>77532.52</v>
       </c>
@@ -32739,7 +32383,7 @@
       </c>
       <c r="AP229" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ229" s="14" t="n">
@@ -32762,15 +32406,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW229" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX229" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW229" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX229" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -32839,15 +32479,33 @@
       <c r="U230" s="14" t="n">
         <v>4.07</v>
       </c>
-      <c r="V230" s="14" t="inlineStr"/>
-      <c r="W230" s="14" t="inlineStr"/>
-      <c r="X230" s="14" t="inlineStr"/>
-      <c r="Y230" s="14" t="inlineStr"/>
-      <c r="Z230" s="14" t="inlineStr"/>
-      <c r="AA230" s="14" t="inlineStr"/>
-      <c r="AB230" s="14" t="inlineStr"/>
-      <c r="AC230" s="14" t="inlineStr"/>
-      <c r="AD230" s="14" t="inlineStr"/>
+      <c r="V230" s="14" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="W230" s="14" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="X230" s="14" t="n">
+        <v>0.5974</v>
+      </c>
+      <c r="Y230" s="14" t="n">
+        <v>3.9413</v>
+      </c>
+      <c r="Z230" s="14" t="n">
+        <v>-33.711</v>
+      </c>
+      <c r="AA230" s="14" t="n">
+        <v>1.374</v>
+      </c>
+      <c r="AB230" s="14" t="n">
+        <v>3.4984</v>
+      </c>
+      <c r="AC230" s="14" t="n">
+        <v>3.4444</v>
+      </c>
+      <c r="AD230" s="14" t="n">
+        <v>0.7574</v>
+      </c>
       <c r="AE230" s="14" t="n">
         <v>114272.26</v>
       </c>
@@ -32889,7 +32547,7 @@
       </c>
       <c r="AP230" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ230" s="14" t="n">
@@ -32912,15 +32570,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW230" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX230" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW230" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX230" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -32989,15 +32643,33 @@
       <c r="U231" s="14" t="n">
         <v>7.49</v>
       </c>
-      <c r="V231" s="14" t="inlineStr"/>
-      <c r="W231" s="14" t="inlineStr"/>
-      <c r="X231" s="14" t="inlineStr"/>
-      <c r="Y231" s="14" t="inlineStr"/>
-      <c r="Z231" s="14" t="inlineStr"/>
-      <c r="AA231" s="14" t="inlineStr"/>
-      <c r="AB231" s="14" t="inlineStr"/>
-      <c r="AC231" s="14" t="inlineStr"/>
-      <c r="AD231" s="14" t="inlineStr"/>
+      <c r="V231" s="14" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="W231" s="14" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="X231" s="14" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="Y231" s="14" t="n">
+        <v>-5.8819</v>
+      </c>
+      <c r="Z231" s="14" t="n">
+        <v>-50.1946</v>
+      </c>
+      <c r="AA231" s="14" t="n">
+        <v>1.2193</v>
+      </c>
+      <c r="AB231" s="14" t="n">
+        <v>2.7636</v>
+      </c>
+      <c r="AC231" s="14" t="n">
+        <v>2.8745</v>
+      </c>
+      <c r="AD231" s="14" t="n">
+        <v>0.7357</v>
+      </c>
       <c r="AE231" s="14" t="n">
         <v>259988.49</v>
       </c>
@@ -33039,7 +32711,7 @@
       </c>
       <c r="AP231" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ231" s="14" t="n">
@@ -33062,15 +32734,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW231" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX231" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW231" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX231" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -33139,15 +32807,33 @@
       <c r="U232" s="14" t="n">
         <v>6.16</v>
       </c>
-      <c r="V232" s="14" t="inlineStr"/>
-      <c r="W232" s="14" t="inlineStr"/>
-      <c r="X232" s="14" t="inlineStr"/>
-      <c r="Y232" s="14" t="inlineStr"/>
-      <c r="Z232" s="14" t="inlineStr"/>
-      <c r="AA232" s="14" t="inlineStr"/>
-      <c r="AB232" s="14" t="inlineStr"/>
-      <c r="AC232" s="14" t="inlineStr"/>
-      <c r="AD232" s="14" t="inlineStr"/>
+      <c r="V232" s="14" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="W232" s="14" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="X232" s="14" t="n">
+        <v>0.5750999999999999</v>
+      </c>
+      <c r="Y232" s="14" t="n">
+        <v>-19.4786</v>
+      </c>
+      <c r="Z232" s="14" t="n">
+        <v>-45.56</v>
+      </c>
+      <c r="AA232" s="14" t="n">
+        <v>1.0595</v>
+      </c>
+      <c r="AB232" s="14" t="n">
+        <v>2.9231</v>
+      </c>
+      <c r="AC232" s="14" t="n">
+        <v>3.0016</v>
+      </c>
+      <c r="AD232" s="14" t="n">
+        <v>0.7575</v>
+      </c>
       <c r="AE232" s="14" t="n">
         <v>427662.49</v>
       </c>
@@ -33189,7 +32875,7 @@
       </c>
       <c r="AP232" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ232" s="14" t="n">
@@ -33212,15 +32898,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AW232" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX232" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW232" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX232" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -33289,15 +32971,33 @@
       <c r="U233" s="14" t="n">
         <v>4.51</v>
       </c>
-      <c r="V233" s="14" t="inlineStr"/>
-      <c r="W233" s="14" t="inlineStr"/>
-      <c r="X233" s="14" t="inlineStr"/>
-      <c r="Y233" s="14" t="inlineStr"/>
-      <c r="Z233" s="14" t="inlineStr"/>
-      <c r="AA233" s="14" t="inlineStr"/>
-      <c r="AB233" s="14" t="inlineStr"/>
-      <c r="AC233" s="14" t="inlineStr"/>
-      <c r="AD233" s="14" t="inlineStr"/>
+      <c r="V233" s="14" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="W233" s="14" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="X233" s="14" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="Y233" s="14" t="n">
+        <v>-21.0917</v>
+      </c>
+      <c r="Z233" s="14" t="n">
+        <v>-14.3837</v>
+      </c>
+      <c r="AA233" s="14" t="n">
+        <v>1.0842</v>
+      </c>
+      <c r="AB233" s="14" t="n">
+        <v>2.9952</v>
+      </c>
+      <c r="AC233" s="14" t="n">
+        <v>2.9231</v>
+      </c>
+      <c r="AD233" s="14" t="n">
+        <v>1.071</v>
+      </c>
       <c r="AE233" s="14" t="n">
         <v>1053263.05</v>
       </c>
@@ -33339,7 +33039,7 @@
       </c>
       <c r="AP233" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ233" s="14" t="n">
@@ -33362,15 +33062,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW233" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX233" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW233" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX233" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -33437,15 +33133,33 @@
       <c r="U234" s="14" t="n">
         <v>98.48999999999999</v>
       </c>
-      <c r="V234" s="14" t="inlineStr"/>
-      <c r="W234" s="14" t="inlineStr"/>
-      <c r="X234" s="14" t="inlineStr"/>
-      <c r="Y234" s="14" t="inlineStr"/>
-      <c r="Z234" s="14" t="inlineStr"/>
-      <c r="AA234" s="14" t="inlineStr"/>
-      <c r="AB234" s="14" t="inlineStr"/>
-      <c r="AC234" s="14" t="inlineStr"/>
-      <c r="AD234" s="14" t="inlineStr"/>
+      <c r="V234" s="14" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="W234" s="14" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="X234" s="14" t="n">
+        <v>0.6014</v>
+      </c>
+      <c r="Y234" s="14" t="n">
+        <v>12.0479</v>
+      </c>
+      <c r="Z234" s="14" t="n">
+        <v>13.7104</v>
+      </c>
+      <c r="AA234" s="14" t="n">
+        <v>1.3662</v>
+      </c>
+      <c r="AB234" s="14" t="n">
+        <v>3.1425</v>
+      </c>
+      <c r="AC234" s="14" t="n">
+        <v>2.9635</v>
+      </c>
+      <c r="AD234" s="14" t="n">
+        <v>0.9786</v>
+      </c>
       <c r="AE234" s="14" t="n">
         <v>2894411.87</v>
       </c>
@@ -33487,7 +33201,7 @@
       </c>
       <c r="AP234" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ234" s="14" t="n">
@@ -33510,15 +33224,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW234" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX234" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW234" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX234" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -33585,15 +33295,33 @@
       <c r="U235" s="14" t="n">
         <v>28.29</v>
       </c>
-      <c r="V235" s="14" t="inlineStr"/>
-      <c r="W235" s="14" t="inlineStr"/>
-      <c r="X235" s="14" t="inlineStr"/>
-      <c r="Y235" s="14" t="inlineStr"/>
-      <c r="Z235" s="14" t="inlineStr"/>
-      <c r="AA235" s="14" t="inlineStr"/>
-      <c r="AB235" s="14" t="inlineStr"/>
-      <c r="AC235" s="14" t="inlineStr"/>
-      <c r="AD235" s="14" t="inlineStr"/>
+      <c r="V235" s="14" t="n">
+        <v>0.6463</v>
+      </c>
+      <c r="W235" s="14" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="X235" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="Y235" s="14" t="n">
+        <v>49.8537</v>
+      </c>
+      <c r="Z235" s="14" t="n">
+        <v>-15.9591</v>
+      </c>
+      <c r="AA235" s="14" t="n">
+        <v>1.5877</v>
+      </c>
+      <c r="AB235" s="14" t="n">
+        <v>2.4566</v>
+      </c>
+      <c r="AC235" s="14" t="n">
+        <v>2.4247</v>
+      </c>
+      <c r="AD235" s="14" t="n">
+        <v>0.9156</v>
+      </c>
       <c r="AE235" s="14" t="n">
         <v>1299216.09</v>
       </c>
@@ -33635,7 +33363,7 @@
       </c>
       <c r="AP235" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ235" s="14" t="n">
@@ -33658,15 +33386,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW235" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX235" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW235" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX235" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -33733,15 +33457,33 @@
       <c r="U236" s="14" t="n">
         <v>4.42</v>
       </c>
-      <c r="V236" s="14" t="inlineStr"/>
-      <c r="W236" s="14" t="inlineStr"/>
-      <c r="X236" s="14" t="inlineStr"/>
-      <c r="Y236" s="14" t="inlineStr"/>
-      <c r="Z236" s="14" t="inlineStr"/>
-      <c r="AA236" s="14" t="inlineStr"/>
-      <c r="AB236" s="14" t="inlineStr"/>
-      <c r="AC236" s="14" t="inlineStr"/>
-      <c r="AD236" s="14" t="inlineStr"/>
+      <c r="V236" s="14" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="W236" s="14" t="n">
+        <v>0.5401</v>
+      </c>
+      <c r="X236" s="14" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="Y236" s="14" t="n">
+        <v>45.8956</v>
+      </c>
+      <c r="Z236" s="14" t="n">
+        <v>-6.5371</v>
+      </c>
+      <c r="AA236" s="14" t="n">
+        <v>1.5818</v>
+      </c>
+      <c r="AB236" s="14" t="n">
+        <v>2.7994</v>
+      </c>
+      <c r="AC236" s="14" t="n">
+        <v>2.6232</v>
+      </c>
+      <c r="AD236" s="14" t="n">
+        <v>0.9515</v>
+      </c>
       <c r="AE236" s="14" t="n">
         <v>820699.12</v>
       </c>
@@ -33783,7 +33525,7 @@
       </c>
       <c r="AP236" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ236" s="14" t="n">
@@ -33806,15 +33548,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW236" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX236" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW236" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX236" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -33881,15 +33619,33 @@
       <c r="U237" s="14" t="n">
         <v>1.03</v>
       </c>
-      <c r="V237" s="14" t="inlineStr"/>
-      <c r="W237" s="14" t="inlineStr"/>
-      <c r="X237" s="14" t="inlineStr"/>
-      <c r="Y237" s="14" t="inlineStr"/>
-      <c r="Z237" s="14" t="inlineStr"/>
-      <c r="AA237" s="14" t="inlineStr"/>
-      <c r="AB237" s="14" t="inlineStr"/>
-      <c r="AC237" s="14" t="inlineStr"/>
-      <c r="AD237" s="14" t="inlineStr"/>
+      <c r="V237" s="14" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="W237" s="14" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="X237" s="14" t="n">
+        <v>1.0579</v>
+      </c>
+      <c r="Y237" s="14" t="n">
+        <v>13.3363</v>
+      </c>
+      <c r="Z237" s="14" t="n">
+        <v>10.0493</v>
+      </c>
+      <c r="AA237" s="14" t="n">
+        <v>1.5484</v>
+      </c>
+      <c r="AB237" s="14" t="n">
+        <v>3.4583</v>
+      </c>
+      <c r="AC237" s="14" t="n">
+        <v>3.1754</v>
+      </c>
+      <c r="AD237" s="14" t="n">
+        <v>0.8469</v>
+      </c>
       <c r="AE237" s="14" t="n">
         <v>407637.62</v>
       </c>
@@ -33931,7 +33687,7 @@
       </c>
       <c r="AP237" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ237" s="14" t="n">
@@ -33954,15 +33710,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW237" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX237" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW237" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX237" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -34029,15 +33781,33 @@
       <c r="U238" s="14" t="n">
         <v>0.76</v>
       </c>
-      <c r="V238" s="14" t="inlineStr"/>
-      <c r="W238" s="14" t="inlineStr"/>
-      <c r="X238" s="14" t="inlineStr"/>
-      <c r="Y238" s="14" t="inlineStr"/>
-      <c r="Z238" s="14" t="inlineStr"/>
-      <c r="AA238" s="14" t="inlineStr"/>
-      <c r="AB238" s="14" t="inlineStr"/>
-      <c r="AC238" s="14" t="inlineStr"/>
-      <c r="AD238" s="14" t="inlineStr"/>
+      <c r="V238" s="14" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="W238" s="14" t="n">
+        <v>0.4637</v>
+      </c>
+      <c r="X238" s="14" t="n">
+        <v>1.1479</v>
+      </c>
+      <c r="Y238" s="14" t="n">
+        <v>0.7621</v>
+      </c>
+      <c r="Z238" s="14" t="n">
+        <v>60.5145</v>
+      </c>
+      <c r="AA238" s="14" t="n">
+        <v>1.5998</v>
+      </c>
+      <c r="AB238" s="14" t="n">
+        <v>3.9432</v>
+      </c>
+      <c r="AC238" s="14" t="n">
+        <v>3.3554</v>
+      </c>
+      <c r="AD238" s="14" t="n">
+        <v>0.8589</v>
+      </c>
       <c r="AE238" s="14" t="n">
         <v>262020.9</v>
       </c>
@@ -34079,7 +33849,7 @@
       </c>
       <c r="AP238" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ238" s="14" t="n">
@@ -34102,15 +33872,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW238" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX238" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW238" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX238" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -34177,15 +33943,33 @@
       <c r="U239" s="14" t="n">
         <v>0.4</v>
       </c>
-      <c r="V239" s="14" t="inlineStr"/>
-      <c r="W239" s="14" t="inlineStr"/>
-      <c r="X239" s="14" t="inlineStr"/>
-      <c r="Y239" s="14" t="inlineStr"/>
-      <c r="Z239" s="14" t="inlineStr"/>
-      <c r="AA239" s="14" t="inlineStr"/>
-      <c r="AB239" s="14" t="inlineStr"/>
-      <c r="AC239" s="14" t="inlineStr"/>
-      <c r="AD239" s="14" t="inlineStr"/>
+      <c r="V239" s="14" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="W239" s="14" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="X239" s="14" t="n">
+        <v>1.0183</v>
+      </c>
+      <c r="Y239" s="14" t="n">
+        <v>2.4782</v>
+      </c>
+      <c r="Z239" s="14" t="n">
+        <v>33.4965</v>
+      </c>
+      <c r="AA239" s="14" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="AB239" s="14" t="n">
+        <v>3.7371</v>
+      </c>
+      <c r="AC239" s="14" t="n">
+        <v>3.0177</v>
+      </c>
+      <c r="AD239" s="14" t="n">
+        <v>1.0176</v>
+      </c>
       <c r="AE239" s="14" t="n">
         <v>134566.39</v>
       </c>
@@ -34227,7 +34011,7 @@
       </c>
       <c r="AP239" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ239" s="14" t="n">
@@ -34250,15 +34034,11 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW239" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX239" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW239" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX239" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -34325,15 +34105,33 @@
       <c r="U240" s="14" t="n">
         <v>0.6</v>
       </c>
-      <c r="V240" s="14" t="inlineStr"/>
-      <c r="W240" s="14" t="inlineStr"/>
-      <c r="X240" s="14" t="inlineStr"/>
-      <c r="Y240" s="14" t="inlineStr"/>
-      <c r="Z240" s="14" t="inlineStr"/>
-      <c r="AA240" s="14" t="inlineStr"/>
-      <c r="AB240" s="14" t="inlineStr"/>
-      <c r="AC240" s="14" t="inlineStr"/>
-      <c r="AD240" s="14" t="inlineStr"/>
+      <c r="V240" s="14" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="W240" s="14" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="X240" s="14" t="n">
+        <v>1.4189</v>
+      </c>
+      <c r="Y240" s="14" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="Z240" s="14" t="n">
+        <v>21.6089</v>
+      </c>
+      <c r="AA240" s="14" t="n">
+        <v>1.5538</v>
+      </c>
+      <c r="AB240" s="14" t="n">
+        <v>4.2056</v>
+      </c>
+      <c r="AC240" s="14" t="n">
+        <v>3.4405</v>
+      </c>
+      <c r="AD240" s="14" t="n">
+        <v>0.7973</v>
+      </c>
       <c r="AE240" s="14" t="n">
         <v>234377.68</v>
       </c>
@@ -34375,7 +34173,7 @@
       </c>
       <c r="AP240" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch_store</t>
         </is>
       </c>
       <c r="AQ240" s="14" t="n">
@@ -34398,15 +34196,125 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AW240" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AX240" s="14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="AW240" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX240" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0.04217667</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.04062</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.04281</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1750576.01</v>
+      </c>
+      <c r="H241" t="n">
+        <v>52.1407</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.00024268</v>
+      </c>
+      <c r="J241" t="n">
+        <v>7.849e-05</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0.00054017</v>
+      </c>
+      <c r="L241" t="n">
+        <v>6</v>
+      </c>
+      <c r="M241" t="n">
+        <v>5365254.15250538</v>
+      </c>
+      <c r="N241" t="n">
+        <v>126560594</v>
+      </c>
+      <c r="O241" t="b">
+        <v>1</v>
+      </c>
+      <c r="P241" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="V241" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="W241" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="X241" t="n">
+        <v>1.5191</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>-4.7131</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>18.0792</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>1.5244</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>4.6561</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>3.985</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>1.0884</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>107060.18</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>0.019954</v>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>alpha_klines_bapi:107060</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>ABSTAIN(L-48_alpha_taker_broken)</t>
+        </is>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AW241" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX241" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -34432,7 +34340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -35380,6 +35288,114 @@
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EXCH_BAL_ADD</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>exchange balance +~40M tokens (30M→70M, ngày chính xác ~mid Jul, tracker range)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>operator on-chain feed 18/08 (khoảng ngày)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EXCH_BAL_ADD_IN_PUMP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>exchange balance +~62M tokens (68M→130M), NGAY SAU pump 05-08/08 = khuôn APR deposit-trong-pump</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>operator on-chain feed 18/08</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>WHALE_HOLDING_DROP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>whale holdings −97.5% trong 90d (đọc theo snapshot 18/08)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>operator on-chain feed 18/08</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PUMP_WINDOW</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>cú pump 05-08/08: xác định range giá + OI đỉnh (đọc DAILY riêng để chốt số)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>operator on-chain feed 18/08</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35431,9 +35447,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>amount_tokens</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DATA-GAP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[DATA-GAP] chưa xác định: total supply · circ supply · unlock schedule. Mâu thuẫn: 130M token exchange × $0.04281 = $5.57M &gt; MC tracker $1.98M → 3 khả năng: (a) MC tracker sai (dùng circ cũ), (b) 130M không phải circ (một phần lock), (c) exchange balance khác trader-owned. Cần contract on-chain + tracker source cụ thể.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>task 18/08 B5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>